--- a/data/PAHOL (TRY).xlsx
+++ b/data/PAHOL (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,12 +403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:G108"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -394,12 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -413,13 +447,22 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>254401</v>
+        <v>1490769</v>
       </c>
       <c r="C3">
-        <v>21031611</v>
+        <v>1377215924</v>
       </c>
       <c r="D3">
-        <v>797101</v>
+        <v>4862303.652870915</v>
+      </c>
+      <c r="E3">
+        <v>314064.21833425394</v>
+      </c>
+      <c r="F3">
+        <v>25964035.514074225</v>
+      </c>
+      <c r="G3">
+        <v>984040.5599759909</v>
       </c>
     </row>
     <row r="4">
@@ -457,13 +500,22 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>601404897</v>
+        <v>3236900263</v>
       </c>
       <c r="C10">
-        <v>587704054</v>
+        <v>3083937695</v>
       </c>
       <c r="D10">
-        <v>11838897</v>
+        <v>943827478.5001456</v>
+      </c>
+      <c r="E10">
+        <v>742448963.9533551</v>
+      </c>
+      <c r="F10">
+        <v>725534938.4899669</v>
+      </c>
+      <c r="G10">
+        <v>14615406.119648678</v>
       </c>
     </row>
     <row r="11">
@@ -501,13 +553,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>11691472</v>
+        <v>23871154</v>
       </c>
       <c r="C17">
-        <v>731042</v>
+        <v>11418</v>
       </c>
       <c r="D17">
-        <v>4619</v>
+        <v>6932338.5358901415</v>
+      </c>
+      <c r="E17">
+        <v>14433406.37362595</v>
+      </c>
+      <c r="F17">
+        <v>902489.1291368207</v>
+      </c>
+      <c r="G17">
+        <v>5702.267776014711</v>
       </c>
     </row>
     <row r="18">
@@ -530,13 +591,22 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>35988149</v>
+        <v>20669077</v>
       </c>
       <c r="C21">
-        <v>7956204</v>
+        <v>34313943</v>
       </c>
       <c r="D21">
-        <v>45691</v>
+        <v>38228193.67718177</v>
+      </c>
+      <c r="E21">
+        <v>44428244.71987791</v>
+      </c>
+      <c r="F21">
+        <v>9822127.253051478</v>
+      </c>
+      <c r="G21">
+        <v>56406.65013074003</v>
       </c>
     </row>
     <row r="22">
@@ -554,13 +624,22 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>649338919</v>
+        <v>3282931263</v>
       </c>
       <c r="C24">
-        <v>617422911</v>
+        <v>4495478980</v>
       </c>
       <c r="D24">
-        <v>12686308</v>
+        <v>993850314.3660884</v>
+      </c>
+      <c r="E24">
+        <v>801624679.2651932</v>
+      </c>
+      <c r="F24">
+        <v>762223590.3862294</v>
+      </c>
+      <c r="G24">
+        <v>15661555.597531425</v>
       </c>
     </row>
     <row r="25">
@@ -573,13 +652,22 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>31902963704</v>
+        <v>45951081228</v>
       </c>
       <c r="C26">
-        <v>30084876029</v>
+        <v>45151081228</v>
       </c>
       <c r="D26">
-        <v>11969421322</v>
+        <v>42187572271.874374</v>
+      </c>
+      <c r="E26">
+        <v>39384984171.614235</v>
+      </c>
+      <c r="F26">
+        <v>37140510743.92522</v>
+      </c>
+      <c r="G26">
+        <v>14776541567.868372</v>
       </c>
     </row>
     <row r="27">
@@ -647,10 +735,19 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>18296253</v>
+        <v>30291350</v>
       </c>
       <c r="C39">
-        <v>18849488</v>
+        <v>27804965</v>
+      </c>
+      <c r="D39">
+        <v>24646435.076365665</v>
+      </c>
+      <c r="E39">
+        <v>22587169.063371398</v>
+      </c>
+      <c r="F39">
+        <v>23270152.836769715</v>
       </c>
     </row>
     <row r="40">
@@ -693,13 +790,22 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>31921259957</v>
+        <v>45981372578</v>
       </c>
       <c r="C47">
-        <v>30103725517</v>
+        <v>45178886193</v>
       </c>
       <c r="D47">
-        <v>11969421322</v>
+        <v>42212218706.95073</v>
+      </c>
+      <c r="E47">
+        <v>39407571340.677605</v>
+      </c>
+      <c r="F47">
+        <v>37163780896.761986</v>
+      </c>
+      <c r="G47">
+        <v>14776541567.868372</v>
       </c>
     </row>
     <row r="48">
@@ -707,13 +813,22 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>32570598876</v>
+        <v>49264303841</v>
       </c>
       <c r="C48">
-        <v>30721148428</v>
+        <v>49674365173</v>
       </c>
       <c r="D48">
-        <v>11982107630</v>
+        <v>43206069021.31682</v>
+      </c>
+      <c r="E48">
+        <v>40209196019.94281</v>
+      </c>
+      <c r="F48">
+        <v>37926004487.14822</v>
+      </c>
+      <c r="G48">
+        <v>14792203123.465902</v>
       </c>
     </row>
     <row r="49">
@@ -726,10 +841,19 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>46875051</v>
+        <v>3858714</v>
       </c>
       <c r="C50">
-        <v>62681369</v>
+        <v>22337441</v>
+      </c>
+      <c r="D50">
+        <v>39732431.81044898</v>
+      </c>
+      <c r="E50">
+        <v>57868389.87147569</v>
+      </c>
+      <c r="F50">
+        <v>77381673.57729228</v>
       </c>
     </row>
     <row r="51">
@@ -752,13 +876,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>2080952</v>
+        <v>5885166</v>
       </c>
       <c r="C54">
-        <v>1159568</v>
+        <v>2483950</v>
       </c>
       <c r="D54">
-        <v>108466</v>
+        <v>4669775.089789203</v>
+      </c>
+      <c r="E54">
+        <v>2568985.8265930647</v>
+      </c>
+      <c r="F54">
+        <v>1431513.724463341</v>
+      </c>
+      <c r="G54">
+        <v>133903.9135295977</v>
       </c>
     </row>
     <row r="55">
@@ -766,13 +899,22 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>962531858</v>
+        <v>1265912688</v>
       </c>
       <c r="C55">
-        <v>904485833</v>
+        <v>1617930972</v>
       </c>
       <c r="D55">
-        <v>126782801</v>
+        <v>1431175009.4437845</v>
+      </c>
+      <c r="E55">
+        <v>1188268975.375832</v>
+      </c>
+      <c r="F55">
+        <v>1116609747.419933</v>
+      </c>
+      <c r="G55">
+        <v>156516449.59843814</v>
       </c>
     </row>
     <row r="56">
@@ -804,8 +946,11 @@
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="D61">
-        <v>1662437</v>
+      <c r="B61">
+        <v>24322438</v>
+      </c>
+      <c r="G61">
+        <v>2052318.8860694023</v>
       </c>
     </row>
     <row r="62">
@@ -813,10 +958,19 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>578276</v>
+        <v>1133784</v>
       </c>
       <c r="C62">
-        <v>292132</v>
+        <v>796617</v>
+      </c>
+      <c r="D62">
+        <v>739728.9670173022</v>
+      </c>
+      <c r="E62">
+        <v>713895.7784028325</v>
+      </c>
+      <c r="F62">
+        <v>360643.51660135406</v>
       </c>
     </row>
     <row r="63">
@@ -839,13 +993,22 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>1012066137</v>
+        <v>1301112790</v>
       </c>
       <c r="C66">
-        <v>968618902</v>
+        <v>1643548980</v>
       </c>
       <c r="D66">
-        <v>128553704</v>
+        <v>1476316945.3110402</v>
+      </c>
+      <c r="E66">
+        <v>1249420246.8523037</v>
+      </c>
+      <c r="F66">
+        <v>1195783578.23829</v>
+      </c>
+      <c r="G66">
+        <v>158702672.39803714</v>
       </c>
     </row>
     <row r="67">
@@ -857,8 +1020,11 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
-      <c r="C68">
-        <v>14094787</v>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>17400357.510551047</v>
       </c>
     </row>
     <row r="69">
@@ -921,13 +1087,22 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>1725472</v>
+        <v>3400323</v>
       </c>
       <c r="C80">
-        <v>1189075</v>
+        <v>2693216</v>
       </c>
       <c r="D80">
-        <v>7479</v>
+        <v>2630535.4522781405</v>
+      </c>
+      <c r="E80">
+        <v>2130137.1257881913</v>
+      </c>
+      <c r="F80">
+        <v>1467942.095734902</v>
+      </c>
+      <c r="G80">
+        <v>9233.007295261752</v>
       </c>
     </row>
     <row r="81">
@@ -940,13 +1115,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>1354546084</v>
+        <v>4687176131</v>
       </c>
       <c r="C82">
-        <v>948426197</v>
+        <v>4251100519</v>
       </c>
       <c r="D82">
-        <v>348282804</v>
+        <v>2269441776.686964</v>
+      </c>
+      <c r="E82">
+        <v>1672220066.2308114</v>
+      </c>
+      <c r="F82">
+        <v>1170855193.9246302</v>
+      </c>
+      <c r="G82">
+        <v>429963587.39754224</v>
       </c>
     </row>
     <row r="83">
@@ -959,13 +1143,22 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>1356271556</v>
+        <v>4690576454</v>
       </c>
       <c r="C84">
-        <v>963710059</v>
+        <v>4253793735</v>
       </c>
       <c r="D84">
-        <v>348290283</v>
+        <v>2272072312.139242</v>
+      </c>
+      <c r="E84">
+        <v>1674350203.3565996</v>
+      </c>
+      <c r="F84">
+        <v>1189723493.530916</v>
+      </c>
+      <c r="G84">
+        <v>429972820.40483755</v>
       </c>
     </row>
     <row r="85">
@@ -978,13 +1171,22 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>30202261183</v>
+        <v>43272614597</v>
       </c>
       <c r="C86">
-        <v>28788819467</v>
+        <v>43777022458</v>
       </c>
       <c r="D86">
-        <v>11505263643</v>
+        <v>39457679763.86654</v>
+      </c>
+      <c r="E86">
+        <v>37285425569.733894</v>
+      </c>
+      <c r="F86">
+        <v>35540497415.37901</v>
+      </c>
+      <c r="G86">
+        <v>14203527630.663029</v>
       </c>
     </row>
     <row r="87">
@@ -992,12 +1194,21 @@
         <v xml:space="preserve">    Ödenmiş Sermaye</v>
       </c>
       <c r="B87">
+        <v>20000000000</v>
+      </c>
+      <c r="C87">
+        <v>20000000000</v>
+      </c>
+      <c r="D87">
         <v>18000000000</v>
       </c>
-      <c r="C87">
+      <c r="E87">
         <v>18000000000</v>
       </c>
-      <c r="D87">
+      <c r="F87">
+        <v>18000000000</v>
+      </c>
+      <c r="G87">
         <v>6000000000</v>
       </c>
     </row>
@@ -1006,13 +1217,22 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>9134294801</v>
+        <v>15717661486</v>
       </c>
       <c r="C88">
-        <v>9134294801</v>
+        <v>15717661486</v>
       </c>
       <c r="D88">
-        <v>4107776113</v>
+        <v>15497946496.506775</v>
+      </c>
+      <c r="E88">
+        <v>15497946496.779785</v>
+      </c>
+      <c r="F88">
+        <v>15497946496.125776</v>
+      </c>
+      <c r="G88">
+        <v>6478295305.549067</v>
       </c>
     </row>
     <row r="89">
@@ -1044,6 +1264,12 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
+      <c r="B94">
+        <v>992901584</v>
+      </c>
+      <c r="C94">
+        <v>992901584</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -1060,10 +1286,19 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-505906</v>
+        <v>-902151</v>
       </c>
       <c r="C97">
-        <v>-87901</v>
+        <v>-618824</v>
+      </c>
+      <c r="D97">
+        <v>-767123.9544074934</v>
+      </c>
+      <c r="E97">
+        <v>-624553.2542741932</v>
+      </c>
+      <c r="F97">
+        <v>-108515.91880746868</v>
       </c>
     </row>
     <row r="98">
@@ -1076,10 +1311,19 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>191875</v>
+        <v>583037</v>
       </c>
       <c r="C99">
-        <v>191875</v>
+        <v>236870</v>
+      </c>
+      <c r="D99">
+        <v>236874.31375437306</v>
+      </c>
+      <c r="E99">
+        <v>236874.35148794606</v>
+      </c>
+      <c r="F99">
+        <v>236874.64787257355</v>
       </c>
     </row>
     <row r="100">
@@ -1102,10 +1346,19 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>1654420692</v>
+        <v>7066495175</v>
       </c>
       <c r="C103">
-        <v>1397295655</v>
+        <v>2042384776</v>
+      </c>
+      <c r="D103">
+        <v>2042422560.454719</v>
+      </c>
+      <c r="E103">
+        <v>2042422558.9875643</v>
+      </c>
+      <c r="F103">
+        <v>1724995451.0908372</v>
       </c>
     </row>
     <row r="104">
@@ -1113,13 +1366,22 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>1413859721</v>
+        <v>-504124534</v>
       </c>
       <c r="C104">
-        <v>257125037</v>
+        <v>5024456566</v>
       </c>
       <c r="D104">
-        <v>1397487530</v>
+        <v>3917840956.5457025</v>
+      </c>
+      <c r="E104">
+        <v>1745444192.8693335</v>
+      </c>
+      <c r="F104">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="G104">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="105">
@@ -1132,13 +1394,22 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>30202261183</v>
+        <v>43272614597</v>
       </c>
       <c r="C106">
-        <v>28788819467</v>
+        <v>43777022458</v>
       </c>
       <c r="D106">
-        <v>11505263643</v>
+        <v>39457679763.86654</v>
+      </c>
+      <c r="E106">
+        <v>37285425569.733894</v>
+      </c>
+      <c r="F106">
+        <v>35540497415.37901</v>
+      </c>
+      <c r="G106">
+        <v>14203527630.663029</v>
       </c>
     </row>
     <row r="107">
@@ -1146,13 +1417,22 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>32570598876</v>
+        <v>49264303841</v>
       </c>
       <c r="C107">
-        <v>30721148428</v>
+        <v>49674365173</v>
       </c>
       <c r="D107">
-        <v>11982107630</v>
+        <v>43206069021.31682</v>
+      </c>
+      <c r="E107">
+        <v>40209196019.94281</v>
+      </c>
+      <c r="F107">
+        <v>37926004487.14822</v>
+      </c>
+      <c r="G107">
+        <v>14792203123.465902</v>
       </c>
     </row>
     <row r="108">
@@ -1162,20 +1442,25 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,15 +1468,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1205,16 +1505,31 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1903540990</v>
+        <v>72257533</v>
       </c>
       <c r="C3">
-        <v>1223252607</v>
+        <v>8219234986.054043</v>
       </c>
       <c r="D3">
-        <v>700077260</v>
+        <v>5193237051.5875</v>
       </c>
       <c r="E3">
-        <v>1753262265</v>
+        <v>2349967622.3425293</v>
+      </c>
+      <c r="F3">
+        <v>1832451851</v>
+      </c>
+      <c r="G3">
+        <v>1510135077.3913946</v>
+      </c>
+      <c r="H3">
+        <v>1128360421.3177102</v>
+      </c>
+      <c r="I3">
+        <v>864262394.5483164</v>
+      </c>
+      <c r="J3">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="4">
@@ -1236,11 +1551,17 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="C7">
-        <v>-658797038</v>
-      </c>
       <c r="D7">
-        <v>-658797038</v>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>-813300957.0461059</v>
+      </c>
+      <c r="H7">
+        <v>-813300955.9468701</v>
+      </c>
+      <c r="I7">
+        <v>-813300957.0732496</v>
       </c>
     </row>
     <row r="8">
@@ -1248,16 +1569,31 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1903540990</v>
+        <v>72257533</v>
       </c>
       <c r="C8">
-        <v>564455569</v>
+        <v>8219234986.054043</v>
       </c>
       <c r="D8">
-        <v>41280222</v>
+        <v>5193237051.5875</v>
       </c>
       <c r="E8">
-        <v>1753262265</v>
+        <v>2349967622.3425293</v>
+      </c>
+      <c r="F8">
+        <v>1832451851</v>
+      </c>
+      <c r="G8">
+        <v>696834120.3452888</v>
+      </c>
+      <c r="H8">
+        <v>315059465.37084</v>
+      </c>
+      <c r="I8">
+        <v>50961437.47506681</v>
+      </c>
+      <c r="J8">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="9">
@@ -1285,16 +1621,31 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1903540990</v>
+        <v>72257533</v>
       </c>
       <c r="C13">
-        <v>564455569</v>
+        <v>8219234986.054043</v>
       </c>
       <c r="D13">
-        <v>41280222</v>
+        <v>5193237051.5875</v>
       </c>
       <c r="E13">
-        <v>1753262265</v>
+        <v>2349967622.3425293</v>
+      </c>
+      <c r="F13">
+        <v>1832451851</v>
+      </c>
+      <c r="G13">
+        <v>696834120.3452888</v>
+      </c>
+      <c r="H13">
+        <v>315059465.37084</v>
+      </c>
+      <c r="I13">
+        <v>50961437.47506681</v>
+      </c>
+      <c r="J13">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="14"/>
@@ -1303,16 +1654,31 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-82013284</v>
+        <v>-67174315</v>
       </c>
       <c r="C15">
-        <v>-78170903</v>
+        <v>-191338425.59233552</v>
       </c>
       <c r="D15">
-        <v>-38908532</v>
+        <v>-143530292.39473513</v>
       </c>
       <c r="E15">
-        <v>-5198123</v>
+        <v>-101247392.63008076</v>
+      </c>
+      <c r="F15">
+        <v>-37228211</v>
+      </c>
+      <c r="G15">
+        <v>-96503877.9629696</v>
+      </c>
+      <c r="H15">
+        <v>-68582313.97319451</v>
+      </c>
+      <c r="I15">
+        <v>-48033528.520380445</v>
+      </c>
+      <c r="J15">
+        <v>-6417209.196505936</v>
       </c>
     </row>
     <row r="16">
@@ -1330,13 +1696,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>52142</v>
+        <v>57843</v>
       </c>
       <c r="C18">
-        <v>38648</v>
+        <v>129855.30304194521</v>
       </c>
       <c r="D18">
-        <v>14170</v>
+        <v>166413.98359477552</v>
+      </c>
+      <c r="E18">
+        <v>64370.566437964735</v>
+      </c>
+      <c r="F18">
+        <v>21809</v>
+      </c>
+      <c r="G18">
+        <v>47712.098888120505</v>
+      </c>
+      <c r="H18">
+        <v>66605.32627508746</v>
+      </c>
+      <c r="I18">
+        <v>17493.209436269422</v>
       </c>
     </row>
     <row r="19">
@@ -1344,10 +1725,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-58243</v>
+        <v>-326456</v>
+      </c>
+      <c r="C19">
+        <v>-184756.45912910835</v>
       </c>
       <c r="D19">
-        <v>-399220</v>
+        <v>-199767.74821365994</v>
+      </c>
+      <c r="E19">
+        <v>-71902.39923758927</v>
+      </c>
+      <c r="F19">
+        <v>-51531</v>
+      </c>
+      <c r="H19">
+        <v>-21378.79276673339</v>
+      </c>
+      <c r="I19">
+        <v>-492846.7940118193</v>
       </c>
     </row>
     <row r="20">
@@ -1360,16 +1756,31 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1821521605</v>
+        <v>4814605</v>
       </c>
       <c r="C21">
-        <v>486323314</v>
+        <v>8027841659.30562</v>
       </c>
       <c r="D21">
-        <v>1986640</v>
+        <v>5049673405.428145</v>
       </c>
       <c r="E21">
-        <v>1748064142</v>
+        <v>2248712697.879649</v>
+      </c>
+      <c r="F21">
+        <v>1795193918</v>
+      </c>
+      <c r="G21">
+        <v>600377954.4812074</v>
+      </c>
+      <c r="H21">
+        <v>246522377.9311539</v>
+      </c>
+      <c r="I21">
+        <v>2452555.3701108177</v>
+      </c>
+      <c r="J21">
+        <v>2158027674.24408</v>
       </c>
     </row>
     <row r="22"/>
@@ -1428,16 +1839,31 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1821521605</v>
+        <v>4814605</v>
       </c>
       <c r="C33">
-        <v>486323314</v>
+        <v>8027841659.30562</v>
       </c>
       <c r="D33">
-        <v>1986640</v>
+        <v>5049673405.428145</v>
       </c>
       <c r="E33">
-        <v>1748064142</v>
+        <v>2248712697.879649</v>
+      </c>
+      <c r="F33">
+        <v>1795193918</v>
+      </c>
+      <c r="G33">
+        <v>600377954.4812074</v>
+      </c>
+      <c r="H33">
+        <v>246522377.9311539</v>
+      </c>
+      <c r="I33">
+        <v>2452555.3701108177</v>
+      </c>
+      <c r="J33">
+        <v>2158027674.24408</v>
       </c>
     </row>
     <row r="34"/>
@@ -1446,13 +1872,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>68637954</v>
+        <v>316591167</v>
       </c>
       <c r="C35">
-        <v>103261351</v>
+        <v>351175889.2086446</v>
       </c>
       <c r="D35">
-        <v>3602346</v>
+        <v>135972163.969999</v>
+      </c>
+      <c r="E35">
+        <v>84735222.62519595</v>
+      </c>
+      <c r="F35">
+        <v>47429557</v>
+      </c>
+      <c r="G35">
+        <v>127478647.8300051</v>
+      </c>
+      <c r="H35">
+        <v>38496549.948485695</v>
+      </c>
+      <c r="I35">
+        <v>4447183.700769754</v>
       </c>
     </row>
     <row r="36">
@@ -1460,16 +1901,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-123721683</v>
+        <v>-97190698</v>
       </c>
       <c r="C36">
-        <v>-254842828</v>
+        <v>-378524735.4353064</v>
       </c>
       <c r="D36">
-        <v>-103423916</v>
+        <v>-269470430.585682</v>
       </c>
       <c r="E36">
-        <v>-29963</v>
+        <v>-152737425.0195296</v>
+      </c>
+      <c r="F36">
+        <v>-69773823</v>
+      </c>
+      <c r="G36">
+        <v>-314609666.96748596</v>
+      </c>
+      <c r="H36">
+        <v>-35326766.401446894</v>
+      </c>
+      <c r="I36">
+        <v>-127679338.27149867</v>
+      </c>
+      <c r="J36">
+        <v>-36990.051823496164</v>
       </c>
     </row>
     <row r="37">
@@ -1477,16 +1933,31 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>189189442</v>
+        <v>125961784</v>
       </c>
       <c r="C37">
-        <v>629602831</v>
+        <v>382909133.7713632</v>
       </c>
       <c r="D37">
-        <v>636816128</v>
+        <v>337801670.9233967</v>
       </c>
       <c r="E37">
-        <v>-601408</v>
+        <v>233558964.85793552</v>
+      </c>
+      <c r="F37">
+        <v>148490344</v>
+      </c>
+      <c r="G37">
+        <v>777260000.358579</v>
+      </c>
+      <c r="H37">
+        <v>830530149.9567298</v>
+      </c>
+      <c r="I37">
+        <v>786164989.3788397</v>
+      </c>
+      <c r="J37">
+        <v>-742452.794682281</v>
       </c>
     </row>
     <row r="38">
@@ -1494,16 +1965,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>1955627318</v>
+        <v>350176858</v>
       </c>
       <c r="C38">
-        <v>964344668</v>
+        <v>8383401946.850322</v>
       </c>
       <c r="D38">
-        <v>538981198</v>
+        <v>5253976809.73586</v>
       </c>
       <c r="E38">
-        <v>1747432771</v>
+        <v>2414269460.3432508</v>
+      </c>
+      <c r="F38">
+        <v>1921339996</v>
+      </c>
+      <c r="G38">
+        <v>1190506935.7023053</v>
+      </c>
+      <c r="H38">
+        <v>1080222311.4349227</v>
+      </c>
+      <c r="I38">
+        <v>665385390.1782215</v>
+      </c>
+      <c r="J38">
+        <v>2157248231.397574</v>
       </c>
     </row>
     <row r="39"/>
@@ -1512,43 +1998,106 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-541767597</v>
+        <v>-854301392</v>
       </c>
       <c r="C40">
-        <v>-707219631</v>
+        <v>-3358852427.897002</v>
       </c>
       <c r="D40">
-        <v>-173609962</v>
+        <v>-1336135853.1901567</v>
       </c>
       <c r="E40">
-        <v>-349945241</v>
+        <v>-668825267.4739174</v>
+      </c>
+      <c r="F40">
+        <v>-621552231</v>
+      </c>
+      <c r="G40">
+        <v>-873079826.2689741</v>
+      </c>
+      <c r="H40">
+        <v>-561461096.8174993</v>
+      </c>
+      <c r="I40">
+        <v>-214325718.10083106</v>
+      </c>
+      <c r="J40">
+        <v>-432015906.28361166</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>-30266424</v>
+      </c>
+      <c r="C41">
+        <v>-2057094.8518471087</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>-989052.5203045836</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>-824034968</v>
+      </c>
+      <c r="C42">
+        <v>-3356795333.0451555</v>
+      </c>
+      <c r="D42">
+        <v>-1336135853.1901567</v>
+      </c>
+      <c r="F42">
+        <v>-621552231</v>
+      </c>
+      <c r="G42">
+        <v>-873079826.2689741</v>
+      </c>
+      <c r="H42">
+        <v>-560472044.2971947</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>1413859721</v>
+        <v>-504124534</v>
       </c>
       <c r="C43">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
       </c>
       <c r="D43">
-        <v>365371236</v>
+        <v>3917840956.5457025</v>
       </c>
       <c r="E43">
-        <v>1397487530</v>
+        <v>1745444192.8693335</v>
+      </c>
+      <c r="F43">
+        <v>1299787765</v>
+      </c>
+      <c r="G43">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="H43">
+        <v>518761214.6174233</v>
+      </c>
+      <c r="I43">
+        <v>451059672.07739043</v>
+      </c>
+      <c r="J43">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="44">
@@ -1562,38 +2111,86 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>1413859721</v>
+        <v>-504124534</v>
       </c>
       <c r="C46">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
       </c>
       <c r="D46">
-        <v>365371236</v>
+        <v>3917840956.5457025</v>
       </c>
       <c r="E46">
-        <v>1397487530</v>
+        <v>1745444192.8693335</v>
+      </c>
+      <c r="F46">
+        <v>1299787765</v>
+      </c>
+      <c r="G46">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="H46">
+        <v>518761214.6174233</v>
+      </c>
+      <c r="I46">
+        <v>451059672.07739043</v>
+      </c>
+      <c r="J46">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>1413859721</v>
+        <v>-504124534</v>
       </c>
       <c r="C48">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
       </c>
       <c r="D48">
-        <v>365371236</v>
+        <v>3917840956.5457025</v>
       </c>
       <c r="E48">
-        <v>1397487530</v>
+        <v>1745444192.8693335</v>
+      </c>
+      <c r="F48">
+        <v>1299787765</v>
+      </c>
+      <c r="G48">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="H48">
+        <v>518761214.6174233</v>
+      </c>
+      <c r="I48">
+        <v>451059672.07739043</v>
+      </c>
+      <c r="J48">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="49"/>
@@ -1602,31 +2199,51 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>2221210</v>
+        <v>1731018</v>
       </c>
       <c r="C50">
-        <v>3446848</v>
+        <v>5753800.939215167</v>
       </c>
       <c r="D50">
-        <v>1295755</v>
+        <v>4154904.1241498925</v>
+      </c>
+      <c r="E50">
+        <v>2742137.7369044465</v>
+      </c>
+      <c r="F50">
+        <v>1223258</v>
+      </c>
+      <c r="G50">
+        <v>4255217.591726501</v>
+      </c>
+      <c r="H50">
+        <v>2909701.1223204895</v>
+      </c>
+      <c r="I50">
+        <v>1599641.043972709</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1634,15 +2251,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1655,6 +2287,27 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
+      <c r="B3">
+        <v>72257533</v>
+      </c>
+      <c r="C3">
+        <v>3025997934.466543</v>
+      </c>
+      <c r="D3">
+        <v>2843269429.2449703</v>
+      </c>
+      <c r="E3">
+        <v>517515771.3425293</v>
+      </c>
+      <c r="F3">
+        <v>1832451851</v>
+      </c>
+      <c r="G3">
+        <v>381774656.07368445</v>
+      </c>
+      <c r="H3">
+        <v>264098026.7693938</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1675,11 +2328,38 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
+      <c r="G7">
+        <v>-1.0992357730865479</v>
+      </c>
+      <c r="H7">
+        <v>1.1263794898986816</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B8">
+        <v>72257533</v>
+      </c>
+      <c r="C8">
+        <v>3025997934.466543</v>
+      </c>
+      <c r="D8">
+        <v>2843269429.2449703</v>
+      </c>
+      <c r="E8">
+        <v>517515771.3425293</v>
+      </c>
+      <c r="F8">
+        <v>1832451851</v>
+      </c>
+      <c r="G8">
+        <v>381774654.97444874</v>
+      </c>
+      <c r="H8">
+        <v>264098027.8957732</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1704,6 +2384,27 @@
     <row r="13">
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>72257533</v>
+      </c>
+      <c r="C13">
+        <v>3025997934.466543</v>
+      </c>
+      <c r="D13">
+        <v>2843269429.2449703</v>
+      </c>
+      <c r="E13">
+        <v>517515771.3425293</v>
+      </c>
+      <c r="F13">
+        <v>1832451851</v>
+      </c>
+      <c r="G13">
+        <v>381774654.97444874</v>
+      </c>
+      <c r="H13">
+        <v>264098027.8957732</v>
       </c>
     </row>
     <row r="14"/>
@@ -1711,6 +2412,27 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
+      <c r="B15">
+        <v>-67174315</v>
+      </c>
+      <c r="C15">
+        <v>-47808133.197600394</v>
+      </c>
+      <c r="D15">
+        <v>-42282899.76465437</v>
+      </c>
+      <c r="E15">
+        <v>-64019181.63008076</v>
+      </c>
+      <c r="F15">
+        <v>-37228211</v>
+      </c>
+      <c r="G15">
+        <v>-27921563.98977509</v>
+      </c>
+      <c r="H15">
+        <v>-20548785.452814065</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1726,11 +2448,50 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
+      <c r="B18">
+        <v>57843</v>
+      </c>
+      <c r="C18">
+        <v>-36558.68055283031</v>
+      </c>
+      <c r="D18">
+        <v>102043.41715681078</v>
+      </c>
+      <c r="E18">
+        <v>42561.566437964735</v>
+      </c>
+      <c r="F18">
+        <v>21809</v>
+      </c>
+      <c r="G18">
+        <v>-18893.22738696695</v>
+      </c>
+      <c r="H18">
+        <v>49112.11683881804</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>-326456</v>
+      </c>
+      <c r="C19">
+        <v>15011.289084551594</v>
+      </c>
+      <c r="D19">
+        <v>-127865.34897607067</v>
+      </c>
+      <c r="E19">
+        <v>-20371.39923758927</v>
+      </c>
+      <c r="F19">
+        <v>-51531</v>
+      </c>
+      <c r="H19">
+        <v>471468.0012450859</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1740,6 +2501,27 @@
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>4814605</v>
+      </c>
+      <c r="C21">
+        <v>2978168253.877475</v>
+      </c>
+      <c r="D21">
+        <v>2800960707.5484962</v>
+      </c>
+      <c r="E21">
+        <v>453518779.87964916</v>
+      </c>
+      <c r="F21">
+        <v>1795193918</v>
+      </c>
+      <c r="G21">
+        <v>353855576.5500535</v>
+      </c>
+      <c r="H21">
+        <v>244069822.56104308</v>
       </c>
     </row>
     <row r="22"/>
@@ -1797,26 +2579,131 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
+      <c r="B33">
+        <v>4814605</v>
+      </c>
+      <c r="C33">
+        <v>2978168253.877475</v>
+      </c>
+      <c r="D33">
+        <v>2800960707.5484962</v>
+      </c>
+      <c r="E33">
+        <v>453518779.87964916</v>
+      </c>
+      <c r="F33">
+        <v>1795193918</v>
+      </c>
+      <c r="G33">
+        <v>353855576.5500535</v>
+      </c>
+      <c r="H33">
+        <v>244069822.56104308</v>
+      </c>
     </row>
     <row r="34"/>
     <row r="35">
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>316591167</v>
+      </c>
+      <c r="C35">
+        <v>215203725.23864564</v>
+      </c>
+      <c r="D35">
+        <v>51236941.344803035</v>
+      </c>
+      <c r="E35">
+        <v>37305665.62519595</v>
+      </c>
+      <c r="F35">
+        <v>47429557</v>
+      </c>
+      <c r="G35">
+        <v>88982097.8815194</v>
+      </c>
+      <c r="H35">
+        <v>34049366.24771594</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
+      <c r="B36">
+        <v>-97190698</v>
+      </c>
+      <c r="C36">
+        <v>-109054304.8496244</v>
+      </c>
+      <c r="D36">
+        <v>-116733005.56615236</v>
+      </c>
+      <c r="E36">
+        <v>-82963602.01952961</v>
+      </c>
+      <c r="F36">
+        <v>-69773823</v>
+      </c>
+      <c r="G36">
+        <v>-279282900.5660391</v>
+      </c>
+      <c r="H36">
+        <v>92352571.87005177</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>125961784</v>
+      </c>
+      <c r="C37">
+        <v>45107462.84796649</v>
+      </c>
+      <c r="D37">
+        <v>104242706.06546119</v>
+      </c>
+      <c r="E37">
+        <v>85068620.85793552</v>
+      </c>
+      <c r="F37">
+        <v>148490344</v>
+      </c>
+      <c r="G37">
+        <v>-53270149.59815073</v>
+      </c>
+      <c r="H37">
+        <v>44365160.57789004</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
+      </c>
+      <c r="B38">
+        <v>350176858</v>
+      </c>
+      <c r="C38">
+        <v>3129425137.114462</v>
+      </c>
+      <c r="D38">
+        <v>2839707349.392609</v>
+      </c>
+      <c r="E38">
+        <v>492929464.34325075</v>
+      </c>
+      <c r="F38">
+        <v>1921339996</v>
+      </c>
+      <c r="G38">
+        <v>110284624.26738262</v>
+      </c>
+      <c r="H38">
+        <v>414836921.25670123</v>
       </c>
     </row>
     <row r="39"/>
@@ -1824,20 +2711,83 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>-854301392</v>
+      </c>
+      <c r="C40">
+        <v>-2022716574.7068455</v>
+      </c>
+      <c r="D40">
+        <v>-667310585.7162393</v>
+      </c>
+      <c r="E40">
+        <v>-47273036.473917365</v>
+      </c>
+      <c r="F40">
+        <v>-621552231</v>
+      </c>
+      <c r="G40">
+        <v>-311618729.4514748</v>
+      </c>
+      <c r="H40">
+        <v>-347135378.71666825</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>-30266424</v>
+      </c>
+      <c r="C41">
+        <v>-2057094.8518471087</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>-824034968</v>
+      </c>
+      <c r="C42">
+        <v>-2020659479.8549988</v>
+      </c>
+      <c r="F42">
+        <v>-621552231</v>
+      </c>
+      <c r="G42">
+        <v>-312607781.97177935</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B43">
+        <v>-504124534</v>
+      </c>
+      <c r="C43">
+        <v>1106708562.407617</v>
+      </c>
+      <c r="D43">
+        <v>2172396763.6763687</v>
+      </c>
+      <c r="E43">
+        <v>445656427.8693335</v>
+      </c>
+      <c r="F43">
+        <v>1299787765</v>
+      </c>
+      <c r="G43">
+        <v>-201334105.18409193</v>
+      </c>
+      <c r="H43">
+        <v>67701542.54003286</v>
       </c>
     </row>
     <row r="44">
@@ -1850,15 +2800,69 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B46">
+        <v>-504124534</v>
+      </c>
+      <c r="C46">
+        <v>1106708562.407617</v>
+      </c>
+      <c r="D46">
+        <v>2172396763.6763687</v>
+      </c>
+      <c r="E46">
+        <v>445656427.8693335</v>
+      </c>
+      <c r="F46">
+        <v>1299787765</v>
+      </c>
+      <c r="G46">
+        <v>-201334105.18409193</v>
+      </c>
+      <c r="H46">
+        <v>67701542.54003286</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
+      </c>
+      <c r="B48">
+        <v>-504124534</v>
+      </c>
+      <c r="C48">
+        <v>1106708562.407617</v>
+      </c>
+      <c r="D48">
+        <v>2172396763.6763687</v>
+      </c>
+      <c r="E48">
+        <v>445656427.8693335</v>
+      </c>
+      <c r="F48">
+        <v>1299787765</v>
+      </c>
+      <c r="G48">
+        <v>-201334105.18409193</v>
+      </c>
+      <c r="H48">
+        <v>67701542.54003286</v>
       </c>
     </row>
     <row r="49"/>
@@ -1866,23 +2870,49 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
+      <c r="B50">
+        <v>1731018</v>
+      </c>
+      <c r="C50">
+        <v>1598896.815065275</v>
+      </c>
+      <c r="D50">
+        <v>1412766.387245446</v>
+      </c>
+      <c r="E50">
+        <v>1518879.7369044465</v>
+      </c>
+      <c r="F50">
+        <v>1223258</v>
+      </c>
+      <c r="G50">
+        <v>1345516.469406011</v>
+      </c>
+      <c r="H50">
+        <v>1310060.0783477805</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1890,15 +2920,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1912,13 +2957,22 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>2426716337</v>
+        <v>6459040668.054043</v>
       </c>
       <c r="C3">
-        <v>1223252607</v>
+        <v>8219234986.054043</v>
+      </c>
+      <c r="D3">
+        <v>5575011707.661184</v>
       </c>
       <c r="E3">
-        <v>1753262265</v>
+        <v>2995840305.261649</v>
+      </c>
+      <c r="G3">
+        <v>1510135077.3913946</v>
+      </c>
+      <c r="J3">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="4">
@@ -1940,8 +2994,11 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="C7">
-        <v>-658797038</v>
+      <c r="D7">
+        <v>-1.0992357730865479</v>
+      </c>
+      <c r="G7">
+        <v>-813300957.0461059</v>
       </c>
     </row>
     <row r="8">
@@ -1949,13 +3006,22 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>2426716337</v>
+        <v>6459040668.054043</v>
       </c>
       <c r="C8">
-        <v>564455569</v>
+        <v>8219234986.054043</v>
+      </c>
+      <c r="D8">
+        <v>5575011706.561949</v>
       </c>
       <c r="E8">
-        <v>1753262265</v>
+        <v>2995840305.261649</v>
+      </c>
+      <c r="G8">
+        <v>696834120.3452888</v>
+      </c>
+      <c r="J8">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="9">
@@ -1983,13 +3049,22 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>2426716337</v>
+        <v>6459040668.054043</v>
       </c>
       <c r="C13">
-        <v>564455569</v>
+        <v>8219234986.054043</v>
+      </c>
+      <c r="D13">
+        <v>5575011706.561949</v>
       </c>
       <c r="E13">
-        <v>1753262265</v>
+        <v>2995840305.261649</v>
+      </c>
+      <c r="G13">
+        <v>696834120.3452888</v>
+      </c>
+      <c r="J13">
+        <v>2164444883.4405856</v>
       </c>
     </row>
     <row r="14"/>
@@ -1998,13 +3073,22 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-121275655</v>
+        <v>-221284529.59233552</v>
       </c>
       <c r="C15">
-        <v>-78170903</v>
+        <v>-191338425.59233552</v>
+      </c>
+      <c r="D15">
+        <v>-171451856.38451022</v>
       </c>
       <c r="E15">
-        <v>-5198123</v>
+        <v>-149717743.99687758</v>
+      </c>
+      <c r="G15">
+        <v>-96503877.9629696</v>
+      </c>
+      <c r="J15">
+        <v>-6417209.196505936</v>
       </c>
     </row>
     <row r="16">
@@ -2022,16 +3106,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>76620</v>
+        <v>165889.3030419452</v>
       </c>
       <c r="C18">
-        <v>38648</v>
+        <v>129855.30304194521</v>
+      </c>
+      <c r="D18">
+        <v>147520.75620780856</v>
+      </c>
+      <c r="E18">
+        <v>94589.25243521265</v>
+      </c>
+      <c r="G18">
+        <v>47712.098888120505</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>-459681.45912910835</v>
+      </c>
+      <c r="C19">
+        <v>-184756.45912910835</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -2043,13 +3142,22 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>2305858279</v>
+        <v>6237462346.30562</v>
       </c>
       <c r="C21">
-        <v>486323314</v>
+        <v>8027841659.30562</v>
+      </c>
+      <c r="D21">
+        <v>5403528981.978199</v>
       </c>
       <c r="E21">
-        <v>1748064142</v>
+        <v>2846638094.9119816</v>
+      </c>
+      <c r="G21">
+        <v>600377954.4812074</v>
+      </c>
+      <c r="J21">
+        <v>2158027674.24408</v>
       </c>
     </row>
     <row r="22"/>
@@ -2108,13 +3216,22 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>2305858279</v>
+        <v>6237462346.30562</v>
       </c>
       <c r="C33">
-        <v>486323314</v>
+        <v>8027841659.30562</v>
+      </c>
+      <c r="D33">
+        <v>5403528981.978199</v>
       </c>
       <c r="E33">
-        <v>1748064142</v>
+        <v>2846638094.9119816</v>
+      </c>
+      <c r="G33">
+        <v>600377954.4812074</v>
+      </c>
+      <c r="J33">
+        <v>2158027674.24408</v>
       </c>
     </row>
     <row r="34"/>
@@ -2123,10 +3240,19 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>168296959</v>
+        <v>620337499.2086446</v>
       </c>
       <c r="C35">
-        <v>103261351</v>
+        <v>351175889.2086446</v>
+      </c>
+      <c r="D35">
+        <v>224954261.8515184</v>
+      </c>
+      <c r="E35">
+        <v>207766686.75188768</v>
+      </c>
+      <c r="G35">
+        <v>127478647.8300051</v>
       </c>
     </row>
     <row r="36">
@@ -2134,13 +3260,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-275140595</v>
+        <v>-405941610.4353064</v>
       </c>
       <c r="C36">
-        <v>-254842828</v>
+        <v>-378524735.4353064</v>
+      </c>
+      <c r="D36">
+        <v>-548753331.151721</v>
       </c>
       <c r="E36">
-        <v>-29963</v>
+        <v>-339667752.4879875</v>
+      </c>
+      <c r="G36">
+        <v>-314609666.96748596</v>
+      </c>
+      <c r="J36">
+        <v>-36990.051823496164</v>
       </c>
     </row>
     <row r="37">
@@ -2148,13 +3283,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>181976145</v>
+        <v>360380573.7713632</v>
       </c>
       <c r="C37">
-        <v>629602831</v>
+        <v>382909133.7713632</v>
+      </c>
+      <c r="D37">
+        <v>284531521.325246</v>
       </c>
       <c r="E37">
-        <v>-601408</v>
+        <v>224653974.37473056</v>
+      </c>
+      <c r="G37">
+        <v>777260000.358579</v>
+      </c>
+      <c r="J37">
+        <v>-742452.794682281</v>
       </c>
     </row>
     <row r="38">
@@ -2162,13 +3306,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>2380990788</v>
+        <v>6812238808.850322</v>
       </c>
       <c r="C38">
-        <v>964344668</v>
+        <v>8383401946.850322</v>
+      </c>
+      <c r="D38">
+        <v>5364261434.0032425</v>
       </c>
       <c r="E38">
-        <v>1747432771</v>
+        <v>2939391003.5506115</v>
+      </c>
+      <c r="G38">
+        <v>1190506935.7023053</v>
+      </c>
+      <c r="J38">
+        <v>2157248231.397574</v>
       </c>
     </row>
     <row r="39"/>
@@ -2177,37 +3330,73 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-1075377266</v>
+        <v>-3591601588.897002</v>
       </c>
       <c r="C40">
-        <v>-707219631</v>
+        <v>-3358852427.897002</v>
+      </c>
+      <c r="D40">
+        <v>-1647754582.6416316</v>
       </c>
       <c r="E40">
-        <v>-349945241</v>
+        <v>-1327579374.5335789</v>
+      </c>
+      <c r="G40">
+        <v>-873079826.2689741</v>
+      </c>
+      <c r="J40">
+        <v>-432015906.28361166</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>-32323518.85184711</v>
+      </c>
+      <c r="C41">
+        <v>-2057094.8518471087</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>-3559278070.0451555</v>
+      </c>
+      <c r="C42">
+        <v>-3356795333.0451555</v>
+      </c>
+      <c r="D42">
+        <v>-1648743635.161936</v>
+      </c>
+      <c r="G42">
+        <v>-873079826.2689741</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>1305613522</v>
+        <v>3220637219.9533195</v>
       </c>
       <c r="C43">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
+      </c>
+      <c r="D43">
+        <v>3716506851.3616104</v>
       </c>
       <c r="E43">
-        <v>1397487530</v>
+        <v>1611811629.017033</v>
+      </c>
+      <c r="G43">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="J43">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="44">
@@ -2221,32 +3410,62 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>1305613522</v>
+        <v>3220637219.9533195</v>
       </c>
       <c r="C46">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
+      </c>
+      <c r="D46">
+        <v>3716506851.3616104</v>
       </c>
       <c r="E46">
-        <v>1397487530</v>
+        <v>1611811629.017033</v>
+      </c>
+      <c r="G46">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="J46">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>1305613522</v>
+        <v>3220637219.9533195</v>
       </c>
       <c r="C48">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
+      </c>
+      <c r="D48">
+        <v>3716506851.3616104</v>
       </c>
       <c r="E48">
-        <v>1397487530</v>
+        <v>1611811629.017033</v>
+      </c>
+      <c r="G48">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="J48">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="49"/>
@@ -2255,28 +3474,42 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>4372303</v>
+        <v>6261560.939215167</v>
       </c>
       <c r="C50">
-        <v>3446848</v>
+        <v>5753800.939215167</v>
+      </c>
+      <c r="D50">
+        <v>5500420.593555903</v>
+      </c>
+      <c r="E50">
+        <v>5397714.3329448905</v>
+      </c>
+      <c r="G50">
+        <v>4255217.591726501</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:J129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2284,15 +3517,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2306,16 +3554,31 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>60280847</v>
+        <v>-647223053</v>
       </c>
       <c r="C3">
-        <v>93461204</v>
+        <v>-756993173.2789545</v>
       </c>
       <c r="D3">
-        <v>24562703</v>
+        <v>165475116.17419118</v>
       </c>
       <c r="E3">
-        <v>-12726319</v>
+        <v>74418170.89391062</v>
+      </c>
+      <c r="F3">
+        <v>26741870</v>
+      </c>
+      <c r="G3">
+        <v>105488105.35862738</v>
+      </c>
+      <c r="H3">
+        <v>-91964140.11664815</v>
+      </c>
+      <c r="I3">
+        <v>30323253.909660075</v>
+      </c>
+      <c r="J3">
+        <v>-15710950.149595967</v>
       </c>
     </row>
     <row r="4">
@@ -2323,35 +3586,83 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>1413859721</v>
+        <v>-504124534</v>
       </c>
       <c r="C4">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
       </c>
       <c r="D4">
-        <v>365371236</v>
+        <v>3917840956.5457025</v>
       </c>
       <c r="E4">
-        <v>1397487530</v>
+        <v>1745444192.8693335</v>
+      </c>
+      <c r="F4">
+        <v>1299787765</v>
+      </c>
+      <c r="G4">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="H4">
+        <v>518761214.6174233</v>
+      </c>
+      <c r="I4">
+        <v>451059672.07739043</v>
+      </c>
+      <c r="J4">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>374639972</v>
+      </c>
+      <c r="C5">
+        <v>-3899506839.074337</v>
+      </c>
+      <c r="D5">
+        <v>-3817105708.7927785</v>
+      </c>
+      <c r="F5">
+        <v>-1250997908</v>
+      </c>
+      <c r="G5">
+        <v>-449695554.38085645</v>
+      </c>
+      <c r="H5">
+        <v>-623996829.7335783</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>2221210</v>
+        <v>1731018</v>
       </c>
       <c r="C6">
-        <v>3446848</v>
+        <v>5753800.939215167</v>
       </c>
       <c r="D6">
-        <v>1295755</v>
+        <v>4154904.1241498925</v>
+      </c>
+      <c r="E6">
+        <v>2742137.7369044465</v>
+      </c>
+      <c r="F6">
+        <v>1223258</v>
+      </c>
+      <c r="G6">
+        <v>4255217.591726501</v>
+      </c>
+      <c r="H6">
+        <v>2909701.1223204895</v>
+      </c>
+      <c r="I6">
+        <v>1599641.043972709</v>
       </c>
     </row>
     <row r="7">
@@ -2364,16 +3675,31 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>822541</v>
+        <v>1044274</v>
       </c>
       <c r="C8">
-        <v>1473728</v>
+        <v>1661311.558185135</v>
       </c>
       <c r="D8">
-        <v>1790040</v>
+        <v>1541678.86804545</v>
       </c>
       <c r="E8">
-        <v>7479</v>
+        <v>1015446.8583569857</v>
+      </c>
+      <c r="F8">
+        <v>1351728</v>
+      </c>
+      <c r="G8">
+        <v>1819353.0714056012</v>
+      </c>
+      <c r="H8">
+        <v>2296986.3226103433</v>
+      </c>
+      <c r="I8">
+        <v>2209847.8912702696</v>
+      </c>
+      <c r="J8">
+        <v>9233.007295261752</v>
       </c>
     </row>
     <row r="9">
@@ -2396,13 +3722,28 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>49488977</v>
+        <v>-219851343</v>
       </c>
       <c r="C12">
-        <v>144105756</v>
+        <v>18207786.68160746</v>
       </c>
       <c r="D12">
-        <v>99742479</v>
+        <v>125996060.43675198</v>
+      </c>
+      <c r="E12">
+        <v>61095345.05629642</v>
+      </c>
+      <c r="F12">
+        <v>20272819</v>
+      </c>
+      <c r="G12">
+        <v>179801257.57448626</v>
+      </c>
+      <c r="H12">
+        <v>-7362005.532742143</v>
+      </c>
+      <c r="I12">
+        <v>123134514.80873007</v>
       </c>
     </row>
     <row r="13">
@@ -2434,14 +3775,26 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
-        <v>-1818087675</v>
-      </c>
       <c r="C18">
-        <v>-506776103</v>
+        <v>-8011405785.400775</v>
+      </c>
+      <c r="D18">
+        <v>-5047061527.184122</v>
       </c>
       <c r="E18">
-        <v>-1741423369</v>
+        <v>-2244473427.8246393</v>
+      </c>
+      <c r="F18">
+        <v>-1793498952</v>
+      </c>
+      <c r="G18">
+        <v>-625627417.7373779</v>
+      </c>
+      <c r="H18">
+        <v>-264098025.0559809</v>
+      </c>
+      <c r="J18">
+        <v>-2149829478.5554614</v>
       </c>
     </row>
     <row r="19">
@@ -2454,33 +3807,45 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>541767597</v>
+        <v>854301392</v>
       </c>
       <c r="C20">
-        <v>707219631</v>
+        <v>3358852427.897002</v>
       </c>
       <c r="D20">
-        <v>173609962</v>
+        <v>1336135853.1901567</v>
       </c>
       <c r="E20">
-        <v>349945241</v>
+        <v>668825267.4739174</v>
+      </c>
+      <c r="F20">
+        <v>621552231</v>
+      </c>
+      <c r="G20">
+        <v>873079826.2689741</v>
+      </c>
+      <c r="H20">
+        <v>561461094.5208035</v>
+      </c>
+      <c r="I20">
+        <v>214325718.10083106</v>
+      </c>
+      <c r="J20">
+        <v>432015906.28361166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>-135773820</v>
-      </c>
-      <c r="C21">
-        <v>-705723299</v>
-      </c>
-      <c r="D21">
-        <v>-729679983</v>
-      </c>
       <c r="E21">
-        <v>-133745260</v>
+        <v>-167616081.10249442</v>
+      </c>
+      <c r="I21">
+        <v>-900807675.657905</v>
+      </c>
+      <c r="J21">
+        <v>-165111774.47341618</v>
       </c>
     </row>
     <row r="22">
@@ -2518,16 +3883,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>54298551</v>
+        <v>-511794505</v>
       </c>
       <c r="C28">
-        <v>-99128402</v>
+        <v>-1879657549.5137782</v>
       </c>
       <c r="D28">
-        <v>-87870511</v>
+        <v>65075066.57851284</v>
       </c>
       <c r="E28">
-        <v>-127728379</v>
+        <v>67032881.06767513</v>
+      </c>
+      <c r="F28">
+        <v>-22047987</v>
+      </c>
+      <c r="G28">
+        <v>239808869.3263382</v>
+      </c>
+      <c r="H28">
+        <v>16312845.69150219</v>
+      </c>
+      <c r="I28">
+        <v>-108478281.73571038</v>
+      </c>
+      <c r="J28">
+        <v>-157683788.62400827</v>
       </c>
     </row>
     <row r="29">
@@ -2555,16 +3935,31 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-13700843</v>
+        <v>-152962568</v>
       </c>
       <c r="C33">
-        <v>-575865156</v>
+        <v>-2358459809.4081626</v>
       </c>
       <c r="D33">
-        <v>-478296316</v>
+        <v>-218292538.17603838</v>
       </c>
       <c r="E33">
-        <v>-11838896</v>
+        <v>-16914023.715768937</v>
+      </c>
+      <c r="F33">
+        <v>195268902</v>
+      </c>
+      <c r="G33">
+        <v>-710919532.3840551</v>
+      </c>
+      <c r="H33">
+        <v>-577646559.7220199</v>
+      </c>
+      <c r="I33">
+        <v>-590468428.2557588</v>
+      </c>
+      <c r="J33">
+        <v>-14615404.88512437</v>
       </c>
     </row>
     <row r="34">
@@ -2597,16 +3992,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-10960430</v>
+        <v>-23859736</v>
       </c>
       <c r="C39">
-        <v>-726422</v>
+        <v>891071.1500311622</v>
       </c>
       <c r="D39">
-        <v>-35348</v>
+        <v>-6029849.628280896</v>
       </c>
       <c r="E39">
-        <v>-4619</v>
+        <v>-13530917.254874418</v>
+      </c>
+      <c r="F39">
+        <v>-20533305</v>
+      </c>
+      <c r="G39">
+        <v>-896785.6416942005</v>
+      </c>
+      <c r="H39">
+        <v>-31578.41877275616</v>
+      </c>
+      <c r="I39">
+        <v>-43637.96521900152</v>
+      </c>
+      <c r="J39">
+        <v>-5702.267776014711</v>
       </c>
     </row>
     <row r="40">
@@ -2624,16 +4034,31 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>921384</v>
+        <v>3401216</v>
       </c>
       <c r="C42">
-        <v>1051101</v>
+        <v>1052482.155543603</v>
       </c>
       <c r="D42">
-        <v>2086253</v>
+        <v>3238260.6803832245</v>
       </c>
       <c r="E42">
-        <v>108466</v>
+        <v>1137470.9444761937</v>
+      </c>
+      <c r="F42">
+        <v>1462717</v>
+      </c>
+      <c r="G42">
+        <v>1297609.9687296343</v>
+      </c>
+      <c r="H42">
+        <v>1995633.4228829716</v>
+      </c>
+      <c r="I42">
+        <v>2575530.039946746</v>
+      </c>
+      <c r="J42">
+        <v>133903.9135295977</v>
       </c>
     </row>
     <row r="43">
@@ -2646,16 +4071,31 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>58046025</v>
+        <v>-352018284</v>
       </c>
       <c r="C44">
-        <v>777703033</v>
+        <v>501351156.5097684</v>
       </c>
       <c r="D44">
-        <v>596070601</v>
+        <v>314565262.3706203</v>
       </c>
       <c r="E44">
-        <v>126782800</v>
+        <v>71659228.81213345</v>
+      </c>
+      <c r="F44">
+        <v>-162668502</v>
+      </c>
+      <c r="G44">
+        <v>960093298.102969</v>
+      </c>
+      <c r="H44">
+        <v>599552898.918461</v>
+      </c>
+      <c r="I44">
+        <v>735863645.8783336</v>
+      </c>
+      <c r="J44">
+        <v>156516448.36391386</v>
       </c>
     </row>
     <row r="45">
@@ -2678,22 +4118,55 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-28031944</v>
+        <v>13644867</v>
       </c>
       <c r="C48">
-        <v>-7910513</v>
+        <v>-24492449.920958944</v>
       </c>
       <c r="D48">
-        <v>-5729539</v>
+        <v>-28406068.668171372</v>
       </c>
       <c r="E48">
-        <v>-45691</v>
+        <v>-34606116.25248949</v>
+      </c>
+      <c r="F48">
+        <v>-35577799</v>
+      </c>
+      <c r="G48">
+        <v>-9765720.719611142</v>
+      </c>
+      <c r="H48">
+        <v>-7557548.509049008</v>
+      </c>
+      <c r="I48">
+        <v>-7073255.165862645</v>
+      </c>
+      <c r="J48">
+        <v>-56406.65013074003</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-641279067</v>
+      </c>
+      <c r="C49">
+        <v>-754614869.6347958</v>
+      </c>
+      <c r="D49">
+        <v>165810314.33143663</v>
+      </c>
+      <c r="F49">
+        <v>26741870</v>
+      </c>
+      <c r="G49">
+        <v>107540424.3788131</v>
+      </c>
+      <c r="H49">
+        <v>-88922769.42465298</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2719,11 +4192,23 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
+      <c r="B54">
+        <v>-5943986</v>
+      </c>
       <c r="C54">
-        <v>-1662437</v>
+        <v>-2057094.8518471087</v>
       </c>
       <c r="D54">
-        <v>-1662437</v>
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>-2052319.020185721</v>
+      </c>
+      <c r="H54">
+        <v>-3041370.691995177</v>
+      </c>
+      <c r="I54">
+        <v>-2052318.8860694023</v>
       </c>
     </row>
     <row r="55">
@@ -2765,8 +4250,17 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
-        <v>-291896</v>
+      <c r="C62">
+        <v>-321208.7923116108</v>
+      </c>
+      <c r="D62">
+        <v>-335198.1572454428</v>
+      </c>
+      <c r="E62">
+        <v>-360352.7072413055</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2776,434 +4270,599 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="C64">
-        <v>-1662437</v>
-      </c>
-      <c r="D64">
-        <v>-1662437</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-804217403</v>
+      </c>
+      <c r="C67">
+        <v>-1921578.9778221732</v>
+      </c>
+      <c r="D67">
+        <v>-5531187.593183694</v>
+      </c>
+      <c r="E67">
+        <v>-2059155.6816839443</v>
+      </c>
+      <c r="F67">
+        <v>-1597561</v>
+      </c>
+      <c r="G67">
+        <v>-7280105.018358676</v>
+      </c>
+      <c r="H67">
+        <v>-26949181.51201882</v>
+      </c>
+      <c r="I67">
+        <v>-27313025.63963003</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-1667975</v>
-      </c>
-      <c r="C68">
-        <v>-22296337</v>
-      </c>
-      <c r="D68">
-        <v>-22124332</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B71">
+        <v>-800000000</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-4217403</v>
+      </c>
+      <c r="C78">
+        <v>-10289126.55999226</v>
+      </c>
+      <c r="D78">
+        <v>-5531187.593183694</v>
+      </c>
+      <c r="E78">
+        <v>-2059155.6816839443</v>
+      </c>
+      <c r="F78">
+        <v>-1597561</v>
+      </c>
+      <c r="G78">
+        <v>-27525369.328074176</v>
+      </c>
+      <c r="H78">
+        <v>-26949181.51201882</v>
+      </c>
+      <c r="I78">
+        <v>-27313025.63963003</v>
+      </c>
+      <c r="J78">
+        <v>14615404.88512437</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-1667975</v>
-      </c>
-      <c r="C79">
-        <v>-5897093</v>
-      </c>
-      <c r="D79">
-        <v>-22124332</v>
-      </c>
-      <c r="E79">
-        <v>11838896</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+      <c r="C92">
+        <v>8367547.582170086</v>
+      </c>
+      <c r="G92">
+        <v>20245264.3097155</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="J98">
+        <v>14615404.88512437</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C99">
-        <v>16399244</v>
-      </c>
-      <c r="E99">
-        <v>11838896</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>201372616</v>
+      </c>
+      <c r="C101">
+        <v>2110192120.1942418</v>
+      </c>
+      <c r="D101">
+        <v>-181045660.5993906</v>
+      </c>
+      <c r="E101">
+        <v>-98008985.99778429</v>
+      </c>
+      <c r="F101">
+        <v>-40024019</v>
+      </c>
+      <c r="G101">
+        <v>-85019226.48664293</v>
+      </c>
+      <c r="H101">
+        <v>118472257.27895415</v>
+      </c>
+      <c r="I101">
+        <v>11238134.020631064</v>
+      </c>
+      <c r="J101">
+        <v>2079585.8244475876</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-79390082</v>
-      </c>
-      <c r="C102">
-        <v>-67329600</v>
-      </c>
-      <c r="D102">
-        <v>9103210</v>
-      </c>
-      <c r="E102">
-        <v>1684524</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C104">
+        <v>2200844083.58875</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="J107">
+        <v>2079585.8244475876</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="E108">
-        <v>1684524</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="G109">
+        <v>94782031.08784331</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-18478727</v>
+      </c>
+      <c r="C110">
+        <v>-72444176.7129006</v>
+      </c>
+      <c r="D110">
+        <v>-55049600.16263861</v>
+      </c>
+      <c r="E110">
+        <v>-36913640.94148785</v>
+      </c>
+      <c r="F110">
+        <v>-19751200</v>
+      </c>
+      <c r="H110">
+        <v>113009452.65458746</v>
+      </c>
+      <c r="I110">
+        <v>134372648.8293611</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>-29901105</v>
-      </c>
-      <c r="C111">
-        <v>76776156</v>
-      </c>
-      <c r="D111">
-        <v>108845689</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-96739663</v>
+      </c>
+      <c r="C118">
+        <v>-362609062.94185615</v>
+      </c>
+      <c r="D118">
+        <v>-261800610.3996056</v>
+      </c>
+      <c r="E118">
+        <v>-145665603.13638785</v>
+      </c>
+      <c r="F118">
+        <v>-67641965</v>
+      </c>
+      <c r="G118">
+        <v>-307195588.86680496</v>
+      </c>
+      <c r="H118">
+        <v>-33033745.324119005</v>
+      </c>
+      <c r="I118">
+        <v>-127581698.5094998</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-117993305</v>
+        <v>316591006</v>
       </c>
       <c r="C119">
-        <v>-247298808</v>
+        <v>344401276.26024866</v>
       </c>
       <c r="D119">
-        <v>-103344825</v>
+        <v>135804549.96285364</v>
+      </c>
+      <c r="E119">
+        <v>84570258.08009143</v>
+      </c>
+      <c r="F119">
+        <v>47369146</v>
+      </c>
+      <c r="G119">
+        <v>127394331.29231873</v>
+      </c>
+      <c r="H119">
+        <v>38496549.948485695</v>
+      </c>
+      <c r="I119">
+        <v>4447183.700769754</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>68504328</v>
-      </c>
-      <c r="C120">
-        <v>103193052</v>
-      </c>
-      <c r="D120">
-        <v>3602346</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-1250067840</v>
+      </c>
+      <c r="C125">
+        <v>1351277367.937465</v>
+      </c>
+      <c r="D125">
+        <v>-21101732.018383116</v>
+      </c>
+      <c r="F125">
+        <v>-14879710</v>
+      </c>
+      <c r="G125">
+        <v>13188773.853625774</v>
+      </c>
+      <c r="H125">
+        <v>-441064.3497128195</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-1250067840</v>
+      </c>
+      <c r="C127">
+        <v>1351277367.937465</v>
+      </c>
+      <c r="D127">
+        <v>-21101732.018383116</v>
+      </c>
+      <c r="E127">
+        <v>-25649970.785557617</v>
+      </c>
+      <c r="F127">
+        <v>-14879710</v>
+      </c>
+      <c r="G127">
+        <v>13188773.853625774</v>
+      </c>
+      <c r="H127">
+        <v>-441064.3497128195</v>
+      </c>
+      <c r="I127">
+        <v>14248362.290661106</v>
+      </c>
+      <c r="J127">
+        <v>984040.5599759909</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>-20777210</v>
+        <v>1377215924</v>
       </c>
       <c r="C128">
-        <v>20234511</v>
+        <v>19836178.01399027</v>
       </c>
       <c r="D128">
-        <v>11541581</v>
-      </c>
-      <c r="E128">
-        <v>797101</v>
+        <v>25964035.67125403</v>
+      </c>
+      <c r="F128">
+        <v>25963556</v>
+      </c>
+      <c r="G128">
+        <v>751792.9330453317</v>
+      </c>
+      <c r="H128">
+        <v>984041.13008951</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>1490769</v>
+      </c>
+      <c r="C129">
+        <v>1377241403.4515393</v>
+      </c>
+      <c r="D129">
+        <v>4862303.652870915</v>
+      </c>
+      <c r="F129">
+        <v>4960175</v>
+      </c>
+      <c r="G129">
+        <v>19836178.01399027</v>
+      </c>
+      <c r="H129">
+        <v>542976.7803766906</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:J129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3211,15 +4870,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3232,21 +4906,96 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
+      <c r="B3">
+        <v>-647223053</v>
+      </c>
+      <c r="C3">
+        <v>-922468289.4531457</v>
+      </c>
+      <c r="D3">
+        <v>91056945.28028056</v>
+      </c>
+      <c r="E3">
+        <v>47676300.89391062</v>
+      </c>
+      <c r="F3">
+        <v>26741870</v>
+      </c>
+      <c r="G3">
+        <v>197452245.47527552</v>
+      </c>
+      <c r="H3">
+        <v>-122287394.02630822</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B4">
+        <v>-504124534</v>
+      </c>
+      <c r="C4">
+        <v>1106708562.407617</v>
+      </c>
+      <c r="D4">
+        <v>2172396763.6763687</v>
+      </c>
+      <c r="E4">
+        <v>445656427.8693335</v>
+      </c>
+      <c r="F4">
+        <v>1299787765</v>
+      </c>
+      <c r="G4">
+        <v>-201334105.18409193</v>
+      </c>
+      <c r="H4">
+        <v>67701542.54003286</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>374639972</v>
+      </c>
+      <c r="C5">
+        <v>-82401130.28155851</v>
+      </c>
+      <c r="F5">
+        <v>-1250997908</v>
+      </c>
+      <c r="G5">
+        <v>174301275.35272187</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B6">
+        <v>1731018</v>
+      </c>
+      <c r="C6">
+        <v>1598896.815065275</v>
+      </c>
+      <c r="D6">
+        <v>1412766.387245446</v>
+      </c>
+      <c r="E6">
+        <v>1518879.7369044465</v>
+      </c>
+      <c r="F6">
+        <v>1223258</v>
+      </c>
+      <c r="G6">
+        <v>1345516.469406011</v>
+      </c>
+      <c r="H6">
+        <v>1310060.0783477805</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3257,6 +5006,27 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B8">
+        <v>1044274</v>
+      </c>
+      <c r="C8">
+        <v>119632.69013968506</v>
+      </c>
+      <c r="D8">
+        <v>526232.0096884642</v>
+      </c>
+      <c r="E8">
+        <v>-336281.14164301427</v>
+      </c>
+      <c r="F8">
+        <v>1351728</v>
+      </c>
+      <c r="G8">
+        <v>-477633.2512047421</v>
+      </c>
+      <c r="H8">
+        <v>87138.4313400737</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3277,6 +5047,27 @@
       <c r="A12" t="str">
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B12">
+        <v>-219851343</v>
+      </c>
+      <c r="C12">
+        <v>-107788273.75514452</v>
+      </c>
+      <c r="D12">
+        <v>64900715.38045555</v>
+      </c>
+      <c r="E12">
+        <v>40822526.05629642</v>
+      </c>
+      <c r="F12">
+        <v>20272819</v>
+      </c>
+      <c r="G12">
+        <v>187163263.1072284</v>
+      </c>
+      <c r="H12">
+        <v>-130496520.34147221</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3307,6 +5098,21 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="C18">
+        <v>-2964344258.216653</v>
+      </c>
+      <c r="D18">
+        <v>-2802588099.359483</v>
+      </c>
+      <c r="E18">
+        <v>-450974475.8246393</v>
+      </c>
+      <c r="F18">
+        <v>-1793498952</v>
+      </c>
+      <c r="G18">
+        <v>-361529392.68139696</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3317,6 +5123,27 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>854301392</v>
+      </c>
+      <c r="C20">
+        <v>2022716574.7068455</v>
+      </c>
+      <c r="D20">
+        <v>667310585.7162393</v>
+      </c>
+      <c r="E20">
+        <v>47273036.473917365</v>
+      </c>
+      <c r="F20">
+        <v>621552231</v>
+      </c>
+      <c r="G20">
+        <v>311618731.7481706</v>
+      </c>
+      <c r="H20">
+        <v>347135376.4199724</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3357,6 +5184,27 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>-511794505</v>
+      </c>
+      <c r="C28">
+        <v>-1944732616.092291</v>
+      </c>
+      <c r="D28">
+        <v>-1957814.4891622886</v>
+      </c>
+      <c r="E28">
+        <v>89080868.06767513</v>
+      </c>
+      <c r="F28">
+        <v>-22047987</v>
+      </c>
+      <c r="G28">
+        <v>223496023.63483602</v>
+      </c>
+      <c r="H28">
+        <v>124791127.42721257</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3382,6 +5230,27 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>-152962568</v>
+      </c>
+      <c r="C33">
+        <v>-2140167271.2321243</v>
+      </c>
+      <c r="D33">
+        <v>-201378514.46026945</v>
+      </c>
+      <c r="E33">
+        <v>-212182925.71576893</v>
+      </c>
+      <c r="F33">
+        <v>195268902</v>
+      </c>
+      <c r="G33">
+        <v>-133272972.66203523</v>
+      </c>
+      <c r="H33">
+        <v>12821868.533738852</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -3412,6 +5281,27 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
+      <c r="B39">
+        <v>-23859736</v>
+      </c>
+      <c r="C39">
+        <v>6920920.778312058</v>
+      </c>
+      <c r="D39">
+        <v>7501067.626593522</v>
+      </c>
+      <c r="E39">
+        <v>7002387.745125582</v>
+      </c>
+      <c r="F39">
+        <v>-20533305</v>
+      </c>
+      <c r="G39">
+        <v>-865207.2229214443</v>
+      </c>
+      <c r="H39">
+        <v>12059.54644624536</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -3427,6 +5317,27 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B42">
+        <v>3401216</v>
+      </c>
+      <c r="C42">
+        <v>-2185778.5248396215</v>
+      </c>
+      <c r="D42">
+        <v>2100789.7359070308</v>
+      </c>
+      <c r="E42">
+        <v>-325246.05552380625</v>
+      </c>
+      <c r="F42">
+        <v>1462717</v>
+      </c>
+      <c r="G42">
+        <v>-698023.4541533373</v>
+      </c>
+      <c r="H42">
+        <v>-579896.6170637745</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -3437,6 +5348,27 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>-352018284</v>
+      </c>
+      <c r="C44">
+        <v>186785894.13914812</v>
+      </c>
+      <c r="D44">
+        <v>242906033.55848688</v>
+      </c>
+      <c r="E44">
+        <v>234327730.81213343</v>
+      </c>
+      <c r="F44">
+        <v>-162668502</v>
+      </c>
+      <c r="G44">
+        <v>360540399.1845081</v>
+      </c>
+      <c r="H44">
+        <v>-136310746.9598726</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -3457,11 +5389,44 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B48">
+        <v>13644867</v>
+      </c>
+      <c r="C48">
+        <v>3913618.7472124286</v>
+      </c>
+      <c r="D48">
+        <v>6200047.58431812</v>
+      </c>
+      <c r="E48">
+        <v>971682.7475105077</v>
+      </c>
+      <c r="F48">
+        <v>-35577799</v>
+      </c>
+      <c r="G48">
+        <v>-2208172.210562134</v>
+      </c>
+      <c r="H48">
+        <v>-484293.34318636265</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-641279067</v>
+      </c>
+      <c r="C49">
+        <v>-920425183.9662324</v>
+      </c>
+      <c r="F49">
+        <v>26741870</v>
+      </c>
+      <c r="G49">
+        <v>196463193.80346608</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3487,6 +5452,18 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
+      <c r="B54">
+        <v>-5943986</v>
+      </c>
+      <c r="C54">
+        <v>-2057094.8518471087</v>
+      </c>
+      <c r="G54">
+        <v>989051.6718094558</v>
+      </c>
+      <c r="H54">
+        <v>-989051.8059257746</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3527,6 +5504,12 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
+      <c r="C62">
+        <v>13989.364933831966</v>
+      </c>
+      <c r="D62">
+        <v>25154.549995862704</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3535,347 +5518,533 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-804217403</v>
+      </c>
+      <c r="C67">
+        <v>3609608.615361521</v>
+      </c>
+      <c r="D67">
+        <v>-3472031.91149975</v>
+      </c>
+      <c r="E67">
+        <v>-461594.6816839443</v>
+      </c>
+      <c r="F67">
+        <v>-1597561</v>
+      </c>
+      <c r="G67">
+        <v>19669076.493660145</v>
+      </c>
+      <c r="H67">
+        <v>363844.12761121243</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B71">
+        <v>-800000000</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-4217403</v>
+      </c>
+      <c r="C78">
+        <v>-4757938.966808565</v>
+      </c>
+      <c r="D78">
+        <v>-3472031.91149975</v>
+      </c>
+      <c r="E78">
+        <v>-461594.6816839443</v>
+      </c>
+      <c r="F78">
+        <v>-1597561</v>
+      </c>
+      <c r="G78">
+        <v>-576187.8160553575</v>
+      </c>
+      <c r="H78">
+        <v>363844.12761121243</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>201372616</v>
+      </c>
+      <c r="C101">
+        <v>2291237780.7936325</v>
+      </c>
+      <c r="D101">
+        <v>-83036674.60160631</v>
+      </c>
+      <c r="E101">
+        <v>-57984966.99778429</v>
+      </c>
+      <c r="F101">
+        <v>-40024019</v>
+      </c>
+      <c r="G101">
+        <v>-203491483.76559708</v>
+      </c>
+      <c r="H101">
+        <v>107234123.25832309</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-18478727</v>
+      </c>
+      <c r="C110">
+        <v>-17394576.55026198</v>
+      </c>
+      <c r="D110">
+        <v>-18135959.221150763</v>
+      </c>
+      <c r="E110">
+        <v>-17162440.94148785</v>
+      </c>
+      <c r="F110">
+        <v>-19751200</v>
+      </c>
+      <c r="H110">
+        <v>-21363196.17477365</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-96739663</v>
+      </c>
+      <c r="C118">
+        <v>-100808452.54225054</v>
+      </c>
+      <c r="D118">
+        <v>-116135007.26321775</v>
+      </c>
+      <c r="E118">
+        <v>-78023638.13638785</v>
+      </c>
+      <c r="F118">
+        <v>-67641965</v>
+      </c>
+      <c r="G118">
+        <v>-274161843.5426859</v>
+      </c>
+      <c r="H118">
+        <v>94547953.1853808</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B119">
+        <v>316591006</v>
+      </c>
+      <c r="C119">
+        <v>208596726.29739502</v>
+      </c>
+      <c r="D119">
+        <v>51234291.88276221</v>
+      </c>
+      <c r="E119">
+        <v>37201112.08009143</v>
+      </c>
+      <c r="F119">
+        <v>47369146</v>
+      </c>
+      <c r="G119">
+        <v>88897781.34383303</v>
+      </c>
+      <c r="H119">
+        <v>34049366.24771594</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-1250067840</v>
+      </c>
+      <c r="C125">
+        <v>1372379099.955848</v>
+      </c>
+      <c r="F125">
+        <v>-14879710</v>
+      </c>
+      <c r="G125">
+        <v>13629838.203338593</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-1250067840</v>
+      </c>
+      <c r="C127">
+        <v>1372379099.955848</v>
+      </c>
+      <c r="D127">
+        <v>4548238.767174501</v>
+      </c>
+      <c r="E127">
+        <v>-10770260.785557617</v>
+      </c>
+      <c r="F127">
+        <v>-14879710</v>
+      </c>
+      <c r="G127">
+        <v>13629838.203338593</v>
+      </c>
+      <c r="H127">
+        <v>-14689426.640373925</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B128">
+        <v>1377215924</v>
+      </c>
+      <c r="C128">
+        <v>-6127857.6572637595</v>
+      </c>
+      <c r="F128">
+        <v>25963556</v>
+      </c>
+      <c r="G128">
+        <v>-232248.19704417826</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>1490769</v>
+      </c>
+      <c r="C129">
+        <v>1372379099.7986684</v>
+      </c>
+      <c r="F129">
+        <v>4960175</v>
+      </c>
+      <c r="G129">
+        <v>19293201.23361358</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:J129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3883,15 +6052,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="I1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3905,13 +6089,22 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>129179348</v>
+        <v>-1430958096.2789545</v>
       </c>
       <c r="C3">
-        <v>93461204</v>
+        <v>-756993173.2789545</v>
+      </c>
+      <c r="D3">
+        <v>362927361.6494667</v>
       </c>
       <c r="E3">
-        <v>-12726319</v>
+        <v>159475045.1238343</v>
+      </c>
+      <c r="G3">
+        <v>105488105.35862738</v>
+      </c>
+      <c r="J3">
+        <v>-15710950.149595967</v>
       </c>
     </row>
     <row r="4">
@@ -3919,29 +6112,59 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>1305613522</v>
+        <v>3220637219.9533195</v>
       </c>
       <c r="C4">
-        <v>257125037</v>
+        <v>5024549518.95332</v>
+      </c>
+      <c r="D4">
+        <v>3716506851.3616104</v>
       </c>
       <c r="E4">
-        <v>1397487530</v>
+        <v>1611811629.017033</v>
+      </c>
+      <c r="G4">
+        <v>317427109.4333314</v>
+      </c>
+      <c r="J4">
+        <v>1725232325.1139624</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>-2273868959.074337</v>
+      </c>
+      <c r="C5">
+        <v>-3899506839.074337</v>
+      </c>
+      <c r="D5">
+        <v>-3642804433.440057</v>
+      </c>
+      <c r="G5">
+        <v>-449695554.38085645</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>4372303</v>
+        <v>6261560.939215167</v>
       </c>
       <c r="C6">
-        <v>3446848</v>
+        <v>5753800.939215167</v>
+      </c>
+      <c r="D6">
+        <v>5500420.593555903</v>
+      </c>
+      <c r="E6">
+        <v>5397714.3329448905</v>
+      </c>
+      <c r="G6">
+        <v>4255217.591726501</v>
       </c>
     </row>
     <row r="7">
@@ -3954,13 +6177,22 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>506229</v>
+        <v>1353857.558185135</v>
       </c>
       <c r="C8">
-        <v>1473728</v>
+        <v>1661311.558185135</v>
+      </c>
+      <c r="D8">
+        <v>1064045.6168407078</v>
       </c>
       <c r="E8">
-        <v>7479</v>
+        <v>624952.0056254927</v>
+      </c>
+      <c r="G8">
+        <v>1819353.0714056012</v>
+      </c>
+      <c r="J8">
+        <v>9233.007295261752</v>
       </c>
     </row>
     <row r="9">
@@ -3983,10 +6215,19 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>93852254</v>
+        <v>-221916375.31839254</v>
       </c>
       <c r="C12">
-        <v>144105756</v>
+        <v>18207786.68160746</v>
+      </c>
+      <c r="D12">
+        <v>313159323.54398036</v>
+      </c>
+      <c r="E12">
+        <v>115862888.87000383</v>
+      </c>
+      <c r="G12">
+        <v>179801257.57448626</v>
       </c>
     </row>
     <row r="13">
@@ -4019,10 +6260,16 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="C18">
-        <v>-506776103</v>
-      </c>
-      <c r="E18">
-        <v>-1741423369</v>
+        <v>-8011405785.400775</v>
+      </c>
+      <c r="D18">
+        <v>-5408590919.865519</v>
+      </c>
+      <c r="G18">
+        <v>-625627417.7373779</v>
+      </c>
+      <c r="J18">
+        <v>-2149829478.5554614</v>
       </c>
     </row>
     <row r="19">
@@ -4035,27 +6282,33 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>1075377266</v>
+        <v>3591601588.897002</v>
       </c>
       <c r="C20">
-        <v>707219631</v>
+        <v>3358852427.897002</v>
+      </c>
+      <c r="D20">
+        <v>1647754584.9383273</v>
       </c>
       <c r="E20">
-        <v>349945241</v>
+        <v>1327579374.5335789</v>
+      </c>
+      <c r="G20">
+        <v>873079826.2689741</v>
+      </c>
+      <c r="J20">
+        <v>432015906.28361166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>-111817136</v>
-      </c>
-      <c r="C21">
-        <v>-705723299</v>
-      </c>
       <c r="E21">
-        <v>-133745260</v>
+        <v>-138040972.37909812</v>
+      </c>
+      <c r="J21">
+        <v>-165111774.47341618</v>
       </c>
     </row>
     <row r="22">
@@ -4093,13 +6346,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>43040660</v>
+        <v>-2369404067.513778</v>
       </c>
       <c r="C28">
-        <v>-99128402</v>
+        <v>-1879657549.5137782</v>
+      </c>
+      <c r="D28">
+        <v>288571090.21334887</v>
       </c>
       <c r="E28">
-        <v>-127728379</v>
+        <v>53134740.97778855</v>
+      </c>
+      <c r="G28">
+        <v>239808869.3263382</v>
+      </c>
+      <c r="J28">
+        <v>-157683788.62400827</v>
       </c>
     </row>
     <row r="29">
@@ -4127,13 +6389,22 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-111269683</v>
+        <v>-2706691279.4081626</v>
       </c>
       <c r="C33">
-        <v>-575865156</v>
+        <v>-2358459809.4081626</v>
+      </c>
+      <c r="D33">
+        <v>-351565510.8380736</v>
       </c>
       <c r="E33">
-        <v>-11838896</v>
+        <v>-137365128.34342325</v>
+      </c>
+      <c r="G33">
+        <v>-710919532.3840551</v>
+      </c>
+      <c r="J33">
+        <v>-14615404.88512437</v>
       </c>
     </row>
     <row r="34">
@@ -4166,13 +6437,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-11651504</v>
+        <v>-2435359.8499688394</v>
       </c>
       <c r="C39">
-        <v>-726422</v>
+        <v>891071.1500311622</v>
+      </c>
+      <c r="D39">
+        <v>-6895056.85120234</v>
       </c>
       <c r="E39">
-        <v>-4619</v>
+        <v>-14384064.90610663</v>
+      </c>
+      <c r="G39">
+        <v>-896785.6416942005</v>
+      </c>
+      <c r="J39">
+        <v>-5702.267776014711</v>
       </c>
     </row>
     <row r="40">
@@ -4190,13 +6470,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-113768</v>
+        <v>2990981.155543603</v>
       </c>
       <c r="C42">
-        <v>1051101</v>
+        <v>1052482.155543603</v>
+      </c>
+      <c r="D42">
+        <v>2540237.2262298875</v>
       </c>
       <c r="E42">
-        <v>108466</v>
+        <v>-140449.36140758614</v>
+      </c>
+      <c r="G42">
+        <v>1297609.9687296343</v>
+      </c>
+      <c r="J42">
+        <v>133903.9135295977</v>
       </c>
     </row>
     <row r="43">
@@ -4209,13 +6498,22 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>239678457</v>
+        <v>312001374.5097685</v>
       </c>
       <c r="C44">
-        <v>777703033</v>
+        <v>501351156.5097684</v>
+      </c>
+      <c r="D44">
+        <v>675105661.5551283</v>
       </c>
       <c r="E44">
-        <v>126782800</v>
+        <v>295888881.1335846</v>
+      </c>
+      <c r="G44">
+        <v>960093298.102969</v>
+      </c>
+      <c r="J44">
+        <v>156516448.36391386</v>
       </c>
     </row>
     <row r="45">
@@ -4238,19 +6536,40 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-30212918</v>
+        <v>24730216.079041056</v>
       </c>
       <c r="C48">
-        <v>-7910513</v>
+        <v>-24492449.920958944</v>
+      </c>
+      <c r="D48">
+        <v>-30614240.87873351</v>
       </c>
       <c r="E48">
-        <v>-45691</v>
+        <v>-37298581.66936022</v>
+      </c>
+      <c r="G48">
+        <v>-9765720.719611142</v>
+      </c>
+      <c r="J48">
+        <v>-56406.65013074003</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-1422635806.6347957</v>
+      </c>
+      <c r="C49">
+        <v>-754614869.6347958</v>
+      </c>
+      <c r="D49">
+        <v>362273508.1349027</v>
+      </c>
+      <c r="G49">
+        <v>107540424.3788131</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -4277,7 +6596,13 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="C54">
-        <v>-1662437</v>
+        <v>-2057094.8518471087</v>
+      </c>
+      <c r="D54">
+        <v>989051.6718094558</v>
+      </c>
+      <c r="G54">
+        <v>-2052319.020185721</v>
       </c>
     </row>
     <row r="55">
@@ -4319,6 +6644,9 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
+      <c r="C62">
+        <v>-321208.7923116108</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -4327,397 +6655,491 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="C64">
-        <v>-1662437</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-804541420.9778222</v>
+      </c>
+      <c r="C67">
+        <v>-1921578.9778221732</v>
+      </c>
+      <c r="D67">
+        <v>14137888.90047645</v>
+      </c>
+      <c r="E67">
+        <v>-2271500.035183275</v>
+      </c>
+      <c r="G67">
+        <v>-7280105.018358676</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-1839980</v>
-      </c>
-      <c r="C68">
-        <v>-22296337</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-12908968.55999226</v>
+      </c>
+      <c r="C78">
+        <v>-10289126.55999226</v>
+      </c>
+      <c r="D78">
+        <v>-6107375.409239052</v>
+      </c>
+      <c r="E78">
+        <v>17973765.306276478</v>
+      </c>
+      <c r="G78">
+        <v>-27525369.328074176</v>
+      </c>
+      <c r="J78">
+        <v>14615404.88512437</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>14559264</v>
-      </c>
-      <c r="C79">
-        <v>-5897093</v>
-      </c>
-      <c r="E79">
-        <v>11838896</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+      <c r="C92">
+        <v>8367547.582170086</v>
+      </c>
+      <c r="G92">
+        <v>20245264.3097155</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="J98">
+        <v>14615404.88512437</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C99">
-        <v>16399244</v>
-      </c>
-      <c r="E99">
-        <v>11838896</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>2351588755.1942415</v>
+      </c>
+      <c r="C101">
+        <v>2110192120.1942418</v>
+      </c>
+      <c r="D101">
+        <v>-384537144.3649877</v>
+      </c>
+      <c r="E101">
+        <v>-192367147.8278893</v>
+      </c>
+      <c r="G101">
+        <v>-85019226.48664293</v>
+      </c>
+      <c r="J101">
+        <v>2079585.8244475876</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-155822892</v>
-      </c>
-      <c r="C102">
-        <v>-67329600</v>
-      </c>
-      <c r="E102">
-        <v>1684524</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C104">
+        <v>2200844083.58875</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="J107">
+        <v>2079585.8244475876</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="E108">
-        <v>1684524</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="G109">
+        <v>94782031.08784331</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-71171703.7129006</v>
+      </c>
+      <c r="C110">
+        <v>-72444176.7129006</v>
+      </c>
+      <c r="E110">
+        <v>-76504258.95788543</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>-61970638</v>
-      </c>
-      <c r="C111">
-        <v>76776156</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-391706760.94185615</v>
+      </c>
+      <c r="C118">
+        <v>-362609062.94185615</v>
+      </c>
+      <c r="D118">
+        <v>-535962453.9422915</v>
+      </c>
+      <c r="E118">
+        <v>-323380294.30111396</v>
+      </c>
+      <c r="G118">
+        <v>-307195588.86680496</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>-261947288</v>
+        <v>613623136.2602487</v>
       </c>
       <c r="C119">
-        <v>-247298808</v>
+        <v>344401276.26024866</v>
+      </c>
+      <c r="D119">
+        <v>224702331.30668667</v>
+      </c>
+      <c r="E119">
+        <v>207517405.43111008</v>
+      </c>
+      <c r="G119">
+        <v>127394331.29231873</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>168095034</v>
-      </c>
-      <c r="C120">
-        <v>103193052</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>116089237.93746495</v>
+      </c>
+      <c r="C125">
+        <v>1351277367.937465</v>
+      </c>
+      <c r="D125">
+        <v>-7471893.815044522</v>
+      </c>
+      <c r="G125">
+        <v>13188773.853625774</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>116089237.93746495</v>
+      </c>
+      <c r="C127">
+        <v>1351277367.937465</v>
+      </c>
+      <c r="D127">
+        <v>-7471893.815044522</v>
+      </c>
+      <c r="E127">
+        <v>-14918337.397778539</v>
+      </c>
+      <c r="G127">
+        <v>13188773.853625774</v>
+      </c>
+      <c r="J127">
+        <v>984040.5599759909</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>-12084280</v>
+        <v>1371088546.0139902</v>
       </c>
       <c r="C128">
-        <v>20234511</v>
-      </c>
-      <c r="E128">
-        <v>797101</v>
+        <v>19836178.01399027</v>
+      </c>
+      <c r="D128">
+        <v>25731787.474209853</v>
+      </c>
+      <c r="G128">
+        <v>751792.9330453317</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>1373771997.4515393</v>
+      </c>
+      <c r="C129">
+        <v>1377241403.4515393</v>
+      </c>
+      <c r="D129">
+        <v>24155504.886484496</v>
+      </c>
+      <c r="G129">
+        <v>19836178.01399027</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/PAHOL (TRY).xlsx
+++ b/data/PAHOL (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>1490769</v>
+        <v>589008</v>
       </c>
       <c r="C3">
-        <v>1377215924</v>
+        <v>1595322.6149598889</v>
       </c>
       <c r="D3">
-        <v>4862303.652870915</v>
+        <v>1473814918</v>
       </c>
       <c r="E3">
-        <v>314064.21833425394</v>
+        <v>5203316.528735872</v>
       </c>
       <c r="F3">
-        <v>25964035.514074225</v>
+        <v>336090.802839565</v>
       </c>
       <c r="G3">
-        <v>984040.5599759909</v>
+        <v>27784997.562482394</v>
+      </c>
+      <c r="H3">
+        <v>1053055.2750744692</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +507,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>3236900263</v>
+        <v>1691363030</v>
       </c>
       <c r="C10">
-        <v>3083937695</v>
+        <v>3463917073.626774</v>
       </c>
       <c r="D10">
-        <v>943827478.5001456</v>
+        <v>3300247477</v>
       </c>
       <c r="E10">
-        <v>742448963.9533551</v>
+        <v>1010021888.7512757</v>
       </c>
       <c r="F10">
-        <v>725534938.4899669</v>
+        <v>794519890.5050526</v>
       </c>
       <c r="G10">
-        <v>14615406.119648678</v>
+        <v>776419616.5311836</v>
+      </c>
+      <c r="H10">
+        <v>15640443.227286516</v>
       </c>
     </row>
     <row r="11">
@@ -553,22 +563,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>23871154</v>
+        <v>16331636</v>
       </c>
       <c r="C17">
-        <v>11418</v>
+        <v>25545333.86553531</v>
       </c>
       <c r="D17">
-        <v>6932338.5358901415</v>
+        <v>12219</v>
       </c>
       <c r="E17">
-        <v>14433406.37362595</v>
+        <v>7418531.268669706</v>
       </c>
       <c r="F17">
-        <v>902489.1291368207</v>
+        <v>15445679.108400885</v>
       </c>
       <c r="G17">
-        <v>5702.267776014711</v>
+        <v>965784.3149860412</v>
+      </c>
+      <c r="H17">
+        <v>6102.190708039474</v>
       </c>
     </row>
     <row r="18">
@@ -591,22 +604,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>20669077</v>
+        <v>59434526</v>
       </c>
       <c r="C21">
-        <v>34313943</v>
+        <v>22118682.350147672</v>
       </c>
       <c r="D21">
-        <v>38228193.67718177</v>
+        <v>36720750</v>
       </c>
       <c r="E21">
-        <v>44428244.71987791</v>
+        <v>40909290.37448104</v>
       </c>
       <c r="F21">
-        <v>9822127.253051478</v>
+        <v>47544175.88814465</v>
       </c>
       <c r="G21">
-        <v>56406.65013074003</v>
+        <v>10510992.470199525</v>
+      </c>
+      <c r="H21">
+        <v>60362.6749601714</v>
       </c>
     </row>
     <row r="22">
@@ -624,22 +640,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>3282931263</v>
+        <v>1767718200</v>
       </c>
       <c r="C24">
-        <v>4495478980</v>
+        <v>3513176412.457417</v>
       </c>
       <c r="D24">
-        <v>993850314.3660884</v>
+        <v>4810795364</v>
       </c>
       <c r="E24">
-        <v>801624679.2651932</v>
+        <v>1063553026.9231623</v>
       </c>
       <c r="F24">
-        <v>762223590.3862294</v>
+        <v>857845836.3044378</v>
       </c>
       <c r="G24">
-        <v>15661555.597531425</v>
+        <v>815681390.8788517</v>
+      </c>
+      <c r="H24">
+        <v>16759963.368029198</v>
       </c>
     </row>
     <row r="25">
@@ -652,22 +671,25 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>45951081228</v>
+        <v>49118013080</v>
       </c>
       <c r="C26">
-        <v>45151081228</v>
+        <v>49173815034.312645</v>
       </c>
       <c r="D26">
-        <v>42187572271.874374</v>
+        <v>48318013080</v>
       </c>
       <c r="E26">
-        <v>39384984171.614235</v>
+        <v>45146356085.735565</v>
       </c>
       <c r="F26">
-        <v>37140510743.92522</v>
+        <v>42147211230.45452</v>
       </c>
       <c r="G26">
-        <v>14776541567.868372</v>
+        <v>39745323870.39483</v>
+      </c>
+      <c r="H26">
+        <v>15812879751.400295</v>
       </c>
     </row>
     <row r="27">
@@ -724,6 +746,12 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
+      <c r="B37">
+        <v>589046352</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -735,19 +763,22 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>30291350</v>
+        <v>32840048</v>
       </c>
       <c r="C39">
-        <v>27804965</v>
+        <v>32415803.986174405</v>
       </c>
       <c r="D39">
-        <v>24646435.076365665</v>
+        <v>29755225</v>
       </c>
       <c r="E39">
-        <v>22587169.063371398</v>
+        <v>26374988.516307224</v>
       </c>
       <c r="F39">
-        <v>23270152.836769715</v>
+        <v>24171297.910486978</v>
+      </c>
+      <c r="G39">
+        <v>24902182.077888485</v>
       </c>
     </row>
     <row r="40">
@@ -790,22 +821,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>45981372578</v>
+        <v>49739899480</v>
       </c>
       <c r="C47">
-        <v>45178886193</v>
+        <v>49206230838.29881</v>
       </c>
       <c r="D47">
-        <v>42212218706.95073</v>
+        <v>48347768305</v>
       </c>
       <c r="E47">
-        <v>39407571340.677605</v>
+        <v>45172731074.25186</v>
       </c>
       <c r="F47">
-        <v>37163780896.761986</v>
+        <v>42171382528.365005</v>
       </c>
       <c r="G47">
-        <v>14776541567.868372</v>
+        <v>39770226052.47272</v>
+      </c>
+      <c r="H47">
+        <v>15812879751.400295</v>
       </c>
     </row>
     <row r="48">
@@ -813,22 +847,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>49264303841</v>
+        <v>51507617680</v>
       </c>
       <c r="C48">
-        <v>49674365173</v>
+        <v>52719407250.75623</v>
       </c>
       <c r="D48">
-        <v>43206069021.31682</v>
+        <v>53158563669</v>
       </c>
       <c r="E48">
-        <v>40209196019.94281</v>
+        <v>46236284101.175026</v>
       </c>
       <c r="F48">
-        <v>37926004487.14822</v>
+        <v>43029228364.66946</v>
       </c>
       <c r="G48">
-        <v>14792203123.465902</v>
+        <v>40585907443.35157</v>
+      </c>
+      <c r="H48">
+        <v>15829639714.768324</v>
       </c>
     </row>
     <row r="49">
@@ -841,19 +878,22 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>3858714</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>22337441</v>
+        <v>4129341.1043980205</v>
       </c>
       <c r="D50">
-        <v>39732431.81044898</v>
+        <v>23904207</v>
       </c>
       <c r="E50">
-        <v>57868389.87147569</v>
+        <v>42519026.76709869</v>
       </c>
       <c r="F50">
-        <v>77381673.57729228</v>
+        <v>61926932.37737097</v>
+      </c>
+      <c r="G50">
+        <v>82808761.00945114</v>
       </c>
     </row>
     <row r="51">
@@ -876,22 +916,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>5885166</v>
+        <v>6360635</v>
       </c>
       <c r="C54">
-        <v>2483950</v>
+        <v>6297916.3187543005</v>
       </c>
       <c r="D54">
-        <v>4669775.089789203</v>
+        <v>2658176</v>
       </c>
       <c r="E54">
-        <v>2568985.8265930647</v>
+        <v>4997285.164580872</v>
       </c>
       <c r="F54">
-        <v>1431513.724463341</v>
+        <v>2749159.1163187185</v>
       </c>
       <c r="G54">
-        <v>133903.9135295977</v>
+        <v>1531911.529057706</v>
+      </c>
+      <c r="H54">
+        <v>143295.13256943272</v>
       </c>
     </row>
     <row r="55">
@@ -899,22 +942,25 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>1265912688</v>
+        <v>298033012</v>
       </c>
       <c r="C55">
-        <v>1617930972</v>
+        <v>1354696227.0687559</v>
       </c>
       <c r="D55">
-        <v>1431175009.4437845</v>
+        <v>1731413905</v>
       </c>
       <c r="E55">
-        <v>1188268975.375832</v>
+        <v>1531549058.5939887</v>
       </c>
       <c r="F55">
-        <v>1116609747.419933</v>
+        <v>1271607049.1620636</v>
       </c>
       <c r="G55">
-        <v>156516449.59843814</v>
+        <v>1194922071.8593347</v>
+      </c>
+      <c r="H55">
+        <v>167493576.5753232</v>
       </c>
     </row>
     <row r="56">
@@ -947,10 +993,16 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
-        <v>24322438</v>
-      </c>
-      <c r="G61">
-        <v>2052318.8860694023</v>
+        <v>28538229</v>
+      </c>
+      <c r="C61">
+        <v>26028268.224225063</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>2196256.2489935094</v>
       </c>
     </row>
     <row r="62">
@@ -958,19 +1010,22 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>1133784</v>
+        <v>1174817</v>
       </c>
       <c r="C62">
-        <v>796617</v>
+        <v>1213300.823722309</v>
       </c>
       <c r="D62">
-        <v>739728.9670173022</v>
+        <v>852492</v>
       </c>
       <c r="E62">
-        <v>713895.7784028325</v>
+        <v>791609.1292639034</v>
       </c>
       <c r="F62">
-        <v>360643.51660135406</v>
+        <v>763964.1554194058</v>
+      </c>
+      <c r="G62">
+        <v>385936.8942960326</v>
       </c>
     </row>
     <row r="63">
@@ -993,22 +1048,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>1301112790</v>
+        <v>334106693</v>
       </c>
       <c r="C66">
-        <v>1643548980</v>
+        <v>1392365053.5398555</v>
       </c>
       <c r="D66">
-        <v>1476316945.3110402</v>
+        <v>1758828780</v>
       </c>
       <c r="E66">
-        <v>1249420246.8523037</v>
+        <v>1579856979.6549325</v>
       </c>
       <c r="F66">
-        <v>1195783578.23829</v>
+        <v>1337047104.8111727</v>
       </c>
       <c r="G66">
-        <v>158702672.39803714</v>
+        <v>1279648681.2921398</v>
+      </c>
+      <c r="H66">
+        <v>169833127.95688614</v>
       </c>
     </row>
     <row r="67">
@@ -1020,11 +1078,11 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>0</v>
       </c>
-      <c r="F68">
-        <v>17400357.510551047</v>
+      <c r="G68">
+        <v>18620714.43997644</v>
       </c>
     </row>
     <row r="69">
@@ -1087,22 +1145,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>3400323</v>
+        <v>4709227</v>
       </c>
       <c r="C80">
-        <v>2693216</v>
+        <v>3638801.3032658007</v>
       </c>
       <c r="D80">
-        <v>2630535.4522781405</v>
+        <v>2882120</v>
       </c>
       <c r="E80">
-        <v>2130137.1257881913</v>
+        <v>2815025.464356354</v>
       </c>
       <c r="F80">
-        <v>1467942.095734902</v>
+        <v>2279532.1942806426</v>
       </c>
       <c r="G80">
-        <v>9233.007295261752</v>
+        <v>1570894.7682555134</v>
+      </c>
+      <c r="H80">
+        <v>9880.555164630274</v>
       </c>
     </row>
     <row r="81">
@@ -1115,22 +1176,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>4687176131</v>
+        <v>5321168587</v>
       </c>
       <c r="C82">
-        <v>4251100519</v>
+        <v>5015906610.671737</v>
       </c>
       <c r="D82">
-        <v>2269441776.686964</v>
+        <v>4549276006</v>
       </c>
       <c r="E82">
-        <v>1672220066.2308114</v>
+        <v>2428606839.6132894</v>
       </c>
       <c r="F82">
-        <v>1170855193.9246302</v>
+        <v>1789499572.9370122</v>
       </c>
       <c r="G82">
-        <v>429963587.39754224</v>
+        <v>1252971969.3065853</v>
+      </c>
+      <c r="H82">
+        <v>460118659.9564264</v>
       </c>
     </row>
     <row r="83">
@@ -1143,22 +1207,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>4690576454</v>
+        <v>5325877814</v>
       </c>
       <c r="C84">
-        <v>4253793735</v>
+        <v>5019545411.975003</v>
       </c>
       <c r="D84">
-        <v>2272072312.139242</v>
+        <v>4552158126</v>
       </c>
       <c r="E84">
-        <v>1674350203.3565996</v>
+        <v>2431421865.077646</v>
       </c>
       <c r="F84">
-        <v>1189723493.530916</v>
+        <v>1791779105.1312928</v>
       </c>
       <c r="G84">
-        <v>429972820.40483755</v>
+        <v>1273163578.514817</v>
+      </c>
+      <c r="H84">
+        <v>460128540.5115911</v>
       </c>
     </row>
     <row r="85">
@@ -1171,22 +1238,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>43272614597</v>
+        <v>45847633173</v>
       </c>
       <c r="C86">
-        <v>43777022458</v>
+        <v>46307496785.24138</v>
       </c>
       <c r="D86">
-        <v>39457679763.86654</v>
+        <v>46847576763</v>
       </c>
       <c r="E86">
-        <v>37285425569.733894</v>
+        <v>42225005256.44245</v>
       </c>
       <c r="F86">
-        <v>35540497415.37901</v>
+        <v>39900402154.726974</v>
       </c>
       <c r="G86">
-        <v>14203527630.663029</v>
+        <v>38033095183.54462</v>
+      </c>
+      <c r="H86">
+        <v>15199678046.299849</v>
       </c>
     </row>
     <row r="87">
@@ -1200,7 +1270,7 @@
         <v>20000000000</v>
       </c>
       <c r="D87">
-        <v>18000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="E87">
         <v>18000000000</v>
@@ -1209,6 +1279,9 @@
         <v>18000000000</v>
       </c>
       <c r="G87">
+        <v>18000000000</v>
+      </c>
+      <c r="H87">
         <v>6000000000</v>
       </c>
     </row>
@@ -1217,22 +1290,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>15717661486</v>
+        <v>18222925962</v>
       </c>
       <c r="C88">
-        <v>15717661486</v>
+        <v>18222684481.698795</v>
       </c>
       <c r="D88">
-        <v>15497946496.506775</v>
+        <v>18222925962</v>
       </c>
       <c r="E88">
-        <v>15497946496.779785</v>
+        <v>17847291968.50326</v>
       </c>
       <c r="F88">
-        <v>15497946496.125776</v>
+        <v>17847291968.795418</v>
       </c>
       <c r="G88">
-        <v>6478295305.549067</v>
+        <v>17847291968.095543</v>
+      </c>
+      <c r="H88">
+        <v>7353448251.935908</v>
       </c>
     </row>
     <row r="89">
@@ -1265,10 +1341,13 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>992901584</v>
+        <v>1062544471</v>
       </c>
       <c r="C94">
-        <v>992901584</v>
+        <v>1062537758.2876326</v>
+      </c>
+      <c r="D94">
+        <v>1062544471</v>
       </c>
     </row>
     <row r="95">
@@ -1286,19 +1365,22 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-902151</v>
+        <v>-1185752</v>
       </c>
       <c r="C97">
-        <v>-618824</v>
+        <v>-965422.4714953683</v>
       </c>
       <c r="D97">
-        <v>-767123.9544074934</v>
+        <v>-662229</v>
       </c>
       <c r="E97">
-        <v>-624553.2542741932</v>
+        <v>-820925.4371024169</v>
       </c>
       <c r="F97">
-        <v>-108515.91880746868</v>
+        <v>-668355.6813902183</v>
+      </c>
+      <c r="G97">
+        <v>-116126.57585226547</v>
       </c>
     </row>
     <row r="98">
@@ -1311,19 +1393,22 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>583037</v>
+        <v>253485</v>
       </c>
       <c r="C99">
-        <v>236870</v>
+        <v>623927.7255284814</v>
       </c>
       <c r="D99">
-        <v>236874.31375437306</v>
+        <v>253485</v>
       </c>
       <c r="E99">
-        <v>236874.35148794606</v>
+        <v>253487.26035720867</v>
       </c>
       <c r="F99">
-        <v>236874.64787257355</v>
+        <v>253487.30073718863</v>
+      </c>
+      <c r="G99">
+        <v>253487.61790845994</v>
       </c>
     </row>
     <row r="100">
@@ -1346,19 +1431,22 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>7066495175</v>
+        <v>7562515074</v>
       </c>
       <c r="C103">
-        <v>2042384776</v>
+        <v>7562096851.47896</v>
       </c>
       <c r="D103">
-        <v>2042422560.454719</v>
+        <v>2185639228</v>
       </c>
       <c r="E103">
-        <v>2042422558.9875643</v>
+        <v>2185665854.332693</v>
       </c>
       <c r="F103">
-        <v>1724995451.0908372</v>
+        <v>2185665852.7626405</v>
+      </c>
+      <c r="G103">
+        <v>1845976307.4145944</v>
       </c>
     </row>
     <row r="104">
@@ -1366,22 +1454,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>-504124534</v>
+        <v>-999420067</v>
       </c>
       <c r="C104">
-        <v>5024456566</v>
+        <v>-539480811.4780462</v>
       </c>
       <c r="D104">
-        <v>3917840956.5457025</v>
+        <v>5376875846</v>
       </c>
       <c r="E104">
-        <v>1745444192.8693335</v>
+        <v>4192614871.7832494</v>
       </c>
       <c r="F104">
-        <v>317427109.4333314</v>
+        <v>1867859201.5495746</v>
       </c>
       <c r="G104">
-        <v>1725232325.1139624</v>
+        <v>339689546.9924187</v>
+      </c>
+      <c r="H104">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="105">
@@ -1394,22 +1485,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>43272614597</v>
+        <v>45847633173</v>
       </c>
       <c r="C106">
-        <v>43777022458</v>
+        <v>46307496785.24138</v>
       </c>
       <c r="D106">
-        <v>39457679763.86654</v>
+        <v>46847576763</v>
       </c>
       <c r="E106">
-        <v>37285425569.733894</v>
+        <v>42225005256.44245</v>
       </c>
       <c r="F106">
-        <v>35540497415.37901</v>
+        <v>39900402154.726974</v>
       </c>
       <c r="G106">
-        <v>14203527630.663029</v>
+        <v>38033095183.54462</v>
+      </c>
+      <c r="H106">
+        <v>15199678046.299849</v>
       </c>
     </row>
     <row r="107">
@@ -1417,39 +1511,48 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>49264303841</v>
+        <v>51507617680</v>
       </c>
       <c r="C107">
-        <v>49674365173</v>
+        <v>52719407250.75623</v>
       </c>
       <c r="D107">
-        <v>43206069021.31682</v>
+        <v>53158563669</v>
       </c>
       <c r="E107">
-        <v>40209196019.94281</v>
+        <v>46236284101.175026</v>
       </c>
       <c r="F107">
-        <v>37926004487.14822</v>
+        <v>43029228364.66946</v>
       </c>
       <c r="G107">
-        <v>14792203123.465902</v>
+        <v>40585907443.35157</v>
+      </c>
+      <c r="H107">
+        <v>15829639714.768324</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>11198</v>
+      </c>
+      <c r="C108">
+        <v>129.4862157786663</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1461,6 +1564,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1468,30 +1572,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1505,31 +1612,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>72257533</v>
+        <v>166025294</v>
       </c>
       <c r="C3">
-        <v>8219234986.054043</v>
+        <v>77325732</v>
       </c>
       <c r="D3">
-        <v>5193237051.5875</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E3">
-        <v>2349967622.3425293</v>
+        <v>5557459615.302675</v>
       </c>
       <c r="F3">
-        <v>1832451851</v>
+        <v>2514749643</v>
       </c>
       <c r="G3">
-        <v>1510135077.3913946</v>
+        <v>1960981445</v>
       </c>
       <c r="H3">
-        <v>1128360421.3177102</v>
+        <v>1616046913.1077275</v>
       </c>
       <c r="I3">
-        <v>864262394.5483164</v>
+        <v>1207496867.6929903</v>
       </c>
       <c r="J3">
-        <v>2164444883.4405856</v>
+        <v>924876586.0319843</v>
+      </c>
+      <c r="K3">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="4">
@@ -1551,17 +1661,29 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="D7">
+      <c r="B7">
         <v>0</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
-        <v>-813300957.0461059</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-813300955.9468701</v>
+        <v>-870341018.3228749</v>
       </c>
       <c r="I7">
-        <v>-813300957.0732496</v>
+        <v>-870341017.1465453</v>
+      </c>
+      <c r="J7">
+        <v>-870341018.3519223</v>
       </c>
     </row>
     <row r="8">
@@ -1569,31 +1691,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>72257533</v>
+        <v>166025294</v>
       </c>
       <c r="C8">
-        <v>8219234986.054043</v>
+        <v>77325732</v>
       </c>
       <c r="D8">
-        <v>5193237051.5875</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E8">
-        <v>2349967622.3425293</v>
+        <v>5557459615.302675</v>
       </c>
       <c r="F8">
-        <v>1832451851</v>
+        <v>2514749643</v>
       </c>
       <c r="G8">
-        <v>696834120.3452888</v>
+        <v>1960981445</v>
       </c>
       <c r="H8">
-        <v>315059465.37084</v>
+        <v>745705894.7848526</v>
       </c>
       <c r="I8">
-        <v>50961437.47506681</v>
+        <v>337155850.54644483</v>
       </c>
       <c r="J8">
-        <v>2164444883.4405856</v>
+        <v>54535567.68006208</v>
+      </c>
+      <c r="K8">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="9">
@@ -1621,31 +1746,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>72257533</v>
+        <v>166025294</v>
       </c>
       <c r="C13">
-        <v>8219234986.054043</v>
+        <v>77325732</v>
       </c>
       <c r="D13">
-        <v>5193237051.5875</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E13">
-        <v>2349967622.3425293</v>
+        <v>5557459615.302675</v>
       </c>
       <c r="F13">
-        <v>1832451851</v>
+        <v>2514749643</v>
       </c>
       <c r="G13">
-        <v>696834120.3452888</v>
+        <v>1960981445</v>
       </c>
       <c r="H13">
-        <v>315059465.37084</v>
+        <v>745705894.7848526</v>
       </c>
       <c r="I13">
-        <v>50961437.47506681</v>
+        <v>337155850.54644483</v>
       </c>
       <c r="J13">
-        <v>2164444883.4405856</v>
+        <v>54535567.68006208</v>
+      </c>
+      <c r="K13">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="14"/>
@@ -1654,31 +1782,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-67174315</v>
+        <v>-150502113</v>
       </c>
       <c r="C15">
-        <v>-191338425.59233552</v>
+        <v>-71885974</v>
       </c>
       <c r="D15">
-        <v>-143530292.39473513</v>
+        <v>-204757757.5454499</v>
       </c>
       <c r="E15">
-        <v>-101247392.63008076</v>
+        <v>-153596648.0314028</v>
       </c>
       <c r="F15">
-        <v>-37228211</v>
+        <v>-108346959</v>
       </c>
       <c r="G15">
-        <v>-96503877.9629696</v>
+        <v>-39839427</v>
       </c>
       <c r="H15">
-        <v>-68582313.97319451</v>
+        <v>-103272082.35860462</v>
       </c>
       <c r="I15">
-        <v>-48033528.520380445</v>
+        <v>-73392266.98953144</v>
       </c>
       <c r="J15">
-        <v>-6417209.196505936</v>
+        <v>-51402312.71570829</v>
+      </c>
+      <c r="K15">
+        <v>-6867273.84062487</v>
       </c>
     </row>
     <row r="16">
@@ -1696,28 +1827,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>57843</v>
+        <v>56386</v>
       </c>
       <c r="C18">
-        <v>129855.30304194521</v>
+        <v>61900</v>
       </c>
       <c r="D18">
-        <v>166413.98359477552</v>
+        <v>138962.57677432577</v>
       </c>
       <c r="E18">
-        <v>64370.566437964735</v>
+        <v>178085.2643664507</v>
       </c>
       <c r="F18">
-        <v>21809</v>
+        <v>68885</v>
       </c>
       <c r="G18">
-        <v>47712.098888120505</v>
+        <v>23339</v>
       </c>
       <c r="H18">
-        <v>66605.32627508746</v>
+        <v>51058.33993289451</v>
       </c>
       <c r="I18">
-        <v>17493.209436269422</v>
+        <v>71276.62520714417</v>
+      </c>
+      <c r="J18">
+        <v>18720.078444018047</v>
       </c>
     </row>
     <row r="19">
@@ -1725,25 +1859,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-326456</v>
+        <v>-610644</v>
       </c>
       <c r="C19">
-        <v>-184756.45912910835</v>
+        <v>-349354</v>
       </c>
       <c r="D19">
-        <v>-199767.74821365994</v>
+        <v>-197714.1713495377</v>
       </c>
       <c r="E19">
-        <v>-71902.39923758927</v>
+        <v>-213778.26240340702</v>
       </c>
       <c r="F19">
-        <v>-51531</v>
-      </c>
-      <c r="H19">
-        <v>-21378.79276673339</v>
+        <v>-76944</v>
+      </c>
+      <c r="G19">
+        <v>-55145</v>
       </c>
       <c r="I19">
-        <v>-492846.7940118193</v>
+        <v>-22878.173332897764</v>
+      </c>
+      <c r="J19">
+        <v>-527412.1183077547</v>
       </c>
     </row>
     <row r="20">
@@ -1756,31 +1893,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>4814605</v>
+        <v>14968923</v>
       </c>
       <c r="C21">
-        <v>8027841659.30562</v>
+        <v>5152304</v>
       </c>
       <c r="D21">
-        <v>5049673405.428145</v>
+        <v>8590866424.246395</v>
       </c>
       <c r="E21">
-        <v>2248712697.879649</v>
+        <v>5403827274.273235</v>
       </c>
       <c r="F21">
-        <v>1795193918</v>
+        <v>2406394625</v>
       </c>
       <c r="G21">
-        <v>600377954.4812074</v>
+        <v>1921110212</v>
       </c>
       <c r="H21">
-        <v>246522377.9311539</v>
+        <v>642484870.766181</v>
       </c>
       <c r="I21">
-        <v>2452555.3701108177</v>
+        <v>263811982.0087877</v>
       </c>
       <c r="J21">
-        <v>2158027674.24408</v>
+        <v>2624562.9244900504</v>
+      </c>
+      <c r="K21">
+        <v>2309378818.87192</v>
       </c>
     </row>
     <row r="22"/>
@@ -1798,11 +1938,35 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1839,31 +2003,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>4814605</v>
+        <v>14968923</v>
       </c>
       <c r="C33">
-        <v>8027841659.30562</v>
+        <v>5152304</v>
       </c>
       <c r="D33">
-        <v>5049673405.428145</v>
+        <v>8590866424.246395</v>
       </c>
       <c r="E33">
-        <v>2248712697.879649</v>
+        <v>5403827274.273235</v>
       </c>
       <c r="F33">
-        <v>1795193918</v>
+        <v>2406394625</v>
       </c>
       <c r="G33">
-        <v>600377954.4812074</v>
+        <v>1921110212</v>
       </c>
       <c r="H33">
-        <v>246522377.9311539</v>
+        <v>642484870.766181</v>
       </c>
       <c r="I33">
-        <v>2452555.3701108177</v>
+        <v>263811982.0087877</v>
       </c>
       <c r="J33">
-        <v>2158027674.24408</v>
+        <v>2624562.9244900504</v>
+      </c>
+      <c r="K33">
+        <v>2309378818.87192</v>
       </c>
     </row>
     <row r="34"/>
@@ -1872,28 +2039,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>316591167</v>
+        <v>410049282</v>
       </c>
       <c r="C35">
-        <v>351175889.2086446</v>
+        <v>338797117</v>
       </c>
       <c r="D35">
-        <v>135972163.969999</v>
+        <v>375805264.1845914</v>
       </c>
       <c r="E35">
-        <v>84735222.62519595</v>
+        <v>145508437.7166238</v>
       </c>
       <c r="F35">
-        <v>47429557</v>
+        <v>90676939</v>
       </c>
       <c r="G35">
-        <v>127478647.8300051</v>
+        <v>50756303</v>
       </c>
       <c r="H35">
-        <v>38496549.948485695</v>
+        <v>136419237.19081527</v>
       </c>
       <c r="I35">
-        <v>4447183.700769754</v>
+        <v>41196467.54846135</v>
+      </c>
+      <c r="J35">
+        <v>4759082.547811901</v>
       </c>
     </row>
     <row r="36">
@@ -1901,31 +2071,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-97190698</v>
+        <v>-114462275</v>
       </c>
       <c r="C36">
-        <v>-378524735.4353064</v>
+        <v>-104007729</v>
       </c>
       <c r="D36">
-        <v>-269470430.585682</v>
+        <v>-405072194.79453427</v>
       </c>
       <c r="E36">
-        <v>-152737425.0195296</v>
+        <v>-288369473.72551847</v>
       </c>
       <c r="F36">
-        <v>-69773823</v>
+        <v>-163447522</v>
       </c>
       <c r="G36">
-        <v>-314609666.96748596</v>
+        <v>-74667813</v>
       </c>
       <c r="H36">
-        <v>-35326766.401446894</v>
+        <v>-336674505.97525805</v>
       </c>
       <c r="I36">
-        <v>-127679338.27149867</v>
+        <v>-37804374.35553959</v>
       </c>
       <c r="J36">
-        <v>-36990.051823496164</v>
+        <v>-136634002.85868266</v>
+      </c>
+      <c r="K36">
+        <v>-39584.3126618287</v>
       </c>
     </row>
     <row r="37">
@@ -1933,31 +2106,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>125961784</v>
+        <v>191229900</v>
       </c>
       <c r="C37">
-        <v>382909133.7713632</v>
+        <v>134796841</v>
       </c>
       <c r="D37">
-        <v>337801670.9233967</v>
+        <v>409764088.5879416</v>
       </c>
       <c r="E37">
-        <v>233558964.85793552</v>
+        <v>361493058.27752864</v>
       </c>
       <c r="F37">
-        <v>148490344</v>
+        <v>249936346</v>
       </c>
       <c r="G37">
-        <v>777260000.358579</v>
+        <v>158905572</v>
       </c>
       <c r="H37">
-        <v>830530149.9567298</v>
+        <v>831772364.6492331</v>
       </c>
       <c r="I37">
-        <v>786164989.3788397</v>
+        <v>888778563.7023568</v>
       </c>
       <c r="J37">
-        <v>-742452.794682281</v>
+        <v>841301896.3003416</v>
+      </c>
+      <c r="K37">
+        <v>-794523.9898983773</v>
       </c>
     </row>
     <row r="38">
@@ -1965,31 +2141,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>350176858</v>
+        <v>501785830</v>
       </c>
       <c r="C38">
-        <v>8383401946.850322</v>
+        <v>374738533</v>
       </c>
       <c r="D38">
-        <v>5253976809.73586</v>
+        <v>8971363582.224396</v>
       </c>
       <c r="E38">
-        <v>2414269460.3432508</v>
+        <v>5622459296.54187</v>
       </c>
       <c r="F38">
-        <v>1921339996</v>
+        <v>2583560388</v>
       </c>
       <c r="G38">
-        <v>1190506935.7023053</v>
+        <v>2056104274</v>
       </c>
       <c r="H38">
-        <v>1080222311.4349227</v>
+        <v>1274001966.630971</v>
       </c>
       <c r="I38">
-        <v>665385390.1782215</v>
+        <v>1155982638.9040666</v>
       </c>
       <c r="J38">
-        <v>2157248231.397574</v>
+        <v>712051538.9139607</v>
+      </c>
+      <c r="K38">
+        <v>2308544710.5693593</v>
       </c>
     </row>
     <row r="39"/>
@@ -1998,31 +2177,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-854301392</v>
+        <v>-1501205897</v>
       </c>
       <c r="C40">
-        <v>-3358852427.897002</v>
+        <v>-914222754</v>
       </c>
       <c r="D40">
-        <v>-1336135853.1901567</v>
+        <v>-3594422233.4493256</v>
       </c>
       <c r="E40">
-        <v>-668825267.4739174</v>
+        <v>-1429844424.7586198</v>
       </c>
       <c r="F40">
-        <v>-621552231</v>
+        <v>-715723947</v>
       </c>
       <c r="G40">
-        <v>-873079826.2689741</v>
+        <v>-665148386</v>
       </c>
       <c r="H40">
-        <v>-561461096.8174993</v>
+        <v>-934312419.6385524</v>
       </c>
       <c r="I40">
-        <v>-214325718.10083106</v>
+        <v>-600838617.6350194</v>
       </c>
       <c r="J40">
-        <v>-432015906.28361166</v>
+        <v>-229357241.16464308</v>
+      </c>
+      <c r="K40">
+        <v>-462314916.2054199</v>
       </c>
     </row>
     <row r="41">
@@ -2030,19 +2212,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-30266424</v>
+        <v>-43107573</v>
       </c>
       <c r="C41">
-        <v>-2057094.8518471087</v>
+        <v>-32389334</v>
       </c>
       <c r="D41">
+        <v>-2201367.1724252747</v>
+      </c>
+      <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
-      <c r="H41">
-        <v>-989052.5203045836</v>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>-1058418.7443024218</v>
       </c>
     </row>
     <row r="42">
@@ -2050,22 +2238,28 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-824034968</v>
+        <v>-1458098324</v>
       </c>
       <c r="C42">
-        <v>-3356795333.0451555</v>
+        <v>-881833420</v>
       </c>
       <c r="D42">
-        <v>-1336135853.1901567</v>
+        <v>-3592220866.2769003</v>
+      </c>
+      <c r="E42">
+        <v>-1429844424.7586198</v>
       </c>
       <c r="F42">
-        <v>-621552231</v>
+        <v>-715723947</v>
       </c>
       <c r="G42">
-        <v>-873079826.2689741</v>
+        <v>-665148386</v>
       </c>
       <c r="H42">
-        <v>-560472044.2971947</v>
+        <v>-934312419.6385524</v>
+      </c>
+      <c r="I42">
+        <v>-599780198.890717</v>
       </c>
     </row>
     <row r="43">
@@ -2073,31 +2267,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-504124534</v>
+        <v>-999420067</v>
       </c>
       <c r="C43">
-        <v>5024549518.95332</v>
+        <v>-539484221</v>
       </c>
       <c r="D43">
-        <v>3917840956.5457025</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E43">
-        <v>1745444192.8693335</v>
+        <v>4192614871.7832494</v>
       </c>
       <c r="F43">
-        <v>1299787765</v>
+        <v>1867836441</v>
       </c>
       <c r="G43">
-        <v>317427109.4333314</v>
+        <v>1390955888</v>
       </c>
       <c r="H43">
-        <v>518761214.6174233</v>
+        <v>339689546.9924187</v>
       </c>
       <c r="I43">
-        <v>451059672.07739043</v>
+        <v>555144021.269047</v>
       </c>
       <c r="J43">
-        <v>1725232325.1139624</v>
+        <v>482694297.74931765</v>
+      </c>
+      <c r="K43">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="44">
@@ -2111,31 +2308,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-504124534</v>
+        <v>-999420067</v>
       </c>
       <c r="C46">
-        <v>5024549518.95332</v>
+        <v>-539484221</v>
       </c>
       <c r="D46">
-        <v>3917840956.5457025</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E46">
-        <v>1745444192.8693335</v>
+        <v>4192614871.7832494</v>
       </c>
       <c r="F46">
-        <v>1299787765</v>
+        <v>1867836441</v>
       </c>
       <c r="G46">
-        <v>317427109.4333314</v>
+        <v>1390955888</v>
       </c>
       <c r="H46">
-        <v>518761214.6174233</v>
+        <v>339689546.9924187</v>
       </c>
       <c r="I46">
-        <v>451059672.07739043</v>
+        <v>555144021.269047</v>
       </c>
       <c r="J46">
-        <v>1725232325.1139624</v>
+        <v>482694297.74931765</v>
+      </c>
+      <c r="K46">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="47">
@@ -2151,6 +2351,9 @@
       <c r="D47">
         <v>0</v>
       </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
       <c r="F47">
         <v>0</v>
       </c>
@@ -2158,6 +2361,9 @@
         <v>0</v>
       </c>
       <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>0</v>
       </c>
     </row>
@@ -2166,31 +2372,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-504124534</v>
+        <v>-999420067</v>
       </c>
       <c r="C48">
-        <v>5024549518.95332</v>
+        <v>-539484221</v>
       </c>
       <c r="D48">
-        <v>3917840956.5457025</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E48">
-        <v>1745444192.8693335</v>
+        <v>4192614871.7832494</v>
       </c>
       <c r="F48">
-        <v>1299787765</v>
+        <v>1867836441</v>
       </c>
       <c r="G48">
-        <v>317427109.4333314</v>
+        <v>1390955888</v>
       </c>
       <c r="H48">
-        <v>518761214.6174233</v>
+        <v>339689546.9924187</v>
       </c>
       <c r="I48">
-        <v>451059672.07739043</v>
+        <v>555144021.269047</v>
       </c>
       <c r="J48">
-        <v>1725232325.1139624</v>
+        <v>482694297.74931765</v>
+      </c>
+      <c r="K48">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="49"/>
@@ -2199,40 +2408,43 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>1731018</v>
+        <v>3810980</v>
       </c>
       <c r="C50">
-        <v>5753800.939215167</v>
+        <v>1852421.2418574824</v>
       </c>
       <c r="D50">
-        <v>4154904.1241498925</v>
+        <v>6157338.098865354</v>
       </c>
       <c r="E50">
-        <v>2742137.7369044465</v>
+        <v>4446304.231068954</v>
       </c>
       <c r="F50">
-        <v>1223258</v>
+        <v>2934419</v>
       </c>
       <c r="G50">
-        <v>4255217.591726501</v>
+        <v>1309049.9945535518</v>
       </c>
       <c r="H50">
-        <v>2909701.1223204895</v>
+        <v>4553653.08485516</v>
       </c>
       <c r="I50">
-        <v>1599641.043972709</v>
+        <v>3113770.1436051102</v>
+      </c>
+      <c r="J50">
+        <v>1711830.2924649685</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2244,6 +2456,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2251,30 +2464,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2288,25 +2504,28 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>72257533</v>
+        <v>88699562</v>
       </c>
       <c r="C3">
-        <v>3025997934.466543</v>
+        <v>77325732</v>
       </c>
       <c r="D3">
-        <v>2843269429.2449703</v>
+        <v>3238223318.083746</v>
       </c>
       <c r="E3">
-        <v>517515771.3425293</v>
+        <v>3042709972.3026752</v>
       </c>
       <c r="F3">
-        <v>1832451851</v>
+        <v>553768198</v>
       </c>
       <c r="G3">
-        <v>381774656.07368445</v>
+        <v>1960981445</v>
       </c>
       <c r="H3">
-        <v>264098026.7693938</v>
+        <v>408550045.4147372</v>
+      </c>
+      <c r="I3">
+        <v>282620281.661006</v>
       </c>
     </row>
     <row r="4">
@@ -2328,11 +2547,26 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
-        <v>-1.0992357730865479</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1.1263794898986816</v>
+        <v>-1.1763296127319336</v>
+      </c>
+      <c r="I7">
+        <v>1.2053769826889038</v>
       </c>
     </row>
     <row r="8">
@@ -2340,25 +2574,28 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>72257533</v>
+        <v>88699562</v>
       </c>
       <c r="C8">
-        <v>3025997934.466543</v>
+        <v>77325732</v>
       </c>
       <c r="D8">
-        <v>2843269429.2449703</v>
+        <v>3238223318.083746</v>
       </c>
       <c r="E8">
-        <v>517515771.3425293</v>
+        <v>3042709972.3026752</v>
       </c>
       <c r="F8">
-        <v>1832451851</v>
+        <v>553768198</v>
       </c>
       <c r="G8">
-        <v>381774654.97444874</v>
+        <v>1960981445</v>
       </c>
       <c r="H8">
-        <v>264098027.8957732</v>
+        <v>408550044.2384078</v>
+      </c>
+      <c r="I8">
+        <v>282620282.8663828</v>
       </c>
     </row>
     <row r="9">
@@ -2386,25 +2623,28 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>72257533</v>
+        <v>88699562</v>
       </c>
       <c r="C13">
-        <v>3025997934.466543</v>
+        <v>77325732</v>
       </c>
       <c r="D13">
-        <v>2843269429.2449703</v>
+        <v>3238223318.083746</v>
       </c>
       <c r="E13">
-        <v>517515771.3425293</v>
+        <v>3042709972.3026752</v>
       </c>
       <c r="F13">
-        <v>1832451851</v>
+        <v>553768198</v>
       </c>
       <c r="G13">
-        <v>381774654.97444874</v>
+        <v>1960981445</v>
       </c>
       <c r="H13">
-        <v>264098027.8957732</v>
+        <v>408550044.2384078</v>
+      </c>
+      <c r="I13">
+        <v>282620282.8663828</v>
       </c>
     </row>
     <row r="14"/>
@@ -2413,25 +2653,28 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-67174315</v>
+        <v>-78616139</v>
       </c>
       <c r="C15">
-        <v>-47808133.197600394</v>
+        <v>-71885974</v>
       </c>
       <c r="D15">
-        <v>-42282899.76465437</v>
+        <v>-51161109.514047116</v>
       </c>
       <c r="E15">
-        <v>-64019181.63008076</v>
+        <v>-45249689.0314028</v>
       </c>
       <c r="F15">
-        <v>-37228211</v>
+        <v>-68507532</v>
       </c>
       <c r="G15">
-        <v>-27921563.98977509</v>
+        <v>-39839427</v>
       </c>
       <c r="H15">
-        <v>-20548785.452814065</v>
+        <v>-29879815.369073182</v>
+      </c>
+      <c r="I15">
+        <v>-21989954.27382315</v>
       </c>
     </row>
     <row r="16">
@@ -2449,25 +2692,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>57843</v>
+        <v>-5514</v>
       </c>
       <c r="C18">
-        <v>-36558.68055283031</v>
+        <v>61900</v>
       </c>
       <c r="D18">
-        <v>102043.41715681078</v>
+        <v>-39122.687592124916</v>
       </c>
       <c r="E18">
-        <v>42561.566437964735</v>
+        <v>109200.26436645069</v>
       </c>
       <c r="F18">
-        <v>21809</v>
+        <v>45546</v>
       </c>
       <c r="G18">
-        <v>-18893.22738696695</v>
+        <v>23339</v>
       </c>
       <c r="H18">
-        <v>49112.11683881804</v>
+        <v>-20218.28527424966</v>
+      </c>
+      <c r="I18">
+        <v>52556.54676312613</v>
       </c>
     </row>
     <row r="19">
@@ -2475,22 +2721,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-326456</v>
+        <v>-261290</v>
       </c>
       <c r="C19">
-        <v>15011.289084551594</v>
+        <v>-349354</v>
       </c>
       <c r="D19">
-        <v>-127865.34897607067</v>
+        <v>16064.091053869313</v>
       </c>
       <c r="E19">
-        <v>-20371.39923758927</v>
+        <v>-136834.26240340702</v>
       </c>
       <c r="F19">
-        <v>-51531</v>
-      </c>
-      <c r="H19">
-        <v>471468.0012450859</v>
+        <v>-21799</v>
+      </c>
+      <c r="G19">
+        <v>-55145</v>
+      </c>
+      <c r="I19">
+        <v>504533.944974857</v>
       </c>
     </row>
     <row r="20">
@@ -2503,25 +2752,28 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>4814605</v>
+        <v>9816619</v>
       </c>
       <c r="C21">
-        <v>2978168253.877475</v>
+        <v>5152304</v>
       </c>
       <c r="D21">
-        <v>2800960707.5484962</v>
+        <v>3187039149.97316</v>
       </c>
       <c r="E21">
-        <v>453518779.87964916</v>
+        <v>2997432649.2732353</v>
       </c>
       <c r="F21">
-        <v>1795193918</v>
+        <v>485284413</v>
       </c>
       <c r="G21">
-        <v>353855576.5500535</v>
+        <v>1921110212</v>
       </c>
       <c r="H21">
-        <v>244069822.56104308</v>
+        <v>378672888.7573933</v>
+      </c>
+      <c r="I21">
+        <v>261187419.08429763</v>
       </c>
     </row>
     <row r="22"/>
@@ -2539,11 +2791,35 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2580,25 +2856,28 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>4814605</v>
+        <v>9816619</v>
       </c>
       <c r="C33">
-        <v>2978168253.877475</v>
+        <v>5152304</v>
       </c>
       <c r="D33">
-        <v>2800960707.5484962</v>
+        <v>3187039149.97316</v>
       </c>
       <c r="E33">
-        <v>453518779.87964916</v>
+        <v>2997432649.2732353</v>
       </c>
       <c r="F33">
-        <v>1795193918</v>
+        <v>485284413</v>
       </c>
       <c r="G33">
-        <v>353855576.5500535</v>
+        <v>1921110212</v>
       </c>
       <c r="H33">
-        <v>244069822.56104308</v>
+        <v>378672888.7573933</v>
+      </c>
+      <c r="I33">
+        <v>261187419.08429763</v>
       </c>
     </row>
     <row r="34"/>
@@ -2607,25 +2886,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>316591167</v>
+        <v>71252165</v>
       </c>
       <c r="C35">
-        <v>215203725.23864564</v>
+        <v>338797117</v>
       </c>
       <c r="D35">
-        <v>51236941.344803035</v>
+        <v>230296826.4679676</v>
       </c>
       <c r="E35">
-        <v>37305665.62519595</v>
+        <v>54831498.71662381</v>
       </c>
       <c r="F35">
-        <v>47429557</v>
+        <v>39920636</v>
       </c>
       <c r="G35">
-        <v>88982097.8815194</v>
+        <v>50756303</v>
       </c>
       <c r="H35">
-        <v>34049366.24771594</v>
+        <v>95222769.64235392</v>
+      </c>
+      <c r="I35">
+        <v>36437385.000649445</v>
       </c>
     </row>
     <row r="36">
@@ -2633,25 +2915,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-97190698</v>
+        <v>-10454546</v>
       </c>
       <c r="C36">
-        <v>-109054304.8496244</v>
+        <v>-104007729</v>
       </c>
       <c r="D36">
-        <v>-116733005.56615236</v>
+        <v>-116702721.0690158</v>
       </c>
       <c r="E36">
-        <v>-82963602.01952961</v>
+        <v>-124921951.72551847</v>
       </c>
       <c r="F36">
-        <v>-69773823</v>
+        <v>-88779709</v>
       </c>
       <c r="G36">
-        <v>-279282900.5660391</v>
+        <v>-74667813</v>
       </c>
       <c r="H36">
-        <v>92352571.87005177</v>
+        <v>-298870131.61971843</v>
+      </c>
+      <c r="I36">
+        <v>98829628.50314307</v>
       </c>
     </row>
     <row r="37">
@@ -2659,25 +2944,28 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>125961784</v>
+        <v>56433059</v>
       </c>
       <c r="C37">
-        <v>45107462.84796649</v>
+        <v>134796841</v>
       </c>
       <c r="D37">
-        <v>104242706.06546119</v>
+        <v>48271030.31041294</v>
       </c>
       <c r="E37">
-        <v>85068620.85793552</v>
+        <v>111556712.27752864</v>
       </c>
       <c r="F37">
-        <v>148490344</v>
+        <v>91030774</v>
       </c>
       <c r="G37">
-        <v>-53270149.59815073</v>
+        <v>158905572</v>
       </c>
       <c r="H37">
-        <v>44365160.57789004</v>
+        <v>-57006199.05312371</v>
+      </c>
+      <c r="I37">
+        <v>47476667.40201521</v>
       </c>
     </row>
     <row r="38">
@@ -2685,25 +2973,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>350176858</v>
+        <v>127047297</v>
       </c>
       <c r="C38">
-        <v>3129425137.114462</v>
+        <v>374738533</v>
       </c>
       <c r="D38">
-        <v>2839707349.392609</v>
+        <v>3348904285.6825256</v>
       </c>
       <c r="E38">
-        <v>492929464.34325075</v>
+        <v>3038898908.54187</v>
       </c>
       <c r="F38">
-        <v>1921339996</v>
+        <v>527456114</v>
       </c>
       <c r="G38">
-        <v>110284624.26738262</v>
+        <v>2056104274</v>
       </c>
       <c r="H38">
-        <v>414836921.25670123</v>
+        <v>118019327.72690439</v>
+      </c>
+      <c r="I38">
+        <v>443931099.99010587</v>
       </c>
     </row>
     <row r="39"/>
@@ -2712,25 +3003,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-854301392</v>
+        <v>-586983143</v>
       </c>
       <c r="C40">
-        <v>-2022716574.7068455</v>
+        <v>-914222754</v>
       </c>
       <c r="D40">
-        <v>-667310585.7162393</v>
+        <v>-2164577808.690706</v>
       </c>
       <c r="E40">
-        <v>-47273036.473917365</v>
+        <v>-714120477.7586198</v>
       </c>
       <c r="F40">
-        <v>-621552231</v>
+        <v>-50575561</v>
       </c>
       <c r="G40">
-        <v>-311618729.4514748</v>
+        <v>-665148386</v>
       </c>
       <c r="H40">
-        <v>-347135378.71666825</v>
+        <v>-333473802.003533</v>
+      </c>
+      <c r="I40">
+        <v>-371481376.4703764</v>
       </c>
     </row>
     <row r="41">
@@ -2738,12 +3032,21 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-30266424</v>
+        <v>-10718239</v>
       </c>
       <c r="C41">
-        <v>-2057094.8518471087</v>
+        <v>-32389334</v>
+      </c>
+      <c r="D41">
+        <v>-2201367.1724252747</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
       </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>0</v>
       </c>
     </row>
@@ -2752,16 +3055,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-824034968</v>
+        <v>-576264904</v>
       </c>
       <c r="C42">
-        <v>-2020659479.8549988</v>
+        <v>-881833420</v>
+      </c>
+      <c r="D42">
+        <v>-2162376441.5182805</v>
+      </c>
+      <c r="E42">
+        <v>-714120477.7586198</v>
       </c>
       <c r="F42">
-        <v>-621552231</v>
+        <v>-50575561</v>
       </c>
       <c r="G42">
-        <v>-312607781.97177935</v>
+        <v>-665148386</v>
+      </c>
+      <c r="H42">
+        <v>-334532220.7478354</v>
       </c>
     </row>
     <row r="43">
@@ -2769,25 +3081,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-504124534</v>
+        <v>-459935846</v>
       </c>
       <c r="C43">
-        <v>1106708562.407617</v>
+        <v>-539484221</v>
       </c>
       <c r="D43">
-        <v>2172396763.6763687</v>
+        <v>1184326476.9918199</v>
       </c>
       <c r="E43">
-        <v>445656427.8693335</v>
+        <v>2324778430.7832494</v>
       </c>
       <c r="F43">
-        <v>1299787765</v>
+        <v>476880553</v>
       </c>
       <c r="G43">
-        <v>-201334105.18409193</v>
+        <v>1390955888</v>
       </c>
       <c r="H43">
-        <v>67701542.54003286</v>
+        <v>-215454474.27662832</v>
+      </c>
+      <c r="I43">
+        <v>72449723.51972938</v>
       </c>
     </row>
     <row r="44">
@@ -2801,25 +3116,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-504124534</v>
+        <v>-459935846</v>
       </c>
       <c r="C46">
-        <v>1106708562.407617</v>
+        <v>-539484221</v>
       </c>
       <c r="D46">
-        <v>2172396763.6763687</v>
+        <v>1184326476.9918199</v>
       </c>
       <c r="E46">
-        <v>445656427.8693335</v>
+        <v>2324778430.7832494</v>
       </c>
       <c r="F46">
-        <v>1299787765</v>
+        <v>476880553</v>
       </c>
       <c r="G46">
-        <v>-201334105.18409193</v>
+        <v>1390955888</v>
       </c>
       <c r="H46">
-        <v>67701542.54003286</v>
+        <v>-215454474.27662832</v>
+      </c>
+      <c r="I46">
+        <v>72449723.51972938</v>
       </c>
     </row>
     <row r="47">
@@ -2832,10 +3150,19 @@
       <c r="C47">
         <v>0</v>
       </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2844,25 +3171,28 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-504124534</v>
+        <v>-459935846</v>
       </c>
       <c r="C48">
-        <v>1106708562.407617</v>
+        <v>-539484221</v>
       </c>
       <c r="D48">
-        <v>2172396763.6763687</v>
+        <v>1184326476.9918199</v>
       </c>
       <c r="E48">
-        <v>445656427.8693335</v>
+        <v>2324778430.7832494</v>
       </c>
       <c r="F48">
-        <v>1299787765</v>
+        <v>476880553</v>
       </c>
       <c r="G48">
-        <v>-201334105.18409193</v>
+        <v>1390955888</v>
       </c>
       <c r="H48">
-        <v>67701542.54003286</v>
+        <v>-215454474.27662832</v>
+      </c>
+      <c r="I48">
+        <v>72449723.51972938</v>
       </c>
     </row>
     <row r="49"/>
@@ -2871,37 +3201,40 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>1731018</v>
+        <v>1958558.7581425176</v>
       </c>
       <c r="C50">
-        <v>1598896.815065275</v>
+        <v>1852421.2418574824</v>
       </c>
       <c r="D50">
-        <v>1412766.387245446</v>
+        <v>1711033.8677964006</v>
       </c>
       <c r="E50">
-        <v>1518879.7369044465</v>
+        <v>1511885.2310689539</v>
       </c>
       <c r="F50">
-        <v>1223258</v>
+        <v>1625369.0054464482</v>
       </c>
       <c r="G50">
-        <v>1345516.469406011</v>
+        <v>1309049.9945535518</v>
       </c>
       <c r="H50">
-        <v>1310060.0783477805</v>
+        <v>1439882.9412500495</v>
+      </c>
+      <c r="I50">
+        <v>1401939.8511401417</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2913,6 +3246,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2920,30 +3254,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2957,22 +3294,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>6459040668.054043</v>
+        <v>6446958584.386421</v>
       </c>
       <c r="C3">
-        <v>8219234986.054043</v>
+        <v>6912027220.386421</v>
       </c>
       <c r="D3">
-        <v>5575011707.661184</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E3">
-        <v>2995840305.261649</v>
-      </c>
-      <c r="G3">
-        <v>1510135077.3913946</v>
-      </c>
-      <c r="J3">
-        <v>2164444883.4405856</v>
+        <v>5966009660.717413</v>
+      </c>
+      <c r="F3">
+        <v>3205919970.075743</v>
+      </c>
+      <c r="H3">
+        <v>1616046913.1077275</v>
+      </c>
+      <c r="K3">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="4">
@@ -2994,11 +3334,14 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="D7">
-        <v>-1.0992357730865479</v>
-      </c>
-      <c r="G7">
-        <v>-813300957.0461059</v>
+      <c r="E7">
+        <v>-1.1763296127319336</v>
+      </c>
+      <c r="F7">
+        <v>0.029047369956970215</v>
+      </c>
+      <c r="H7">
+        <v>-870341018.3228749</v>
       </c>
     </row>
     <row r="8">
@@ -3006,22 +3349,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>6459040668.054043</v>
+        <v>6446958584.386421</v>
       </c>
       <c r="C8">
-        <v>8219234986.054043</v>
+        <v>6912027220.386421</v>
       </c>
       <c r="D8">
-        <v>5575011706.561949</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E8">
-        <v>2995840305.261649</v>
-      </c>
-      <c r="G8">
-        <v>696834120.3452888</v>
-      </c>
-      <c r="J8">
-        <v>2164444883.4405856</v>
+        <v>5966009659.541083</v>
+      </c>
+      <c r="F8">
+        <v>3205919970.1047907</v>
+      </c>
+      <c r="H8">
+        <v>745705894.7848526</v>
+      </c>
+      <c r="K8">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="9">
@@ -3049,22 +3395,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>6459040668.054043</v>
+        <v>6446958584.386421</v>
       </c>
       <c r="C13">
-        <v>8219234986.054043</v>
+        <v>6912027220.386421</v>
       </c>
       <c r="D13">
-        <v>5575011706.561949</v>
+        <v>8795682933.386421</v>
       </c>
       <c r="E13">
-        <v>2995840305.261649</v>
-      </c>
-      <c r="G13">
-        <v>696834120.3452888</v>
-      </c>
-      <c r="J13">
-        <v>2164444883.4405856</v>
+        <v>5966009659.541083</v>
+      </c>
+      <c r="F13">
+        <v>3205919970.1047907</v>
+      </c>
+      <c r="H13">
+        <v>745705894.7848526</v>
+      </c>
+      <c r="K13">
+        <v>2316246092.7125444</v>
       </c>
     </row>
     <row r="14"/>
@@ -3073,22 +3422,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-221284529.59233552</v>
+        <v>-246912911.5454499</v>
       </c>
       <c r="C15">
-        <v>-191338425.59233552</v>
+        <v>-236804304.5454499</v>
       </c>
       <c r="D15">
-        <v>-171451856.38451022</v>
+        <v>-204757757.5454499</v>
       </c>
       <c r="E15">
-        <v>-149717743.99687758</v>
-      </c>
-      <c r="G15">
-        <v>-96503877.9629696</v>
-      </c>
-      <c r="J15">
-        <v>-6417209.196505936</v>
+        <v>-183476463.40047598</v>
+      </c>
+      <c r="F15">
+        <v>-160216728.64289632</v>
+      </c>
+      <c r="H15">
+        <v>-103272082.35860462</v>
+      </c>
+      <c r="K15">
+        <v>-6867273.84062487</v>
       </c>
     </row>
     <row r="16">
@@ -3106,19 +3458,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>165889.3030419452</v>
+        <v>126463.57677432577</v>
       </c>
       <c r="C18">
-        <v>129855.30304194521</v>
+        <v>177523.57677432577</v>
       </c>
       <c r="D18">
-        <v>147520.75620780856</v>
+        <v>138962.57677432577</v>
       </c>
       <c r="E18">
-        <v>94589.25243521265</v>
-      </c>
-      <c r="G18">
-        <v>47712.098888120505</v>
+        <v>157866.97909220104</v>
+      </c>
+      <c r="F18">
+        <v>101223.26148887647</v>
+      </c>
+      <c r="H18">
+        <v>51058.33993289451</v>
       </c>
     </row>
     <row r="19">
@@ -3126,10 +3481,13 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-459681.45912910835</v>
+        <v>-731414.1713495377</v>
       </c>
       <c r="C19">
-        <v>-184756.45912910835</v>
+        <v>-491923.1713495377</v>
+      </c>
+      <c r="D19">
+        <v>-197714.1713495377</v>
       </c>
     </row>
     <row r="20">
@@ -3142,22 +3500,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>6237462346.30562</v>
+        <v>6199440722.246395</v>
       </c>
       <c r="C21">
-        <v>8027841659.30562</v>
+        <v>6674908516.246395</v>
       </c>
       <c r="D21">
-        <v>5403528981.978199</v>
+        <v>8590866424.246395</v>
       </c>
       <c r="E21">
-        <v>2846638094.9119816</v>
-      </c>
-      <c r="G21">
-        <v>600377954.4812074</v>
-      </c>
-      <c r="J21">
-        <v>2158027674.24408</v>
+        <v>5782500163.030628</v>
+      </c>
+      <c r="F21">
+        <v>3046254932.841691</v>
+      </c>
+      <c r="H21">
+        <v>642484870.766181</v>
+      </c>
+      <c r="K21">
+        <v>2309378818.87192</v>
       </c>
     </row>
     <row r="22"/>
@@ -3216,22 +3577,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>6237462346.30562</v>
+        <v>6199440722.246395</v>
       </c>
       <c r="C33">
-        <v>8027841659.30562</v>
+        <v>6674908516.246395</v>
       </c>
       <c r="D33">
-        <v>5403528981.978199</v>
+        <v>8590866424.246395</v>
       </c>
       <c r="E33">
-        <v>2846638094.9119816</v>
-      </c>
-      <c r="G33">
-        <v>600377954.4812074</v>
-      </c>
-      <c r="J33">
-        <v>2158027674.24408</v>
+        <v>5782500163.030628</v>
+      </c>
+      <c r="F33">
+        <v>3046254932.841691</v>
+      </c>
+      <c r="H33">
+        <v>642484870.766181</v>
+      </c>
+      <c r="K33">
+        <v>2309378818.87192</v>
       </c>
     </row>
     <row r="34"/>
@@ -3240,19 +3604,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>620337499.2086446</v>
+        <v>695177607.1845914</v>
       </c>
       <c r="C35">
-        <v>351175889.2086446</v>
+        <v>663846078.1845914</v>
       </c>
       <c r="D35">
-        <v>224954261.8515184</v>
+        <v>375805264.1845914</v>
       </c>
       <c r="E35">
-        <v>207766686.75188768</v>
-      </c>
-      <c r="G35">
-        <v>127478647.8300051</v>
+        <v>240731207.35897774</v>
+      </c>
+      <c r="F35">
+        <v>222337093.64300337</v>
+      </c>
+      <c r="H35">
+        <v>136419237.19081527</v>
       </c>
     </row>
     <row r="36">
@@ -3260,22 +3627,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-405941610.4353064</v>
+        <v>-356086947.79453427</v>
       </c>
       <c r="C36">
-        <v>-378524735.4353064</v>
+        <v>-434412110.79453427</v>
       </c>
       <c r="D36">
-        <v>-548753331.151721</v>
+        <v>-405072194.79453427</v>
       </c>
       <c r="E36">
-        <v>-339667752.4879875</v>
-      </c>
-      <c r="G36">
-        <v>-314609666.96748596</v>
-      </c>
-      <c r="J36">
-        <v>-36990.051823496164</v>
+        <v>-587239605.3452369</v>
+      </c>
+      <c r="F36">
+        <v>-363488025.11657536</v>
+      </c>
+      <c r="H36">
+        <v>-336674505.97525805</v>
+      </c>
+      <c r="K36">
+        <v>-39584.3126618287</v>
       </c>
     </row>
     <row r="37">
@@ -3283,22 +3653,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>360380573.7713632</v>
+        <v>351057642.5879416</v>
       </c>
       <c r="C37">
-        <v>382909133.7713632</v>
+        <v>385655357.5879416</v>
       </c>
       <c r="D37">
-        <v>284531521.325246</v>
+        <v>409764088.5879416</v>
       </c>
       <c r="E37">
-        <v>224653974.37473056</v>
-      </c>
-      <c r="G37">
-        <v>777260000.358579</v>
-      </c>
-      <c r="J37">
-        <v>-742452.794682281</v>
+        <v>304486859.22440493</v>
+      </c>
+      <c r="F37">
+        <v>240406814.3488915</v>
+      </c>
+      <c r="H37">
+        <v>831772364.6492331</v>
+      </c>
+      <c r="K37">
+        <v>-794523.9898983773</v>
       </c>
     </row>
     <row r="38">
@@ -3306,22 +3679,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>6812238808.850322</v>
+        <v>6889589024.224396</v>
       </c>
       <c r="C38">
-        <v>8383401946.850322</v>
+        <v>7289997841.224396</v>
       </c>
       <c r="D38">
-        <v>5364261434.0032425</v>
+        <v>8971363582.224396</v>
       </c>
       <c r="E38">
-        <v>2939391003.5506115</v>
-      </c>
-      <c r="G38">
-        <v>1190506935.7023053</v>
-      </c>
-      <c r="J38">
-        <v>2157248231.397574</v>
+        <v>5740478624.268774</v>
+      </c>
+      <c r="F38">
+        <v>3145510815.7170105</v>
+      </c>
+      <c r="H38">
+        <v>1274001966.630971</v>
+      </c>
+      <c r="K38">
+        <v>2308544710.5693593</v>
       </c>
     </row>
     <row r="39"/>
@@ -3330,22 +3706,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-3591601588.897002</v>
+        <v>-4379904183.449326</v>
       </c>
       <c r="C40">
-        <v>-3358852427.897002</v>
+        <v>-3843496601.4493256</v>
       </c>
       <c r="D40">
-        <v>-1647754582.6416316</v>
+        <v>-3594422233.4493256</v>
       </c>
       <c r="E40">
-        <v>-1327579374.5335789</v>
-      </c>
-      <c r="G40">
-        <v>-873079826.2689741</v>
-      </c>
-      <c r="J40">
-        <v>-432015906.28361166</v>
+        <v>-1763318226.7621527</v>
+      </c>
+      <c r="F40">
+        <v>-1420679125.4739094</v>
+      </c>
+      <c r="H40">
+        <v>-934312419.6385524</v>
+      </c>
+      <c r="K40">
+        <v>-462314916.2054199</v>
       </c>
     </row>
     <row r="41">
@@ -3353,10 +3732,13 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-32323518.85184711</v>
+        <v>-45308940.17242528</v>
       </c>
       <c r="C41">
-        <v>-2057094.8518471087</v>
+        <v>-34590701.17242528</v>
+      </c>
+      <c r="D41">
+        <v>-2201367.1724252747</v>
       </c>
     </row>
     <row r="42">
@@ -3364,16 +3746,19 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-3559278070.0451555</v>
+        <v>-4334595243.2769</v>
       </c>
       <c r="C42">
-        <v>-3356795333.0451555</v>
+        <v>-3808905900.2769003</v>
       </c>
       <c r="D42">
-        <v>-1648743635.161936</v>
-      </c>
-      <c r="G42">
-        <v>-873079826.2689741</v>
+        <v>-3592220866.2769003</v>
+      </c>
+      <c r="E42">
+        <v>-1764376645.5064552</v>
+      </c>
+      <c r="H42">
+        <v>-934312419.6385524</v>
       </c>
     </row>
     <row r="43">
@@ -3381,22 +3766,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>3220637219.9533195</v>
+        <v>2509684840.775069</v>
       </c>
       <c r="C43">
-        <v>5024549518.95332</v>
+        <v>3446501239.775069</v>
       </c>
       <c r="D43">
-        <v>3716506851.3616104</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E43">
-        <v>1611811629.017033</v>
-      </c>
-      <c r="G43">
-        <v>317427109.4333314</v>
-      </c>
-      <c r="J43">
-        <v>1725232325.1139624</v>
+        <v>3977160397.506621</v>
+      </c>
+      <c r="F43">
+        <v>1724831690.2431011</v>
+      </c>
+      <c r="H43">
+        <v>339689546.9924187</v>
+      </c>
+      <c r="K43">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="44">
@@ -3410,22 +3798,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>3220637219.9533195</v>
+        <v>2509684840.775069</v>
       </c>
       <c r="C46">
-        <v>5024549518.95332</v>
+        <v>3446501239.775069</v>
       </c>
       <c r="D46">
-        <v>3716506851.3616104</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E46">
-        <v>1611811629.017033</v>
-      </c>
-      <c r="G46">
-        <v>317427109.4333314</v>
-      </c>
-      <c r="J46">
-        <v>1725232325.1139624</v>
+        <v>3977160397.506621</v>
+      </c>
+      <c r="F46">
+        <v>1724831690.2431011</v>
+      </c>
+      <c r="H46">
+        <v>339689546.9924187</v>
+      </c>
+      <c r="K46">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="47">
@@ -3441,7 +3832,10 @@
       <c r="D47">
         <v>0</v>
       </c>
-      <c r="G47">
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -3450,22 +3844,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>3220637219.9533195</v>
+        <v>2509684840.775069</v>
       </c>
       <c r="C48">
-        <v>5024549518.95332</v>
+        <v>3446501239.775069</v>
       </c>
       <c r="D48">
-        <v>3716506851.3616104</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E48">
-        <v>1611811629.017033</v>
-      </c>
-      <c r="G48">
-        <v>317427109.4333314</v>
-      </c>
-      <c r="J48">
-        <v>1725232325.1139624</v>
+        <v>3977160397.506621</v>
+      </c>
+      <c r="F48">
+        <v>1724831690.2431011</v>
+      </c>
+      <c r="H48">
+        <v>339689546.9924187</v>
+      </c>
+      <c r="K48">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="49"/>
@@ -3474,31 +3871,34 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>6261560.939215167</v>
+        <v>7033899.098865354</v>
       </c>
       <c r="C50">
-        <v>5753800.939215167</v>
+        <v>6700709.346169285</v>
       </c>
       <c r="D50">
-        <v>5500420.593555903</v>
+        <v>6157338.098865354</v>
       </c>
       <c r="E50">
-        <v>5397714.3329448905</v>
-      </c>
-      <c r="G50">
-        <v>4255217.591726501</v>
+        <v>5886187.172319003</v>
+      </c>
+      <c r="F50">
+        <v>5776241.792390191</v>
+      </c>
+      <c r="H50">
+        <v>4553653.08485516</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3510,6 +3910,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3517,30 +3918,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3554,31 +3958,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-647223053</v>
+        <v>-127256692</v>
       </c>
       <c r="C3">
-        <v>-756993173.2789545</v>
+        <v>-692615404.1131005</v>
       </c>
       <c r="D3">
-        <v>165475116.17419118</v>
+        <v>-810084143.6212894</v>
       </c>
       <c r="E3">
-        <v>74418170.89391062</v>
+        <v>177080550.40439</v>
       </c>
       <c r="F3">
-        <v>26741870</v>
+        <v>86389493</v>
       </c>
       <c r="G3">
-        <v>105488105.35862738</v>
+        <v>28617384.703678038</v>
       </c>
       <c r="H3">
-        <v>-91964140.11664815</v>
+        <v>112886409.6904951</v>
       </c>
       <c r="I3">
-        <v>30323253.909660075</v>
+        <v>-98413954.47143638</v>
       </c>
       <c r="J3">
-        <v>-15710950.149595967</v>
+        <v>32449945.445103556</v>
+      </c>
+      <c r="K3">
+        <v>-16812822.15833432</v>
       </c>
     </row>
     <row r="4">
@@ -3586,31 +3993,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-504124534</v>
+        <v>-999420067</v>
       </c>
       <c r="C4">
-        <v>5024549518.95332</v>
+        <v>-539480811.4780462</v>
       </c>
       <c r="D4">
-        <v>3917840956.5457025</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E4">
-        <v>1745444192.8693335</v>
+        <v>4192614871.7832494</v>
       </c>
       <c r="F4">
-        <v>1299787765</v>
+        <v>1867836441</v>
       </c>
       <c r="G4">
-        <v>317427109.4333314</v>
+        <v>1390947099.217028</v>
       </c>
       <c r="H4">
-        <v>518761214.6174233</v>
+        <v>339689546.9924187</v>
       </c>
       <c r="I4">
-        <v>451059672.07739043</v>
+        <v>555144021.269047</v>
       </c>
       <c r="J4">
-        <v>1725232325.1139624</v>
+        <v>482694297.74931765</v>
+      </c>
+      <c r="K4">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="5">
@@ -3618,22 +4028,28 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>374639972</v>
+        <v>746830884</v>
       </c>
       <c r="C5">
-        <v>-3899506839.074337</v>
+        <v>400914977.3033512</v>
       </c>
       <c r="D5">
-        <v>-3817105708.7927785</v>
+        <v>-4172994909.0476403</v>
+      </c>
+      <c r="E5">
+        <v>-4084814656.6836414</v>
       </c>
       <c r="F5">
-        <v>-1250997908</v>
+        <v>-1789350102</v>
       </c>
       <c r="G5">
-        <v>-449695554.38085645</v>
+        <v>-1338735413.6689928</v>
       </c>
       <c r="H5">
-        <v>-623996829.7335783</v>
+        <v>-481234509.0022028</v>
+      </c>
+      <c r="I5">
+        <v>-667760232.5626926</v>
       </c>
     </row>
     <row r="6">
@@ -3641,28 +4057,31 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>1731018</v>
+        <v>3810980</v>
       </c>
       <c r="C6">
-        <v>5753800.939215167</v>
+        <v>1852421.2418574824</v>
       </c>
       <c r="D6">
-        <v>4154904.1241498925</v>
+        <v>6157338.098865354</v>
       </c>
       <c r="E6">
-        <v>2742137.7369044465</v>
+        <v>4446304.231068954</v>
       </c>
       <c r="F6">
-        <v>1223258</v>
+        <v>2934419</v>
       </c>
       <c r="G6">
-        <v>4255217.591726501</v>
+        <v>1309049.9945535518</v>
       </c>
       <c r="H6">
-        <v>2909701.1223204895</v>
+        <v>4553653.08485516</v>
       </c>
       <c r="I6">
-        <v>1599641.043972709</v>
+        <v>3113770.1436051102</v>
+      </c>
+      <c r="J6">
+        <v>1711830.2924649685</v>
       </c>
     </row>
     <row r="7">
@@ -3675,31 +4094,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1044274</v>
+        <v>2149432</v>
       </c>
       <c r="C8">
-        <v>1661311.558185135</v>
+        <v>1117513.1280665367</v>
       </c>
       <c r="D8">
-        <v>1541678.86804545</v>
+        <v>1777826.0074277082</v>
       </c>
       <c r="E8">
-        <v>1015446.8583569857</v>
+        <v>1649802.9964391994</v>
       </c>
       <c r="F8">
-        <v>1351728</v>
+        <v>1086651</v>
       </c>
       <c r="G8">
-        <v>1819353.0714056012</v>
+        <v>1446530.111422025</v>
       </c>
       <c r="H8">
-        <v>2296986.3226103433</v>
+        <v>1946951.606459545</v>
       </c>
       <c r="I8">
-        <v>2209847.8912702696</v>
+        <v>2458083.195125356</v>
       </c>
       <c r="J8">
-        <v>9233.007295261752</v>
+        <v>2364833.395760767</v>
+      </c>
+      <c r="K8">
+        <v>9880.555164630274</v>
       </c>
     </row>
     <row r="9">
@@ -3722,28 +4144,31 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-219851343</v>
+        <v>-296134613</v>
       </c>
       <c r="C12">
-        <v>18207786.68160746</v>
+        <v>-235270400.32171547</v>
       </c>
       <c r="D12">
-        <v>125996060.43675198</v>
+        <v>19484771.860384706</v>
       </c>
       <c r="E12">
-        <v>61095345.05629642</v>
+        <v>134832669.99153012</v>
       </c>
       <c r="F12">
-        <v>20272819</v>
+        <v>65379410</v>
       </c>
       <c r="G12">
-        <v>179801257.57448626</v>
+        <v>21694633.18575079</v>
       </c>
       <c r="H12">
-        <v>-7362005.532742143</v>
+        <v>192411441.61624366</v>
       </c>
       <c r="I12">
-        <v>123134514.80873007</v>
+        <v>-7878332.53699491</v>
+      </c>
+      <c r="J12">
+        <v>131770432.6803686</v>
       </c>
     </row>
     <row r="13">
@@ -3775,26 +4200,29 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>-8011405785.400775</v>
+      <c r="B18">
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>-5047061527.184122</v>
+        <v>-8573277836.5195055</v>
       </c>
       <c r="E18">
-        <v>-2244473427.8246393</v>
+        <v>-5401032214.522052</v>
       </c>
       <c r="F18">
-        <v>-1793498952</v>
+        <v>-2401858093</v>
       </c>
       <c r="G18">
-        <v>-625627417.7373779</v>
+        <v>-1919284233.8635027</v>
       </c>
       <c r="H18">
-        <v>-264098025.0559809</v>
-      </c>
-      <c r="J18">
-        <v>-2149829478.5554614</v>
+        <v>-669505180.2495198</v>
+      </c>
+      <c r="I18">
+        <v>-282620279.8274244</v>
+      </c>
+      <c r="K18">
+        <v>-2300605650.8063645</v>
       </c>
     </row>
     <row r="19">
@@ -3807,45 +4235,45 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>854301392</v>
+        <v>1501205897</v>
       </c>
       <c r="C20">
-        <v>3358852427.897002</v>
+        <v>914216978.3845204</v>
       </c>
       <c r="D20">
-        <v>1336135853.1901567</v>
+        <v>3594422233.4493256</v>
       </c>
       <c r="E20">
-        <v>668825267.4739174</v>
+        <v>1429844424.7586198</v>
       </c>
       <c r="F20">
-        <v>621552231</v>
+        <v>715723947</v>
       </c>
       <c r="G20">
-        <v>873079826.2689741</v>
+        <v>665144184.3055986</v>
       </c>
       <c r="H20">
-        <v>561461094.5208035</v>
+        <v>934312419.6385524</v>
       </c>
       <c r="I20">
-        <v>214325718.10083106</v>
+        <v>600838615.1772472</v>
       </c>
       <c r="J20">
-        <v>432015906.28361166</v>
+        <v>229357241.16464308</v>
+      </c>
+      <c r="K20">
+        <v>462314916.2054199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="E21">
-        <v>-167616081.10249442</v>
-      </c>
-      <c r="I21">
-        <v>-900807675.657905</v>
-      </c>
       <c r="J21">
-        <v>-165111774.47341618</v>
+        <v>-963984934.4241183</v>
+      </c>
+      <c r="K21">
+        <v>-176691726.09143183</v>
       </c>
     </row>
     <row r="22">
@@ -3883,31 +4311,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-511794505</v>
+        <v>140172816</v>
       </c>
       <c r="C28">
-        <v>-1879657549.5137782</v>
+        <v>-547688708.3369067</v>
       </c>
       <c r="D28">
-        <v>65075066.57851284</v>
+        <v>-2011485479.7218196</v>
       </c>
       <c r="E28">
-        <v>67032881.06767513</v>
+        <v>69639042.2545156</v>
       </c>
       <c r="F28">
-        <v>-22047987</v>
+        <v>8288775</v>
       </c>
       <c r="G28">
-        <v>239808869.3263382</v>
+        <v>-23594300.844357267</v>
       </c>
       <c r="H28">
-        <v>16312845.69150219</v>
+        <v>256627628.09279516</v>
       </c>
       <c r="I28">
-        <v>-108478281.73571038</v>
+        <v>17456931.05102429</v>
       </c>
       <c r="J28">
-        <v>-157683788.62400827</v>
+        <v>-116086299.1415632</v>
+      </c>
+      <c r="K28">
+        <v>-168742785.77327222</v>
       </c>
     </row>
     <row r="29">
@@ -3935,31 +4366,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-152962568</v>
+        <v>1608884447</v>
       </c>
       <c r="C33">
-        <v>-2358459809.4081626</v>
+        <v>-163690446.99261913</v>
       </c>
       <c r="D33">
-        <v>-218292538.17603838</v>
+        <v>-2523868064.349897</v>
       </c>
       <c r="E33">
-        <v>-16914023.715768937</v>
+        <v>-233602270.25731614</v>
       </c>
       <c r="F33">
-        <v>195268902</v>
+        <v>-18100052</v>
       </c>
       <c r="G33">
-        <v>-710919532.3840551</v>
+        <v>208963894.04326645</v>
       </c>
       <c r="H33">
-        <v>-577646559.7220199</v>
+        <v>-760779173.3185974</v>
       </c>
       <c r="I33">
-        <v>-590468428.2557588</v>
+        <v>-618159232.0328075</v>
       </c>
       <c r="J33">
-        <v>-14615404.88512437</v>
+        <v>-631880349.6827695</v>
+      </c>
+      <c r="K33">
+        <v>-15640441.906180063</v>
       </c>
     </row>
     <row r="34">
@@ -3992,31 +4426,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-23859736</v>
+        <v>-16319417</v>
       </c>
       <c r="C39">
-        <v>891071.1500311622</v>
+        <v>-25533115.07535547</v>
       </c>
       <c r="D39">
-        <v>-6029849.628280896</v>
+        <v>953565.5471659453</v>
       </c>
       <c r="E39">
-        <v>-13530917.254874418</v>
+        <v>-6452747.190747857</v>
       </c>
       <c r="F39">
-        <v>-20533305</v>
+        <v>-14479718</v>
       </c>
       <c r="G39">
-        <v>-896785.6416942005</v>
+        <v>-21973388.114703864</v>
       </c>
       <c r="H39">
-        <v>-31578.41877275616</v>
+        <v>-959680.8190712805</v>
       </c>
       <c r="I39">
-        <v>-43637.96521900152</v>
+        <v>-33793.1400591586</v>
       </c>
       <c r="J39">
-        <v>-5702.267776014711</v>
+        <v>-46698.4709131369</v>
+      </c>
+      <c r="K39">
+        <v>-6102.190708039474</v>
       </c>
     </row>
     <row r="40">
@@ -4034,31 +4471,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>3401216</v>
+        <v>3702459</v>
       </c>
       <c r="C42">
-        <v>1052482.155543603</v>
+        <v>3639756.9329409273</v>
       </c>
       <c r="D42">
-        <v>3238260.6803832245</v>
+        <v>1126296.9545116925</v>
       </c>
       <c r="E42">
-        <v>1137470.9444761937</v>
+        <v>3465372.9025427513</v>
       </c>
       <c r="F42">
-        <v>1462717</v>
+        <v>1217232</v>
       </c>
       <c r="G42">
-        <v>1297609.9687296343</v>
+        <v>1565303.2155795323</v>
       </c>
       <c r="H42">
-        <v>1995633.4228829716</v>
+        <v>1388616.5653510233</v>
       </c>
       <c r="I42">
-        <v>2575530.039946746</v>
+        <v>2135595.2066987013</v>
       </c>
       <c r="J42">
-        <v>133903.9135295977</v>
+        <v>2756162.301627945</v>
+      </c>
+      <c r="K42">
+        <v>143295.13256943272</v>
       </c>
     </row>
     <row r="43">
@@ -4071,31 +4511,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-352018284</v>
+        <v>-1433380893</v>
       </c>
       <c r="C44">
-        <v>501351156.5097684</v>
+        <v>-376706739.5046267</v>
       </c>
       <c r="D44">
-        <v>314565262.3706203</v>
+        <v>536512925.89014685</v>
       </c>
       <c r="E44">
-        <v>71659228.81213345</v>
+        <v>336626987.1057431</v>
       </c>
       <c r="F44">
-        <v>-162668502</v>
+        <v>76684044</v>
       </c>
       <c r="G44">
-        <v>960093298.102969</v>
+        <v>-174077097.11044964</v>
       </c>
       <c r="H44">
-        <v>599552898.918461</v>
+        <v>1027428495.5852267</v>
       </c>
       <c r="I44">
-        <v>735863645.8783336</v>
+        <v>641601950.7444688</v>
       </c>
       <c r="J44">
-        <v>156516448.36391386</v>
+        <v>787472717.6353551</v>
+      </c>
+      <c r="K44">
+        <v>167493575.2542168</v>
       </c>
     </row>
     <row r="45">
@@ -4118,31 +4561,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>13644867</v>
+        <v>-22713780</v>
       </c>
       <c r="C48">
-        <v>-24492449.920958944</v>
+        <v>14601836.302753743</v>
       </c>
       <c r="D48">
-        <v>-28406068.668171372</v>
+        <v>-26210203.763747666</v>
       </c>
       <c r="E48">
-        <v>-34606116.25248949</v>
+        <v>-30398300.3057062</v>
       </c>
       <c r="F48">
-        <v>-35577799</v>
+        <v>-37032731</v>
       </c>
       <c r="G48">
-        <v>-9765720.719611142</v>
+        <v>-38073012.87804973</v>
       </c>
       <c r="H48">
-        <v>-7557548.509049008</v>
+        <v>-10450629.920113724</v>
       </c>
       <c r="I48">
-        <v>-7073255.165862645</v>
+        <v>-8087589.727276508</v>
       </c>
       <c r="J48">
-        <v>-56406.65013074003</v>
+        <v>-7569330.947640136</v>
+      </c>
+      <c r="K48">
+        <v>-60362.6749601714</v>
       </c>
     </row>
     <row r="49">
@@ -4150,22 +4596,28 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-641279067</v>
+        <v>-112416367</v>
       </c>
       <c r="C49">
-        <v>-754614869.6347958</v>
+        <v>-686254542.5116016</v>
       </c>
       <c r="D49">
-        <v>165810314.33143663</v>
+        <v>-807539039.9943908</v>
+      </c>
+      <c r="E49">
+        <v>177439257.35412303</v>
       </c>
       <c r="F49">
-        <v>26741870</v>
+        <v>86775114</v>
       </c>
       <c r="G49">
-        <v>107540424.3788131</v>
+        <v>28617384.703678038</v>
       </c>
       <c r="H49">
-        <v>-88922769.42465298</v>
+        <v>115082666.08301106</v>
+      </c>
+      <c r="I49">
+        <v>-95159280.24262153</v>
       </c>
     </row>
     <row r="50">
@@ -4193,22 +4645,28 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-5943986</v>
+        <v>-14569344</v>
       </c>
       <c r="C54">
-        <v>-2057094.8518471087</v>
+        <v>-6360861.601498938</v>
       </c>
       <c r="D54">
+        <v>-2201367.1724252747</v>
+      </c>
+      <c r="E54">
         <v>0</v>
       </c>
-      <c r="G54">
-        <v>-2052319.020185721</v>
+      <c r="F54">
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>-3041370.691995177</v>
+        <v>-2196256.3925159443</v>
       </c>
       <c r="I54">
-        <v>-2052318.8860694023</v>
+        <v>-3254674.2288148683</v>
+      </c>
+      <c r="J54">
+        <v>-2196256.2489935094</v>
       </c>
     </row>
     <row r="55">
@@ -4250,16 +4708,19 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-321208.7923116108</v>
+      <c r="B62">
+        <v>-270981</v>
       </c>
       <c r="D62">
-        <v>-335198.1572454428</v>
+        <v>-343736.4544732731</v>
       </c>
       <c r="E62">
-        <v>-360352.7072413055</v>
-      </c>
-      <c r="H62">
+        <v>-358706.9497330142</v>
+      </c>
+      <c r="F62">
+        <v>-385621</v>
+      </c>
+      <c r="I62">
         <v>0</v>
       </c>
     </row>
@@ -4284,28 +4745,31 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-804217403</v>
+        <v>-1395942155</v>
       </c>
       <c r="C67">
-        <v>-1921578.9778221732</v>
+        <v>-860620398.1637738</v>
       </c>
       <c r="D67">
-        <v>-5531187.593183694</v>
+        <v>-2056347.026099429</v>
       </c>
       <c r="E67">
-        <v>-2059155.6816839443</v>
+        <v>-5919111.985150956</v>
       </c>
       <c r="F67">
-        <v>-1597561</v>
+        <v>-2203546</v>
       </c>
       <c r="G67">
-        <v>-7280105.018358676</v>
+        <v>-1709604.3666577016</v>
       </c>
       <c r="H67">
-        <v>-26949181.51201882</v>
+        <v>-7790688.010731759</v>
       </c>
       <c r="I67">
-        <v>-27313025.63963003</v>
+        <v>-28839235.804328207</v>
+      </c>
+      <c r="J67">
+        <v>-29228597.78133371</v>
       </c>
     </row>
     <row r="68">
@@ -4327,10 +4791,10 @@
       <c r="A71" t="str">
         <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
-      <c r="B71">
-        <v>-800000000</v>
-      </c>
-      <c r="F71">
+      <c r="C71">
+        <v>-856107211.7597771</v>
+      </c>
+      <c r="G71">
         <v>0</v>
       </c>
     </row>
@@ -4358,6 +4822,12 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B76">
+        <v>-800000000</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4369,31 +4839,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-4217403</v>
+        <v>-6895803</v>
       </c>
       <c r="C78">
-        <v>-10289126.55999226</v>
+        <v>-4513186.403996649</v>
       </c>
       <c r="D78">
-        <v>-5531187.593183694</v>
+        <v>-11010744.31339805</v>
       </c>
       <c r="E78">
-        <v>-2059155.6816839443</v>
+        <v>-5919111.985150956</v>
       </c>
       <c r="F78">
-        <v>-1597561</v>
+        <v>-2203546</v>
       </c>
       <c r="G78">
-        <v>-27525369.328074176</v>
+        <v>-1709604.3666577016</v>
       </c>
       <c r="H78">
-        <v>-26949181.51201882</v>
+        <v>-29455833.98514459</v>
       </c>
       <c r="I78">
-        <v>-27313025.63963003</v>
+        <v>-28839235.804328207</v>
       </c>
       <c r="J78">
-        <v>14615404.88512437</v>
+        <v>-29228597.78133371</v>
+      </c>
+      <c r="K78">
+        <v>15640441.906180063</v>
       </c>
     </row>
     <row r="79">
@@ -4405,6 +4878,12 @@
       <c r="A80" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B80">
+        <v>-589046352</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4465,11 +4944,11 @@
       <c r="A92" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="C92">
-        <v>8367547.582170086</v>
-      </c>
-      <c r="G92">
-        <v>20245264.3097155</v>
+      <c r="D92">
+        <v>8954397.287298622</v>
+      </c>
+      <c r="H92">
+        <v>21665145.97441283</v>
       </c>
     </row>
     <row r="93">
@@ -4501,8 +4980,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="J98">
-        <v>14615404.88512437</v>
+      <c r="K98">
+        <v>15640441.906180063</v>
       </c>
     </row>
     <row r="99">
@@ -4516,31 +4995,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>201372616</v>
+        <v>272230406</v>
       </c>
       <c r="C101">
-        <v>2110192120.1942418</v>
+        <v>215495686.01066536</v>
       </c>
       <c r="D101">
-        <v>-181045660.5993906</v>
+        <v>2258188365.371181</v>
       </c>
       <c r="E101">
-        <v>-98008985.99778429</v>
+        <v>-193743119.62118903</v>
       </c>
       <c r="F101">
-        <v>-40024019</v>
+        <v>-104881471</v>
       </c>
       <c r="G101">
-        <v>-85019226.48664293</v>
+        <v>-42831064.13688793</v>
       </c>
       <c r="H101">
-        <v>118472257.27895415</v>
+        <v>-90981966.16681609</v>
       </c>
       <c r="I101">
-        <v>11238134.020631064</v>
+        <v>126781192.31246549</v>
       </c>
       <c r="J101">
-        <v>2079585.8244475876</v>
+        <v>12026309.477231441</v>
+      </c>
+      <c r="K101">
+        <v>2225435.527228727</v>
       </c>
     </row>
     <row r="102">
@@ -4557,8 +5039,8 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
-        <v>2200844083.58875</v>
+      <c r="D104">
+        <v>2355198114.898958</v>
       </c>
     </row>
     <row r="105">
@@ -4575,8 +5057,8 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="J107">
-        <v>2079585.8244475876</v>
+      <c r="K107">
+        <v>2225435.527228727</v>
       </c>
     </row>
     <row r="108">
@@ -4588,8 +5070,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="G109">
-        <v>94782031.08784331</v>
+      <c r="H109">
+        <v>101429475.44942756</v>
       </c>
     </row>
     <row r="110">
@@ -4597,25 +5079,28 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-18478727</v>
+        <v>-23904207</v>
       </c>
       <c r="C110">
-        <v>-72444176.7129006</v>
+        <v>-19774714.31105014</v>
       </c>
       <c r="D110">
-        <v>-55049600.16263861</v>
+        <v>-77524977.66739237</v>
       </c>
       <c r="E110">
-        <v>-36913640.94148785</v>
+        <v>-58910449.62965889</v>
       </c>
       <c r="F110">
-        <v>-19751200</v>
-      </c>
-      <c r="H110">
-        <v>113009452.65458746</v>
+        <v>-39502061</v>
+      </c>
+      <c r="G110">
+        <v>-21136430.951137137</v>
       </c>
       <c r="I110">
-        <v>134372648.8293611</v>
+        <v>120935259.26827176</v>
+      </c>
+      <c r="J110">
+        <v>143796742.15760002</v>
       </c>
     </row>
     <row r="111">
@@ -4658,28 +5143,31 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-96739663</v>
+        <v>-113888821</v>
       </c>
       <c r="C118">
-        <v>-362609062.94185615</v>
+        <v>-103524403.94688809</v>
       </c>
       <c r="D118">
-        <v>-261800610.3996056</v>
+        <v>-388040292.2924725</v>
       </c>
       <c r="E118">
-        <v>-145665603.13638785</v>
+        <v>-280161738.25776756</v>
       </c>
       <c r="F118">
-        <v>-67641965</v>
+        <v>-155879817</v>
       </c>
       <c r="G118">
-        <v>-307195588.86680496</v>
+        <v>-72385967.56762804</v>
       </c>
       <c r="H118">
-        <v>-33033745.324119005</v>
+        <v>-328740448.812079</v>
       </c>
       <c r="I118">
-        <v>-127581698.5094998</v>
+        <v>-35350534.50426762</v>
+      </c>
+      <c r="J118">
+        <v>-136529515.22818047</v>
       </c>
     </row>
     <row r="119">
@@ -4687,28 +5175,31 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>316591006</v>
+        <v>410023434</v>
       </c>
       <c r="C119">
-        <v>344401276.26024866</v>
+        <v>338794804.26860356</v>
       </c>
       <c r="D119">
-        <v>135804549.96285364</v>
+        <v>368555520.4320877</v>
       </c>
       <c r="E119">
-        <v>84570258.08009143</v>
+        <v>145329068.26623747</v>
       </c>
       <c r="F119">
-        <v>47369146</v>
+        <v>90500407</v>
       </c>
       <c r="G119">
-        <v>127394331.29231873</v>
+        <v>50691334.38187724</v>
       </c>
       <c r="H119">
-        <v>38496549.948485695</v>
+        <v>136329007.19583538</v>
       </c>
       <c r="I119">
-        <v>4447183.700769754</v>
+        <v>41196467.54846135</v>
+      </c>
+      <c r="J119">
+        <v>4759082.547811901</v>
       </c>
     </row>
     <row r="120">
@@ -4741,22 +5232,28 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-1250067840</v>
+        <v>-1250968441</v>
       </c>
       <c r="C125">
-        <v>1351277367.937465</v>
+        <v>-1337740116.266209</v>
       </c>
       <c r="D125">
-        <v>-21101732.018383116</v>
+        <v>1446047874.7237918</v>
+      </c>
+      <c r="E125">
+        <v>-22581681.201949976</v>
       </c>
       <c r="F125">
-        <v>-14879710</v>
+        <v>-20695524</v>
       </c>
       <c r="G125">
-        <v>13188773.853625774</v>
+        <v>-15923283.79986759</v>
       </c>
       <c r="H125">
-        <v>-441064.3497128195</v>
+        <v>14113755.512947265</v>
+      </c>
+      <c r="I125">
+        <v>-471997.96329910145</v>
       </c>
     </row>
     <row r="126">
@@ -4769,31 +5266,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-1250067840</v>
+        <v>-1250968441</v>
       </c>
       <c r="C127">
-        <v>1351277367.937465</v>
+        <v>-1337740116.266209</v>
       </c>
       <c r="D127">
-        <v>-21101732.018383116</v>
+        <v>1446047874.7237918</v>
       </c>
       <c r="E127">
-        <v>-25649970.785557617</v>
+        <v>-22581681.201949976</v>
       </c>
       <c r="F127">
-        <v>-14879710</v>
+        <v>-20695524</v>
       </c>
       <c r="G127">
-        <v>13188773.853625774</v>
+        <v>-15923283.79986759</v>
       </c>
       <c r="H127">
-        <v>-441064.3497128195</v>
+        <v>14113755.512947265</v>
       </c>
       <c r="I127">
-        <v>14248362.290661106</v>
+        <v>-471997.96329910145</v>
       </c>
       <c r="J127">
-        <v>984040.5599759909</v>
+        <v>15247657.141001288</v>
+      </c>
+      <c r="K127">
+        <v>1053055.2750744692</v>
       </c>
     </row>
     <row r="128">
@@ -4801,22 +5301,28 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>1377215924</v>
+        <v>1473814918</v>
       </c>
       <c r="C128">
-        <v>19836178.01399027</v>
+        <v>1473805605.8585064</v>
       </c>
       <c r="D128">
-        <v>25964035.67125403</v>
+        <v>21227368.814409755</v>
+      </c>
+      <c r="E128">
+        <v>27784997.730685852</v>
       </c>
       <c r="F128">
-        <v>25963556</v>
+        <v>27784658</v>
       </c>
       <c r="G128">
-        <v>751792.9330453317</v>
+        <v>27784484.41816104</v>
       </c>
       <c r="H128">
-        <v>984041.13008951</v>
+        <v>804519.1896626797</v>
+      </c>
+      <c r="I128">
+        <v>1053055.8851723382</v>
       </c>
     </row>
     <row r="129">
@@ -4824,34 +5330,40 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1490769</v>
+        <v>589008</v>
       </c>
       <c r="C129">
-        <v>1377241403.4515393</v>
+        <v>1595322.6149598889</v>
       </c>
       <c r="D129">
-        <v>4862303.652870915</v>
+        <v>1473832872.2862744</v>
+      </c>
+      <c r="E129">
+        <v>5203316.528735872</v>
       </c>
       <c r="F129">
-        <v>4960175</v>
+        <v>336087</v>
       </c>
       <c r="G129">
-        <v>19836178.01399027</v>
+        <v>5308051.98636319</v>
       </c>
       <c r="H129">
-        <v>542976.7803766906</v>
+        <v>21227368.814409755</v>
+      </c>
+      <c r="I129">
+        <v>581057.9218732368</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4863,6 +5375,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4870,30 +5383,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4907,25 +5423,28 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-647223053</v>
+        <v>565358712.1131005</v>
       </c>
       <c r="C3">
-        <v>-922468289.4531457</v>
+        <v>-692615404.1131005</v>
       </c>
       <c r="D3">
-        <v>91056945.28028056</v>
+        <v>-987164694.0256793</v>
       </c>
       <c r="E3">
-        <v>47676300.89391062</v>
+        <v>90691057.40439</v>
       </c>
       <c r="F3">
-        <v>26741870</v>
+        <v>57772108.29632196</v>
       </c>
       <c r="G3">
-        <v>197452245.47527552</v>
+        <v>28617384.703678038</v>
       </c>
       <c r="H3">
-        <v>-122287394.02630822</v>
+        <v>211300364.16193148</v>
+      </c>
+      <c r="I3">
+        <v>-130863899.91653994</v>
       </c>
     </row>
     <row r="4">
@@ -4933,25 +5452,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-504124534</v>
+        <v>-459939255.5219538</v>
       </c>
       <c r="C4">
-        <v>1106708562.407617</v>
+        <v>-539480811.4780462</v>
       </c>
       <c r="D4">
-        <v>2172396763.6763687</v>
+        <v>1184326476.9918199</v>
       </c>
       <c r="E4">
-        <v>445656427.8693335</v>
+        <v>2324778430.7832494</v>
       </c>
       <c r="F4">
-        <v>1299787765</v>
+        <v>476889341.7829721</v>
       </c>
       <c r="G4">
-        <v>-201334105.18409193</v>
+        <v>1390947099.217028</v>
       </c>
       <c r="H4">
-        <v>67701542.54003286</v>
+        <v>-215454474.27662832</v>
+      </c>
+      <c r="I4">
+        <v>72449723.51972938</v>
       </c>
     </row>
     <row r="5">
@@ -4959,16 +5481,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>374639972</v>
+        <v>345915906.6966488</v>
       </c>
       <c r="C5">
-        <v>-82401130.28155851</v>
+        <v>400914977.3033512</v>
+      </c>
+      <c r="D5">
+        <v>-88180252.36399889</v>
+      </c>
+      <c r="E5">
+        <v>-2295464554.6836414</v>
       </c>
       <c r="F5">
-        <v>-1250997908</v>
+        <v>-450614688.33100724</v>
       </c>
       <c r="G5">
-        <v>174301275.35272187</v>
+        <v>-1338735413.6689928</v>
+      </c>
+      <c r="H5">
+        <v>186525723.56048983</v>
       </c>
     </row>
     <row r="6">
@@ -4976,25 +5507,28 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>1731018</v>
+        <v>1958558.7581425176</v>
       </c>
       <c r="C6">
-        <v>1598896.815065275</v>
+        <v>1852421.2418574824</v>
       </c>
       <c r="D6">
-        <v>1412766.387245446</v>
+        <v>1711033.8677964006</v>
       </c>
       <c r="E6">
-        <v>1518879.7369044465</v>
+        <v>1511885.2310689539</v>
       </c>
       <c r="F6">
-        <v>1223258</v>
+        <v>1625369.0054464482</v>
       </c>
       <c r="G6">
-        <v>1345516.469406011</v>
+        <v>1309049.9945535518</v>
       </c>
       <c r="H6">
-        <v>1310060.0783477805</v>
+        <v>1439882.9412500495</v>
+      </c>
+      <c r="I6">
+        <v>1401939.8511401417</v>
       </c>
     </row>
     <row r="7">
@@ -5007,25 +5541,28 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1044274</v>
+        <v>1031918.8719334633</v>
       </c>
       <c r="C8">
-        <v>119632.69013968506</v>
+        <v>1117513.1280665367</v>
       </c>
       <c r="D8">
-        <v>526232.0096884642</v>
+        <v>128023.01098850882</v>
       </c>
       <c r="E8">
-        <v>-336281.14164301427</v>
+        <v>563151.9964391994</v>
       </c>
       <c r="F8">
-        <v>1351728</v>
+        <v>-359879.1114220249</v>
       </c>
       <c r="G8">
-        <v>-477633.2512047421</v>
+        <v>1446530.111422025</v>
       </c>
       <c r="H8">
-        <v>87138.4313400737</v>
+        <v>-511131.5886658109</v>
+      </c>
+      <c r="I8">
+        <v>93249.79936458869</v>
       </c>
     </row>
     <row r="9">
@@ -5048,25 +5585,28 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-219851343</v>
+        <v>-60864212.678284526</v>
       </c>
       <c r="C12">
-        <v>-107788273.75514452</v>
+        <v>-235270400.32171547</v>
       </c>
       <c r="D12">
-        <v>64900715.38045555</v>
+        <v>-115347898.13114542</v>
       </c>
       <c r="E12">
-        <v>40822526.05629642</v>
+        <v>69453259.99153012</v>
       </c>
       <c r="F12">
-        <v>20272819</v>
+        <v>43684776.81424921</v>
       </c>
       <c r="G12">
-        <v>187163263.1072284</v>
+        <v>21694633.18575079</v>
       </c>
       <c r="H12">
-        <v>-130496520.34147221</v>
+        <v>200289774.15323856</v>
+      </c>
+      <c r="I12">
+        <v>-139648765.2173635</v>
       </c>
     </row>
     <row r="13">
@@ -5098,20 +5638,20 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>-2964344258.216653</v>
-      </c>
       <c r="D18">
-        <v>-2802588099.359483</v>
+        <v>-3172245621.9974537</v>
       </c>
       <c r="E18">
-        <v>-450974475.8246393</v>
+        <v>-2999174121.522052</v>
       </c>
       <c r="F18">
-        <v>-1793498952</v>
+        <v>-482573859.13649726</v>
       </c>
       <c r="G18">
-        <v>-361529392.68139696</v>
+        <v>-1919284233.8635027</v>
+      </c>
+      <c r="H18">
+        <v>-386884900.4220954</v>
       </c>
     </row>
     <row r="19">
@@ -5124,25 +5664,28 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>854301392</v>
+        <v>586988918.6154796</v>
       </c>
       <c r="C20">
-        <v>2022716574.7068455</v>
+        <v>914216978.3845204</v>
       </c>
       <c r="D20">
-        <v>667310585.7162393</v>
+        <v>2164577808.690706</v>
       </c>
       <c r="E20">
-        <v>47273036.473917365</v>
+        <v>714120477.7586198</v>
       </c>
       <c r="F20">
-        <v>621552231</v>
+        <v>50579762.69440138</v>
       </c>
       <c r="G20">
-        <v>311618731.7481706</v>
+        <v>665144184.3055986</v>
       </c>
       <c r="H20">
-        <v>347135376.4199724</v>
+        <v>333473804.46130526</v>
+      </c>
+      <c r="I20">
+        <v>371481374.0126041</v>
       </c>
     </row>
     <row r="21">
@@ -5185,25 +5728,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-511794505</v>
+        <v>687861524.3369067</v>
       </c>
       <c r="C28">
-        <v>-1944732616.092291</v>
+        <v>-547688708.3369067</v>
       </c>
       <c r="D28">
-        <v>-1957814.4891622886</v>
+        <v>-2081124521.9763353</v>
       </c>
       <c r="E28">
-        <v>89080868.06767513</v>
+        <v>61350267.2545156</v>
       </c>
       <c r="F28">
-        <v>-22047987</v>
+        <v>31883075.844357267</v>
       </c>
       <c r="G28">
-        <v>223496023.63483602</v>
+        <v>-23594300.844357267</v>
       </c>
       <c r="H28">
-        <v>124791127.42721257</v>
+        <v>239170697.04177088</v>
+      </c>
+      <c r="I28">
+        <v>133543230.1925875</v>
       </c>
     </row>
     <row r="29">
@@ -5231,25 +5777,28 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-152962568</v>
+        <v>1772574893.992619</v>
       </c>
       <c r="C33">
-        <v>-2140167271.2321243</v>
+        <v>-163690446.99261913</v>
       </c>
       <c r="D33">
-        <v>-201378514.46026945</v>
+        <v>-2290265794.092581</v>
       </c>
       <c r="E33">
-        <v>-212182925.71576893</v>
+        <v>-215502218.25731614</v>
       </c>
       <c r="F33">
-        <v>195268902</v>
+        <v>-227063946.04326645</v>
       </c>
       <c r="G33">
-        <v>-133272972.66203523</v>
+        <v>208963894.04326645</v>
       </c>
       <c r="H33">
-        <v>12821868.533738852</v>
+        <v>-142619941.28578997</v>
+      </c>
+      <c r="I33">
+        <v>13721117.649962068</v>
       </c>
     </row>
     <row r="34">
@@ -5282,25 +5831,28 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-23859736</v>
+        <v>9213698.07535547</v>
       </c>
       <c r="C39">
-        <v>6920920.778312058</v>
+        <v>-25533115.07535547</v>
       </c>
       <c r="D39">
-        <v>7501067.626593522</v>
+        <v>7406312.737913802</v>
       </c>
       <c r="E39">
-        <v>7002387.745125582</v>
+        <v>8026970.809252143</v>
       </c>
       <c r="F39">
-        <v>-20533305</v>
+        <v>7493670.114703864</v>
       </c>
       <c r="G39">
-        <v>-865207.2229214443</v>
+        <v>-21973388.114703864</v>
       </c>
       <c r="H39">
-        <v>12059.54644624536</v>
+        <v>-925887.679012122</v>
+      </c>
+      <c r="I39">
+        <v>12905.330853978303</v>
       </c>
     </row>
     <row r="40">
@@ -5318,25 +5870,28 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>3401216</v>
+        <v>62702.067059072666</v>
       </c>
       <c r="C42">
-        <v>-2185778.5248396215</v>
+        <v>3639756.9329409273</v>
       </c>
       <c r="D42">
-        <v>2100789.7359070308</v>
+        <v>-2339075.9480310585</v>
       </c>
       <c r="E42">
-        <v>-325246.05552380625</v>
+        <v>2248140.9025427513</v>
       </c>
       <c r="F42">
-        <v>1462717</v>
+        <v>-348071.2155795323</v>
       </c>
       <c r="G42">
-        <v>-698023.4541533373</v>
+        <v>1565303.2155795323</v>
       </c>
       <c r="H42">
-        <v>-579896.6170637745</v>
+        <v>-746978.6413476779</v>
+      </c>
+      <c r="I42">
+        <v>-620567.0949292439</v>
       </c>
     </row>
     <row r="43">
@@ -5349,25 +5904,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-352018284</v>
+        <v>-1056674153.4953732</v>
       </c>
       <c r="C44">
-        <v>186785894.13914812</v>
+        <v>-376706739.5046267</v>
       </c>
       <c r="D44">
-        <v>242906033.55848688</v>
+        <v>199885938.78440374</v>
       </c>
       <c r="E44">
-        <v>234327730.81213343</v>
+        <v>259942943.1057431</v>
       </c>
       <c r="F44">
-        <v>-162668502</v>
+        <v>250761141.11044964</v>
       </c>
       <c r="G44">
-        <v>360540399.1845081</v>
+        <v>-174077097.11044964</v>
       </c>
       <c r="H44">
-        <v>-136310746.9598726</v>
+        <v>385826544.84075785</v>
+      </c>
+      <c r="I44">
+        <v>-145870766.8908863</v>
       </c>
     </row>
     <row r="45">
@@ -5390,25 +5948,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>13644867</v>
+        <v>-37315616.30275375</v>
       </c>
       <c r="C48">
-        <v>3913618.7472124286</v>
+        <v>14601836.302753743</v>
       </c>
       <c r="D48">
-        <v>6200047.58431812</v>
+        <v>4188096.541958533</v>
       </c>
       <c r="E48">
-        <v>971682.7475105077</v>
+        <v>6634430.694293801</v>
       </c>
       <c r="F48">
-        <v>-35577799</v>
+        <v>1040281.8780497313</v>
       </c>
       <c r="G48">
-        <v>-2208172.210562134</v>
+        <v>-38073012.87804973</v>
       </c>
       <c r="H48">
-        <v>-484293.34318636265</v>
+        <v>-2363040.192837216</v>
+      </c>
+      <c r="I48">
+        <v>-518258.7796363719</v>
       </c>
     </row>
     <row r="49">
@@ -5416,16 +5977,25 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-641279067</v>
+        <v>573838175.5116016</v>
       </c>
       <c r="C49">
-        <v>-920425183.9662324</v>
+        <v>-686254542.5116016</v>
+      </c>
+      <c r="D49">
+        <v>-984978297.3485138</v>
+      </c>
+      <c r="E49">
+        <v>90664143.35412303</v>
       </c>
       <c r="F49">
-        <v>26741870</v>
+        <v>58157729.29632196</v>
       </c>
       <c r="G49">
-        <v>196463193.80346608</v>
+        <v>28617384.703678038</v>
+      </c>
+      <c r="H49">
+        <v>210241946.32563257</v>
       </c>
     </row>
     <row r="50">
@@ -5453,16 +6023,22 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-5943986</v>
+        <v>-8208482.398501062</v>
       </c>
       <c r="C54">
-        <v>-2057094.8518471087</v>
-      </c>
-      <c r="G54">
-        <v>989051.6718094558</v>
+        <v>-6360861.601498938</v>
+      </c>
+      <c r="D54">
+        <v>-2201367.1724252747</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>-989051.8059257746</v>
+        <v>1058417.836298924</v>
+      </c>
+      <c r="I54">
+        <v>-1058417.9798213588</v>
       </c>
     </row>
     <row r="55">
@@ -5504,11 +6080,11 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>13989.364933831966</v>
-      </c>
       <c r="D62">
-        <v>25154.549995862704</v>
+        <v>14970.495259741147</v>
+      </c>
+      <c r="E62">
+        <v>26914.05026698578</v>
       </c>
     </row>
     <row r="63">
@@ -5532,25 +6108,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-804217403</v>
+        <v>-535321756.8362262</v>
       </c>
       <c r="C67">
-        <v>3609608.615361521</v>
+        <v>-860620398.1637738</v>
       </c>
       <c r="D67">
-        <v>-3472031.91149975</v>
+        <v>3862764.9590515266</v>
       </c>
       <c r="E67">
-        <v>-461594.6816839443</v>
+        <v>-3715565.9851509556</v>
       </c>
       <c r="F67">
-        <v>-1597561</v>
+        <v>-493941.63334229845</v>
       </c>
       <c r="G67">
-        <v>19669076.493660145</v>
+        <v>-1709604.3666577016</v>
       </c>
       <c r="H67">
-        <v>363844.12761121243</v>
+        <v>21048547.793596447</v>
+      </c>
+      <c r="I67">
+        <v>389361.9770055041</v>
       </c>
     </row>
     <row r="68">
@@ -5572,10 +6151,10 @@
       <c r="A71" t="str">
         <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
-      <c r="B71">
-        <v>-800000000</v>
-      </c>
-      <c r="F71">
+      <c r="C71">
+        <v>-856107211.7597771</v>
+      </c>
+      <c r="G71">
         <v>0</v>
       </c>
     </row>
@@ -5614,25 +6193,28 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-4217403</v>
+        <v>-2382616.596003351</v>
       </c>
       <c r="C78">
-        <v>-4757938.966808565</v>
+        <v>-4513186.403996649</v>
       </c>
       <c r="D78">
-        <v>-3472031.91149975</v>
+        <v>-5091632.3282470945</v>
       </c>
       <c r="E78">
-        <v>-461594.6816839443</v>
+        <v>-3715565.9851509556</v>
       </c>
       <c r="F78">
-        <v>-1597561</v>
+        <v>-493941.63334229845</v>
       </c>
       <c r="G78">
-        <v>-576187.8160553575</v>
+        <v>-1709604.3666577016</v>
       </c>
       <c r="H78">
-        <v>363844.12761121243</v>
+        <v>-616598.1808163822</v>
+      </c>
+      <c r="I78">
+        <v>389361.9770055041</v>
       </c>
     </row>
     <row r="79">
@@ -5746,25 +6328,28 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>201372616</v>
+        <v>56734719.98933464</v>
       </c>
       <c r="C101">
-        <v>2291237780.7936325</v>
+        <v>215495686.01066536</v>
       </c>
       <c r="D101">
-        <v>-83036674.60160631</v>
+        <v>2451931484.99237</v>
       </c>
       <c r="E101">
-        <v>-57984966.99778429</v>
+        <v>-88861648.62118903</v>
       </c>
       <c r="F101">
-        <v>-40024019</v>
+        <v>-62050406.86311207</v>
       </c>
       <c r="G101">
-        <v>-203491483.76559708</v>
+        <v>-42831064.13688793</v>
       </c>
       <c r="H101">
-        <v>107234123.25832309</v>
+        <v>-217763158.47928157</v>
+      </c>
+      <c r="I101">
+        <v>114754882.83523405</v>
       </c>
     </row>
     <row r="102">
@@ -5812,22 +6397,25 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-18478727</v>
+        <v>-4129492.6889498606</v>
       </c>
       <c r="C110">
-        <v>-17394576.55026198</v>
+        <v>-19774714.31105014</v>
       </c>
       <c r="D110">
-        <v>-18135959.221150763</v>
+        <v>-18614528.03773348</v>
       </c>
       <c r="E110">
-        <v>-17162440.94148785</v>
+        <v>-19408388.629658893</v>
       </c>
       <c r="F110">
-        <v>-19751200</v>
-      </c>
-      <c r="H110">
-        <v>-21363196.17477365</v>
+        <v>-18365630.048862863</v>
+      </c>
+      <c r="G110">
+        <v>-21136430.951137137</v>
+      </c>
+      <c r="I110">
+        <v>-22861482.889328256</v>
       </c>
     </row>
     <row r="111">
@@ -5870,25 +6458,28 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-96739663</v>
+        <v>-10364417.05311191</v>
       </c>
       <c r="C118">
-        <v>-100808452.54225054</v>
+        <v>-103524403.94688809</v>
       </c>
       <c r="D118">
-        <v>-116135007.26321775</v>
+        <v>-107878554.03470492</v>
       </c>
       <c r="E118">
-        <v>-78023638.13638785</v>
+        <v>-124281921.25776756</v>
       </c>
       <c r="F118">
-        <v>-67641965</v>
+        <v>-83493849.43237196</v>
       </c>
       <c r="G118">
-        <v>-274161843.5426859</v>
+        <v>-72385967.56762804</v>
       </c>
       <c r="H118">
-        <v>94547953.1853808</v>
+        <v>-293389914.3078114</v>
+      </c>
+      <c r="I118">
+        <v>101178980.72391285</v>
       </c>
     </row>
     <row r="119">
@@ -5896,25 +6487,28 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>316591006</v>
+        <v>71228629.73139644</v>
       </c>
       <c r="C119">
-        <v>208596726.29739502</v>
+        <v>338794804.26860356</v>
       </c>
       <c r="D119">
-        <v>51234291.88276221</v>
+        <v>223226452.16585025</v>
       </c>
       <c r="E119">
-        <v>37201112.08009143</v>
+        <v>54828661.26623747</v>
       </c>
       <c r="F119">
-        <v>47369146</v>
+        <v>39809072.61812276</v>
       </c>
       <c r="G119">
-        <v>88897781.34383303</v>
+        <v>50691334.38187724</v>
       </c>
       <c r="H119">
-        <v>34049366.24771594</v>
+        <v>95132539.64737403</v>
+      </c>
+      <c r="I119">
+        <v>36437385.000649445</v>
       </c>
     </row>
     <row r="120">
@@ -5947,16 +6541,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-1250067840</v>
+        <v>86771675.26620889</v>
       </c>
       <c r="C125">
-        <v>1372379099.955848</v>
+        <v>-1337740116.266209</v>
+      </c>
+      <c r="D125">
+        <v>1468629555.925742</v>
+      </c>
+      <c r="E125">
+        <v>-1886157.2019499764</v>
       </c>
       <c r="F125">
-        <v>-14879710</v>
+        <v>-4772240.200132409</v>
       </c>
       <c r="G125">
-        <v>13629838.203338593</v>
+        <v>-15923283.79986759</v>
+      </c>
+      <c r="H125">
+        <v>14585753.476246366</v>
       </c>
     </row>
     <row r="126">
@@ -5969,25 +6572,28 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-1250067840</v>
+        <v>86771675.26620889</v>
       </c>
       <c r="C127">
-        <v>1372379099.955848</v>
+        <v>-1337740116.266209</v>
       </c>
       <c r="D127">
-        <v>4548238.767174501</v>
+        <v>1468629555.925742</v>
       </c>
       <c r="E127">
-        <v>-10770260.785557617</v>
+        <v>-1886157.2019499764</v>
       </c>
       <c r="F127">
-        <v>-14879710</v>
+        <v>-4772240.200132409</v>
       </c>
       <c r="G127">
-        <v>13629838.203338593</v>
+        <v>-15923283.79986759</v>
       </c>
       <c r="H127">
-        <v>-14689426.640373925</v>
+        <v>14585753.476246366</v>
+      </c>
+      <c r="I127">
+        <v>-15719655.104300389</v>
       </c>
     </row>
     <row r="128">
@@ -5995,16 +6601,25 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>1377215924</v>
+        <v>9312.141493558884</v>
       </c>
       <c r="C128">
-        <v>-6127857.6572637595</v>
+        <v>1473805605.8585064</v>
+      </c>
+      <c r="D128">
+        <v>-6557628.916276097</v>
+      </c>
+      <c r="E128">
+        <v>339.730685852468</v>
       </c>
       <c r="F128">
-        <v>25963556</v>
+        <v>173.58183896169066</v>
       </c>
       <c r="G128">
-        <v>-232248.19704417826</v>
+        <v>27784484.41816104</v>
+      </c>
+      <c r="H128">
+        <v>-248536.69550965854</v>
       </c>
     </row>
     <row r="129">
@@ -6012,28 +6627,37 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1490769</v>
+        <v>-1006314.6149598889</v>
       </c>
       <c r="C129">
-        <v>1372379099.7986684</v>
+        <v>1595322.6149598889</v>
+      </c>
+      <c r="D129">
+        <v>1468629555.7575386</v>
+      </c>
+      <c r="E129">
+        <v>4867229.528735872</v>
       </c>
       <c r="F129">
-        <v>4960175</v>
+        <v>-4971964.98636319</v>
       </c>
       <c r="G129">
-        <v>19293201.23361358</v>
+        <v>5308051.98636319</v>
+      </c>
+      <c r="H129">
+        <v>20646310.892536517</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6045,6 +6669,7 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6052,30 +6677,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -6089,22 +6717,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-1430958096.2789545</v>
+        <v>-1023730328.6212894</v>
       </c>
       <c r="C3">
-        <v>-756993173.2789545</v>
+        <v>-1531316932.438068</v>
       </c>
       <c r="D3">
-        <v>362927361.6494667</v>
+        <v>-810084143.6212894</v>
       </c>
       <c r="E3">
-        <v>159475045.1238343</v>
-      </c>
-      <c r="G3">
-        <v>105488105.35862738</v>
-      </c>
-      <c r="J3">
-        <v>-15710950.149595967</v>
+        <v>388380914.5663215</v>
+      </c>
+      <c r="F3">
+        <v>166825957.24539155</v>
+      </c>
+      <c r="H3">
+        <v>112886409.6904951</v>
+      </c>
+      <c r="K3">
+        <v>-16812822.15833432</v>
       </c>
     </row>
     <row r="4">
@@ -6112,22 +6743,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>3220637219.9533195</v>
+        <v>2509684840.775069</v>
       </c>
       <c r="C4">
-        <v>5024549518.95332</v>
+        <v>3446513438.079995</v>
       </c>
       <c r="D4">
-        <v>3716506851.3616104</v>
+        <v>5376941348.775069</v>
       </c>
       <c r="E4">
-        <v>1611811629.017033</v>
-      </c>
-      <c r="G4">
-        <v>317427109.4333314</v>
-      </c>
-      <c r="J4">
-        <v>1725232325.1139624</v>
+        <v>3977160397.506621</v>
+      </c>
+      <c r="F4">
+        <v>1724831690.2431011</v>
+      </c>
+      <c r="H4">
+        <v>339689546.9924187</v>
+      </c>
+      <c r="K4">
+        <v>1846229794.3639395</v>
       </c>
     </row>
     <row r="5">
@@ -6135,16 +6769,19 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-2273868959.074337</v>
+        <v>-1636813923.0476403</v>
       </c>
       <c r="C5">
-        <v>-3899506839.074337</v>
+        <v>-2433344518.0752964</v>
       </c>
       <c r="D5">
-        <v>-3642804433.440057</v>
-      </c>
-      <c r="G5">
-        <v>-449695554.38085645</v>
+        <v>-4172994909.0476403</v>
+      </c>
+      <c r="E5">
+        <v>-3898288933.123152</v>
+      </c>
+      <c r="H5">
+        <v>-481234509.0022028</v>
       </c>
     </row>
     <row r="6">
@@ -6152,19 +6789,22 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>6261560.939215167</v>
+        <v>7033899.098865354</v>
       </c>
       <c r="C6">
-        <v>5753800.939215167</v>
+        <v>6700709.346169285</v>
       </c>
       <c r="D6">
-        <v>5500420.593555903</v>
+        <v>6157338.098865354</v>
       </c>
       <c r="E6">
-        <v>5397714.3329448905</v>
-      </c>
-      <c r="G6">
-        <v>4255217.591726501</v>
+        <v>5886187.172319003</v>
+      </c>
+      <c r="F6">
+        <v>5776241.792390191</v>
+      </c>
+      <c r="H6">
+        <v>4553653.08485516</v>
       </c>
     </row>
     <row r="7">
@@ -6177,22 +6817,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1353857.558185135</v>
+        <v>2840607.0074277082</v>
       </c>
       <c r="C8">
-        <v>1661311.558185135</v>
+        <v>1448809.02407222</v>
       </c>
       <c r="D8">
-        <v>1064045.6168407078</v>
+        <v>1777826.0074277082</v>
       </c>
       <c r="E8">
-        <v>624952.0056254927</v>
-      </c>
-      <c r="G8">
-        <v>1819353.0714056012</v>
-      </c>
-      <c r="J8">
-        <v>9233.007295261752</v>
+        <v>1138671.4077733885</v>
+      </c>
+      <c r="F8">
+        <v>668769.2106987778</v>
+      </c>
+      <c r="H8">
+        <v>1946951.606459545</v>
+      </c>
+      <c r="K8">
+        <v>9880.555164630274</v>
       </c>
     </row>
     <row r="9">
@@ -6215,19 +6858,22 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-221916375.31839254</v>
+        <v>-342029251.1396153</v>
       </c>
       <c r="C12">
-        <v>18207786.68160746</v>
+        <v>-237480261.64708155</v>
       </c>
       <c r="D12">
-        <v>313159323.54398036</v>
+        <v>19484771.860384706</v>
       </c>
       <c r="E12">
-        <v>115862888.87000383</v>
-      </c>
-      <c r="G12">
-        <v>179801257.57448626</v>
+        <v>335122444.1447687</v>
+      </c>
+      <c r="F12">
+        <v>126020418.93587506</v>
+      </c>
+      <c r="H12">
+        <v>192411441.61624366</v>
       </c>
     </row>
     <row r="13">
@@ -6259,17 +6905,20 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>-8011405785.400775</v>
+      <c r="B18">
+        <v>-6171419743.5195055</v>
       </c>
       <c r="D18">
-        <v>-5408590919.865519</v>
-      </c>
-      <c r="G18">
-        <v>-625627417.7373779</v>
-      </c>
-      <c r="J18">
-        <v>-2149829478.5554614</v>
+        <v>-8573277836.5195055</v>
+      </c>
+      <c r="E18">
+        <v>-5787917114.944147</v>
+      </c>
+      <c r="H18">
+        <v>-669505180.2495198</v>
+      </c>
+      <c r="K18">
+        <v>-2300605650.8063645</v>
       </c>
     </row>
     <row r="19">
@@ -6282,33 +6931,33 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>3591601588.897002</v>
+        <v>4379904183.449326</v>
       </c>
       <c r="C20">
-        <v>3358852427.897002</v>
+        <v>3843495027.5282474</v>
       </c>
       <c r="D20">
-        <v>1647754584.9383273</v>
+        <v>3594422233.4493256</v>
       </c>
       <c r="E20">
-        <v>1327579374.5335789</v>
-      </c>
-      <c r="G20">
-        <v>873079826.2689741</v>
-      </c>
-      <c r="J20">
-        <v>432015906.28361166</v>
+        <v>1763318229.219925</v>
+      </c>
+      <c r="F20">
+        <v>1420679125.4739094</v>
+      </c>
+      <c r="H20">
+        <v>934312419.6385524</v>
+      </c>
+      <c r="K20">
+        <v>462314916.2054199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="E21">
-        <v>-138040972.37909812</v>
-      </c>
-      <c r="J21">
-        <v>-165111774.47341618</v>
+      <c r="K21">
+        <v>-176691726.09143183</v>
       </c>
     </row>
     <row r="22">
@@ -6346,22 +6995,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-2369404067.513778</v>
+        <v>-1879601438.7218196</v>
       </c>
       <c r="C28">
-        <v>-1879657549.5137782</v>
+        <v>-2535579887.214369</v>
       </c>
       <c r="D28">
-        <v>288571090.21334887</v>
+        <v>-2011485479.7218196</v>
       </c>
       <c r="E28">
-        <v>53134740.97778855</v>
-      </c>
-      <c r="G28">
-        <v>239808869.3263382</v>
-      </c>
-      <c r="J28">
-        <v>-157683788.62400827</v>
+        <v>308809739.29628646</v>
+      </c>
+      <c r="F28">
+        <v>381002702.2343584</v>
+      </c>
+      <c r="H28">
+        <v>256627628.09279516</v>
+      </c>
+      <c r="K28">
+        <v>-168742785.77327222</v>
       </c>
     </row>
     <row r="29">
@@ -6389,22 +7041,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-2706691279.4081626</v>
+        <v>-896883565.3498969</v>
       </c>
       <c r="C33">
-        <v>-2358459809.4081626</v>
+        <v>-2896522405.3857822</v>
       </c>
       <c r="D33">
-        <v>-351565510.8380736</v>
+        <v>-2523868064.349897</v>
       </c>
       <c r="E33">
-        <v>-137365128.34342325</v>
-      </c>
-      <c r="G33">
-        <v>-710919532.3840551</v>
-      </c>
-      <c r="J33">
-        <v>-14615404.88512437</v>
+        <v>-376222211.5431061</v>
+      </c>
+      <c r="F33">
+        <v>-146998875.6358279</v>
+      </c>
+      <c r="H33">
+        <v>-760779173.3185974</v>
+      </c>
+      <c r="K33">
+        <v>-15640441.906180063</v>
       </c>
     </row>
     <row r="34">
@@ -6437,22 +7092,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-2435359.8499688394</v>
+        <v>-886133.4528340548</v>
       </c>
       <c r="C39">
-        <v>891071.1500311622</v>
+        <v>-2606161.413485661</v>
       </c>
       <c r="D39">
-        <v>-6895056.85120234</v>
+        <v>953565.5471659453</v>
       </c>
       <c r="E39">
-        <v>-14384064.90610663</v>
-      </c>
-      <c r="G39">
-        <v>-896785.6416942005</v>
-      </c>
-      <c r="J39">
-        <v>-5702.267776014711</v>
+        <v>-7378634.869759979</v>
+      </c>
+      <c r="F39">
+        <v>-15392700.348158143</v>
+      </c>
+      <c r="H39">
+        <v>-959680.8190712805</v>
+      </c>
+      <c r="K39">
+        <v>-6102.190708039474</v>
       </c>
     </row>
     <row r="40">
@@ -6470,22 +7128,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>2990981.155543603</v>
+        <v>3611523.9545116927</v>
       </c>
       <c r="C42">
-        <v>1052482.155543603</v>
+        <v>3200750.6718730875</v>
       </c>
       <c r="D42">
-        <v>2540237.2262298875</v>
+        <v>1126296.9545116925</v>
       </c>
       <c r="E42">
-        <v>-140449.36140758614</v>
-      </c>
-      <c r="G42">
-        <v>1297609.9687296343</v>
-      </c>
-      <c r="J42">
-        <v>133903.9135295977</v>
+        <v>2718394.2611950734</v>
+      </c>
+      <c r="F42">
+        <v>-150313.73627692182</v>
+      </c>
+      <c r="H42">
+        <v>1388616.5653510233</v>
+      </c>
+      <c r="K42">
+        <v>143295.13256943272</v>
       </c>
     </row>
     <row r="43">
@@ -6498,22 +7159,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>312001374.5097685</v>
+        <v>-973552011.1098531</v>
       </c>
       <c r="C44">
-        <v>501351156.5097684</v>
+        <v>333883283.49596983</v>
       </c>
       <c r="D44">
-        <v>675105661.5551283</v>
+        <v>536512925.89014685</v>
       </c>
       <c r="E44">
-        <v>295888881.1335846</v>
-      </c>
-      <c r="G44">
-        <v>960093298.102969</v>
-      </c>
-      <c r="J44">
-        <v>156516448.36391386</v>
+        <v>722453531.946501</v>
+      </c>
+      <c r="F44">
+        <v>316639821.94987154</v>
+      </c>
+      <c r="H44">
+        <v>1027428495.5852267</v>
+      </c>
+      <c r="K44">
+        <v>167493575.2542168</v>
       </c>
     </row>
     <row r="45">
@@ -6536,22 +7200,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>24730216.079041056</v>
+        <v>-11891252.763747666</v>
       </c>
       <c r="C48">
-        <v>-24492449.920958944</v>
+        <v>26464645.417055808</v>
       </c>
       <c r="D48">
-        <v>-30614240.87873351</v>
+        <v>-26210203.763747666</v>
       </c>
       <c r="E48">
-        <v>-37298581.66936022</v>
-      </c>
-      <c r="G48">
-        <v>-9765720.719611142</v>
-      </c>
-      <c r="J48">
-        <v>-56406.65013074003</v>
+        <v>-32761340.498543415</v>
+      </c>
+      <c r="F48">
+        <v>-39914029.97247359</v>
+      </c>
+      <c r="H48">
+        <v>-10450629.920113724</v>
+      </c>
+      <c r="K48">
+        <v>-60362.6749601714</v>
       </c>
     </row>
     <row r="49">
@@ -6559,16 +7226,19 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-1422635806.6347957</v>
+        <v>-1006730520.9943908</v>
       </c>
       <c r="C49">
-        <v>-754614869.6347958</v>
+        <v>-1522410967.2096705</v>
       </c>
       <c r="D49">
-        <v>362273508.1349027</v>
-      </c>
-      <c r="G49">
-        <v>107540424.3788131</v>
+        <v>-807539039.9943908</v>
+      </c>
+      <c r="E49">
+        <v>387681203.67975557</v>
+      </c>
+      <c r="H49">
+        <v>115082666.08301106</v>
       </c>
     </row>
     <row r="50">
@@ -6595,14 +7265,20 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="C54">
-        <v>-2057094.8518471087</v>
+      <c r="B54">
+        <v>-16770711.172425274</v>
       </c>
       <c r="D54">
-        <v>989051.6718094558</v>
-      </c>
-      <c r="G54">
-        <v>-2052319.020185721</v>
+        <v>-2201367.1724252747</v>
+      </c>
+      <c r="E54">
+        <v>1058417.836298924</v>
+      </c>
+      <c r="F54">
+        <v>-0.1435224348679185</v>
+      </c>
+      <c r="H54">
+        <v>-2196256.3925159443</v>
       </c>
     </row>
     <row r="55">
@@ -6644,8 +7320,11 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-321208.7923116108</v>
+      <c r="B62">
+        <v>-229096.45447327307</v>
+      </c>
+      <c r="D62">
+        <v>-343736.4544732731</v>
       </c>
     </row>
     <row r="63">
@@ -6669,19 +7348,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-804541420.9778222</v>
+        <v>-1395794956.0260994</v>
       </c>
       <c r="C67">
-        <v>-1921578.9778221732</v>
+        <v>-860967140.8232155</v>
       </c>
       <c r="D67">
-        <v>14137888.90047645</v>
+        <v>-2056347.026099429</v>
       </c>
       <c r="E67">
-        <v>-2271500.035183275</v>
-      </c>
-      <c r="G67">
-        <v>-7280105.018358676</v>
+        <v>15129435.80844549</v>
+      </c>
+      <c r="F67">
+        <v>19234363.77060195</v>
+      </c>
+      <c r="H67">
+        <v>-7790688.010731759</v>
       </c>
     </row>
     <row r="68">
@@ -6739,22 +7421,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-12908968.55999226</v>
+        <v>-15703001.31339805</v>
       </c>
       <c r="C78">
-        <v>-10289126.55999226</v>
+        <v>-13814326.350736998</v>
       </c>
       <c r="D78">
-        <v>-6107375.409239052</v>
+        <v>-11010744.31339805</v>
       </c>
       <c r="E78">
-        <v>17973765.306276478</v>
-      </c>
-      <c r="G78">
-        <v>-27525369.328074176</v>
-      </c>
-      <c r="J78">
-        <v>14615404.88512437</v>
+        <v>-6535710.165967338</v>
+      </c>
+      <c r="F78">
+        <v>-2430782.203810878</v>
+      </c>
+      <c r="H78">
+        <v>-29455833.98514459</v>
+      </c>
+      <c r="K78">
+        <v>15640441.906180063</v>
       </c>
     </row>
     <row r="79">
@@ -6826,11 +7511,11 @@
       <c r="A92" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="C92">
-        <v>8367547.582170086</v>
-      </c>
-      <c r="G92">
-        <v>20245264.3097155</v>
+      <c r="D92">
+        <v>8954397.287298622</v>
+      </c>
+      <c r="H92">
+        <v>21665145.97441283</v>
       </c>
     </row>
     <row r="93">
@@ -6862,8 +7547,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="J98">
-        <v>14615404.88512437</v>
+      <c r="K98">
+        <v>15640441.906180063</v>
       </c>
     </row>
     <row r="99">
@@ -6877,22 +7562,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>2351588755.1942415</v>
+        <v>2635300242.371181</v>
       </c>
       <c r="C101">
-        <v>2110192120.1942418</v>
+        <v>2516515115.5187345</v>
       </c>
       <c r="D101">
-        <v>-384537144.3649877</v>
+        <v>2258188365.371181</v>
       </c>
       <c r="E101">
-        <v>-192367147.8278893</v>
-      </c>
-      <c r="G101">
-        <v>-85019226.48664293</v>
-      </c>
-      <c r="J101">
-        <v>2079585.8244475876</v>
+        <v>-411506278.1004706</v>
+      </c>
+      <c r="F101">
+        <v>-207889746.64404753</v>
+      </c>
+      <c r="H101">
+        <v>-90981966.16681609</v>
+      </c>
+      <c r="K101">
+        <v>2225435.527228727</v>
       </c>
     </row>
     <row r="102">
@@ -6909,8 +7597,8 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
-        <v>2200844083.58875</v>
+      <c r="D104">
+        <v>2355198114.898958</v>
       </c>
     </row>
     <row r="105">
@@ -6927,8 +7615,8 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="J107">
-        <v>2079585.8244475876</v>
+      <c r="K107">
+        <v>2225435.527228727</v>
       </c>
     </row>
     <row r="108">
@@ -6940,8 +7628,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="G109">
-        <v>94782031.08784331</v>
+      <c r="H109">
+        <v>101429475.44942756</v>
       </c>
     </row>
     <row r="110">
@@ -6949,13 +7637,13 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-71171703.7129006</v>
+        <v>-61927123.66739237</v>
       </c>
       <c r="C110">
-        <v>-72444176.7129006</v>
-      </c>
-      <c r="E110">
-        <v>-76504258.95788543</v>
+        <v>-76163261.02730536</v>
+      </c>
+      <c r="D110">
+        <v>-77524977.66739237</v>
       </c>
     </row>
     <row r="111">
@@ -6998,19 +7686,22 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-391706760.94185615</v>
+        <v>-346049296.2924725</v>
       </c>
       <c r="C118">
-        <v>-362609062.94185615</v>
+        <v>-419178728.67173254</v>
       </c>
       <c r="D118">
-        <v>-535962453.9422915</v>
+        <v>-388040292.2924725</v>
       </c>
       <c r="E118">
-        <v>-323380294.30111396</v>
-      </c>
-      <c r="G118">
-        <v>-307195588.86680496</v>
+        <v>-573551652.5655789</v>
+      </c>
+      <c r="F118">
+        <v>-348090750.58389854</v>
+      </c>
+      <c r="H118">
+        <v>-328740448.812079</v>
       </c>
     </row>
     <row r="119">
@@ -7018,19 +7709,22 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>613623136.2602487</v>
+        <v>688078547.4320877</v>
       </c>
       <c r="C119">
-        <v>344401276.26024866</v>
+        <v>656658990.318814</v>
       </c>
       <c r="D119">
-        <v>224702331.30668667</v>
+        <v>368555520.4320877</v>
       </c>
       <c r="E119">
-        <v>207517405.43111008</v>
-      </c>
-      <c r="G119">
-        <v>127394331.29231873</v>
+        <v>240461607.9136115</v>
+      </c>
+      <c r="F119">
+        <v>222070331.6480235</v>
+      </c>
+      <c r="H119">
+        <v>136329007.19583538</v>
       </c>
     </row>
     <row r="120">
@@ -7063,16 +7757,19 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>116089237.93746495</v>
+        <v>215774957.72379184</v>
       </c>
       <c r="C125">
-        <v>1351277367.937465</v>
+        <v>124231042.25745058</v>
       </c>
       <c r="D125">
-        <v>-7471893.815044522</v>
-      </c>
-      <c r="G125">
-        <v>13188773.853625774</v>
+        <v>1446047874.7237918</v>
+      </c>
+      <c r="E125">
+        <v>-7995927.72570361</v>
+      </c>
+      <c r="H125">
+        <v>14113755.512947265</v>
       </c>
     </row>
     <row r="126">
@@ -7085,22 +7782,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>116089237.93746495</v>
+        <v>215774957.72379184</v>
       </c>
       <c r="C127">
-        <v>1351277367.937465</v>
+        <v>124231042.25745058</v>
       </c>
       <c r="D127">
-        <v>-7471893.815044522</v>
+        <v>1446047874.7237918</v>
       </c>
       <c r="E127">
-        <v>-14918337.397778539</v>
-      </c>
-      <c r="G127">
-        <v>13188773.853625774</v>
-      </c>
-      <c r="J127">
-        <v>984040.5599759909</v>
+        <v>-7995927.72570361</v>
+      </c>
+      <c r="F127">
+        <v>-21829425.628054023</v>
+      </c>
+      <c r="H127">
+        <v>14113755.512947265</v>
+      </c>
+      <c r="K127">
+        <v>1053055.2750744692</v>
       </c>
     </row>
     <row r="128">
@@ -7108,16 +7808,19 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>1371088546.0139902</v>
+        <v>1467257628.8144097</v>
       </c>
       <c r="C128">
-        <v>19836178.01399027</v>
+        <v>1467248490.2547553</v>
       </c>
       <c r="D128">
-        <v>25731787.474209853</v>
-      </c>
-      <c r="G128">
-        <v>751792.9330453317</v>
+        <v>21227368.814409755</v>
+      </c>
+      <c r="E128">
+        <v>27536461.035176195</v>
+      </c>
+      <c r="H128">
+        <v>804519.1896626797</v>
       </c>
     </row>
     <row r="129">
@@ -7125,21 +7828,24 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1373771997.4515393</v>
+        <v>1474085793.2862744</v>
       </c>
       <c r="C129">
-        <v>1377241403.4515393</v>
+        <v>1470120142.9148712</v>
       </c>
       <c r="D129">
-        <v>24155504.886484496</v>
-      </c>
-      <c r="G129">
-        <v>19836178.01399027</v>
+        <v>1473832872.2862744</v>
+      </c>
+      <c r="E129">
+        <v>25849627.42127239</v>
+      </c>
+      <c r="H129">
+        <v>21227368.814409755</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>